--- a/gabarito/Bolao_Copa2026_TurimMFO_Master - Copia.xlsx
+++ b/gabarito/Bolao_Copa2026_TurimMFO_Master - Copia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pbrandao\Projetos\bolao-copa-2026\gabarito\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA69064-1B36-46F5-AFBE-29FE0C18FB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DACC5F-AE09-4446-A8D2-3EE8EF6BBA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regras" sheetId="1" r:id="rId1"/>
@@ -4914,83 +4914,77 @@
     <xf numFmtId="0" fontId="66" fillId="60" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="46" fillId="41" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="47" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="41" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="42" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="44" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4999,13 +4993,22 @@
     <xf numFmtId="164" fontId="46" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5021,9 +5024,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5481,13 +5481,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="252" t="s">
+      <c r="B1" s="254" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="253"/>
     </row>
     <row r="2" spans="2:3" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="254" t="s">
+      <c r="B2" s="255" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="253"/>
@@ -5715,7 +5715,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:65" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="255" t="s">
+      <c r="A1" s="252" t="s">
         <v>1027</v>
       </c>
       <c r="B1" s="253"/>
@@ -5784,7 +5784,7 @@
       <c r="BM1" s="253"/>
     </row>
     <row r="2" spans="1:65" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="256" t="s">
+      <c r="A2" s="268" t="s">
         <v>1028</v>
       </c>
       <c r="B2" s="253"/>
@@ -5920,67 +5920,67 @@
         <v>994</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="270" t="s">
+      <c r="AH3" s="273" t="s">
         <v>996</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="270" t="s">
+      <c r="AJ3" s="273" t="s">
         <v>998</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="270" t="s">
+      <c r="AL3" s="273" t="s">
         <v>1000</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="270" t="s">
+      <c r="AN3" s="273" t="s">
         <v>1002</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="270" t="s">
+      <c r="AP3" s="273" t="s">
         <v>1004</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="270" t="s">
+      <c r="AR3" s="273" t="s">
         <v>1006</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="270" t="s">
+      <c r="AT3" s="273" t="s">
         <v>1008</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="270" t="s">
+      <c r="AV3" s="273" t="s">
         <v>1010</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="274" t="s">
+      <c r="AX3" s="275" t="s">
         <v>1012</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="274" t="s">
+      <c r="AZ3" s="275" t="s">
         <v>1014</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="274" t="s">
+      <c r="BB3" s="275" t="s">
         <v>1016</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="274" t="s">
+      <c r="BD3" s="275" t="s">
         <v>1018</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="277" t="s">
+      <c r="BF3" s="281" t="s">
         <v>1020</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="277" t="s">
+      <c r="BH3" s="281" t="s">
         <v>1022</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="273" t="s">
+      <c r="BJ3" s="279" t="s">
         <v>1024</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="275" t="s">
+      <c r="BL3" s="280" t="s">
         <v>1026</v>
       </c>
       <c r="BM3" s="253"/>
@@ -5989,131 +5989,131 @@
       <c r="A4" s="210" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="272">
+      <c r="B4" s="270">
         <v>46201</v>
       </c>
       <c r="C4" s="253"/>
-      <c r="D4" s="272">
+      <c r="D4" s="270">
         <v>46202</v>
       </c>
       <c r="E4" s="253"/>
-      <c r="F4" s="272">
+      <c r="F4" s="270">
         <v>46202</v>
       </c>
       <c r="G4" s="253"/>
-      <c r="H4" s="272">
+      <c r="H4" s="270">
         <v>46202</v>
       </c>
       <c r="I4" s="253"/>
-      <c r="J4" s="272">
+      <c r="J4" s="270">
         <v>46203</v>
       </c>
       <c r="K4" s="253"/>
-      <c r="L4" s="272">
+      <c r="L4" s="270">
         <v>46203</v>
       </c>
       <c r="M4" s="253"/>
-      <c r="N4" s="272">
+      <c r="N4" s="270">
         <v>46203</v>
       </c>
       <c r="O4" s="253"/>
-      <c r="P4" s="272">
+      <c r="P4" s="270">
         <v>46204</v>
       </c>
       <c r="Q4" s="253"/>
-      <c r="R4" s="272">
+      <c r="R4" s="270">
         <v>46204</v>
       </c>
       <c r="S4" s="253"/>
-      <c r="T4" s="272">
+      <c r="T4" s="270">
         <v>46204</v>
       </c>
       <c r="U4" s="253"/>
-      <c r="V4" s="272">
+      <c r="V4" s="270">
         <v>46205</v>
       </c>
       <c r="W4" s="253"/>
-      <c r="X4" s="272">
+      <c r="X4" s="270">
         <v>46205</v>
       </c>
       <c r="Y4" s="253"/>
-      <c r="Z4" s="272">
+      <c r="Z4" s="270">
         <v>46205</v>
       </c>
       <c r="AA4" s="253"/>
-      <c r="AB4" s="272">
+      <c r="AB4" s="270">
         <v>46206</v>
       </c>
       <c r="AC4" s="253"/>
-      <c r="AD4" s="272">
+      <c r="AD4" s="270">
         <v>46206</v>
       </c>
       <c r="AE4" s="253"/>
-      <c r="AF4" s="272">
+      <c r="AF4" s="270">
         <v>46206</v>
       </c>
       <c r="AG4" s="253"/>
-      <c r="AH4" s="276">
+      <c r="AH4" s="274">
         <v>46207</v>
       </c>
       <c r="AI4" s="253"/>
-      <c r="AJ4" s="276">
+      <c r="AJ4" s="274">
         <v>46207</v>
       </c>
       <c r="AK4" s="253"/>
-      <c r="AL4" s="276">
+      <c r="AL4" s="274">
         <v>46208</v>
       </c>
       <c r="AM4" s="253"/>
-      <c r="AN4" s="276">
+      <c r="AN4" s="274">
         <v>46208</v>
       </c>
       <c r="AO4" s="253"/>
-      <c r="AP4" s="276">
+      <c r="AP4" s="274">
         <v>46209</v>
       </c>
       <c r="AQ4" s="253"/>
-      <c r="AR4" s="276">
+      <c r="AR4" s="274">
         <v>46209</v>
       </c>
       <c r="AS4" s="253"/>
-      <c r="AT4" s="276">
+      <c r="AT4" s="274">
         <v>46210</v>
       </c>
       <c r="AU4" s="253"/>
-      <c r="AV4" s="276">
+      <c r="AV4" s="274">
         <v>46210</v>
       </c>
       <c r="AW4" s="253"/>
-      <c r="AX4" s="278">
+      <c r="AX4" s="272">
         <v>46212</v>
       </c>
       <c r="AY4" s="253"/>
-      <c r="AZ4" s="278">
+      <c r="AZ4" s="272">
         <v>46213</v>
       </c>
       <c r="BA4" s="253"/>
-      <c r="BB4" s="278">
+      <c r="BB4" s="272">
         <v>46214</v>
       </c>
       <c r="BC4" s="253"/>
-      <c r="BD4" s="278">
+      <c r="BD4" s="272">
         <v>46214</v>
       </c>
       <c r="BE4" s="253"/>
-      <c r="BF4" s="279">
+      <c r="BF4" s="277">
         <v>46217</v>
       </c>
       <c r="BG4" s="253"/>
-      <c r="BH4" s="279">
+      <c r="BH4" s="277">
         <v>46218</v>
       </c>
       <c r="BI4" s="253"/>
-      <c r="BJ4" s="281">
+      <c r="BJ4" s="276">
         <v>46221</v>
       </c>
       <c r="BK4" s="253"/>
-      <c r="BL4" s="280">
+      <c r="BL4" s="278">
         <v>46222</v>
       </c>
       <c r="BM4" s="253"/>
@@ -7568,19 +7568,43 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="AX4:AY4"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AR4:AS4"/>
-    <mergeCell ref="AV4:AW4"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="A2:BM2"/>
+    <mergeCell ref="AR3:AS3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="AD4:AE4"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="BJ3:BK3"/>
+    <mergeCell ref="AZ3:BA3"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="BL3:BM3"/>
+    <mergeCell ref="AJ4:AK4"/>
+    <mergeCell ref="AL4:AM4"/>
+    <mergeCell ref="BF3:BG3"/>
+    <mergeCell ref="BH3:BI3"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="A1:BM1"/>
+    <mergeCell ref="AT4:AU4"/>
+    <mergeCell ref="AZ4:BA4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="BB4:BC4"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="BD4:BE4"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="BF4:BG4"/>
+    <mergeCell ref="BL4:BM4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="BH4:BI4"/>
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AP4:AQ4"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="AP3:AQ3"/>
     <mergeCell ref="BB3:BC3"/>
@@ -7597,43 +7621,19 @@
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="AV3:AW3"/>
     <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="BH4:BI4"/>
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AP4:AQ4"/>
-    <mergeCell ref="A1:BM1"/>
-    <mergeCell ref="AT4:AU4"/>
-    <mergeCell ref="AZ4:BA4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="BB4:BC4"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="BD4:BE4"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="BF4:BG4"/>
-    <mergeCell ref="BL4:BM4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="A2:BM2"/>
-    <mergeCell ref="AR3:AS3"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="AD4:AE4"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="BJ3:BK3"/>
-    <mergeCell ref="AZ3:BA3"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="BL3:BM3"/>
-    <mergeCell ref="AJ4:AK4"/>
-    <mergeCell ref="AL4:AM4"/>
-    <mergeCell ref="BF3:BG3"/>
-    <mergeCell ref="BH3:BI3"/>
-    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="AX4:AY4"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AR4:AS4"/>
+    <mergeCell ref="AV4:AW4"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="X3:Y3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7653,7 +7653,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="255" t="s">
+      <c r="A1" s="252" t="s">
         <v>1031</v>
       </c>
       <c r="B1" s="253"/>
@@ -7691,7 +7691,7 @@
       <c r="AH1" s="253"/>
     </row>
     <row r="2" spans="1:34" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="256" t="s">
+      <c r="A2" s="268" t="s">
         <v>1032</v>
       </c>
       <c r="B2" s="253"/>
@@ -8425,7 +8425,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="255" t="s">
+      <c r="A1" s="252" t="s">
         <v>1065</v>
       </c>
       <c r="B1" s="253"/>
@@ -8857,7 +8857,7 @@
       <c r="J1" s="253"/>
     </row>
     <row r="2" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="256" t="s">
+      <c r="A2" s="268" t="s">
         <v>1079</v>
       </c>
       <c r="B2" s="253"/>
@@ -8871,49 +8871,49 @@
       <c r="J2" s="253"/>
     </row>
     <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="289" t="s">
+      <c r="A4" s="284" t="s">
         <v>1080</v>
       </c>
       <c r="B4" s="253"/>
-      <c r="C4" s="289" t="s">
+      <c r="C4" s="284" t="s">
         <v>1081</v>
       </c>
       <c r="D4" s="253"/>
-      <c r="E4" s="289" t="s">
+      <c r="E4" s="284" t="s">
         <v>1082</v>
       </c>
       <c r="F4" s="253"/>
-      <c r="G4" s="289" t="s">
+      <c r="G4" s="284" t="s">
         <v>1083</v>
       </c>
       <c r="H4" s="253"/>
-      <c r="I4" s="289" t="s">
+      <c r="I4" s="284" t="s">
         <v>1084</v>
       </c>
       <c r="J4" s="253"/>
     </row>
     <row r="5" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="285" t="str">
+      <c r="A5" s="286" t="str">
         <f>IFERROR(INDEX(Ranking!$I$4:$I$7,MATCH(1,Ranking!$P$4:$P$7,0)),"?")</f>
         <v>Pedro Brandao</v>
       </c>
       <c r="B5" s="253"/>
-      <c r="C5" s="284">
+      <c r="C5" s="285">
         <f>IFERROR(MAX(Ranking!$M$4:$M$7),0)</f>
         <v>0</v>
       </c>
       <c r="D5" s="253"/>
-      <c r="E5" s="287">
+      <c r="E5" s="288">
         <f>COUNTIF('Jogos - Grupos'!H3:H74,"Finalizado")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5" s="253"/>
-      <c r="G5" s="286">
+      <c r="G5" s="287">
         <f>COUNTIF('Mata-Mata - Jogos'!I4:I35,"Finalizado")</f>
         <v>0</v>
       </c>
       <c r="H5" s="253"/>
-      <c r="I5" s="288" t="s">
+      <c r="I5" s="289" t="s">
         <v>1077</v>
       </c>
       <c r="J5" s="253"/>
@@ -9064,6 +9064,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="I5:J5"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="A1:J1"/>
@@ -9071,11 +9076,6 @@
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="I5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9098,7 +9098,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="255" t="s">
+      <c r="A1" s="252" t="s">
         <v>44</v>
       </c>
       <c r="B1" s="253"/>
@@ -9151,15 +9151,11 @@
       <c r="E3" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="10">
-        <v>2</v>
-      </c>
-      <c r="G3" s="10">
-        <v>1</v>
-      </c>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
       <c r="H3" s="11" t="str">
         <f t="shared" ref="H3:H34" si="0">IF(AND(F3="",G3=""),"Aguardando",IF(AND(ISNUMBER(F3),ISNUMBER(G3)),"Finalizado","Verificar"))</f>
-        <v>Finalizado</v>
+        <v>Aguardando</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -9178,15 +9174,11 @@
       <c r="E4" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="10">
-        <v>1</v>
-      </c>
-      <c r="G4" s="10">
-        <v>2</v>
-      </c>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
       <c r="H4" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>Finalizado</v>
+        <v>Aguardando</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -9435,15 +9427,11 @@
       <c r="E15" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="10">
-        <v>2</v>
-      </c>
-      <c r="G15" s="10">
-        <v>0</v>
-      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
       <c r="H15" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>Finalizado</v>
+        <v>Aguardando</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -9462,15 +9450,11 @@
       <c r="E16" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="F16" s="10">
-        <v>1</v>
-      </c>
-      <c r="G16" s="10">
-        <v>2</v>
-      </c>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
       <c r="H16" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>Finalizado</v>
+        <v>Aguardando</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -10828,7 +10812,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:145" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="255" t="s">
+      <c r="A1" s="252" t="s">
         <v>185</v>
       </c>
       <c r="B1" s="253"/>
@@ -10977,7 +10961,7 @@
       <c r="EO1" s="253"/>
     </row>
     <row r="2" spans="1:145" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="256" t="s">
+      <c r="A2" s="268" t="s">
         <v>186</v>
       </c>
       <c r="B2" s="253"/>
@@ -11129,147 +11113,147 @@
       <c r="A3" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="B3" s="258" t="s">
+      <c r="B3" s="256" t="s">
         <v>188</v>
       </c>
       <c r="C3" s="253"/>
-      <c r="D3" s="258" t="s">
+      <c r="D3" s="256" t="s">
         <v>189</v>
       </c>
       <c r="E3" s="253"/>
-      <c r="F3" s="258" t="s">
+      <c r="F3" s="256" t="s">
         <v>190</v>
       </c>
       <c r="G3" s="253"/>
-      <c r="H3" s="258" t="s">
+      <c r="H3" s="256" t="s">
         <v>191</v>
       </c>
       <c r="I3" s="253"/>
-      <c r="J3" s="258" t="s">
+      <c r="J3" s="256" t="s">
         <v>192</v>
       </c>
       <c r="K3" s="253"/>
-      <c r="L3" s="258" t="s">
+      <c r="L3" s="256" t="s">
         <v>193</v>
       </c>
       <c r="M3" s="253"/>
-      <c r="N3" s="259" t="s">
+      <c r="N3" s="260" t="s">
         <v>194</v>
       </c>
       <c r="O3" s="253"/>
-      <c r="P3" s="259" t="s">
+      <c r="P3" s="260" t="s">
         <v>195</v>
       </c>
       <c r="Q3" s="253"/>
-      <c r="R3" s="259" t="s">
+      <c r="R3" s="260" t="s">
         <v>196</v>
       </c>
       <c r="S3" s="253"/>
-      <c r="T3" s="259" t="s">
+      <c r="T3" s="260" t="s">
         <v>197</v>
       </c>
       <c r="U3" s="253"/>
-      <c r="V3" s="259" t="s">
+      <c r="V3" s="260" t="s">
         <v>198</v>
       </c>
       <c r="W3" s="253"/>
-      <c r="X3" s="259" t="s">
+      <c r="X3" s="260" t="s">
         <v>199</v>
       </c>
       <c r="Y3" s="253"/>
-      <c r="Z3" s="266" t="s">
+      <c r="Z3" s="261" t="s">
         <v>200</v>
       </c>
       <c r="AA3" s="253"/>
-      <c r="AB3" s="266" t="s">
+      <c r="AB3" s="261" t="s">
         <v>201</v>
       </c>
       <c r="AC3" s="253"/>
-      <c r="AD3" s="266" t="s">
+      <c r="AD3" s="261" t="s">
         <v>202</v>
       </c>
       <c r="AE3" s="253"/>
-      <c r="AF3" s="266" t="s">
+      <c r="AF3" s="261" t="s">
         <v>203</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="266" t="s">
+      <c r="AH3" s="261" t="s">
         <v>204</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="266" t="s">
+      <c r="AJ3" s="261" t="s">
         <v>205</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="268" t="s">
+      <c r="AL3" s="257" t="s">
         <v>206</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="268" t="s">
+      <c r="AN3" s="257" t="s">
         <v>207</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="268" t="s">
+      <c r="AP3" s="257" t="s">
         <v>208</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="268" t="s">
+      <c r="AR3" s="257" t="s">
         <v>209</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="268" t="s">
+      <c r="AT3" s="257" t="s">
         <v>210</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="268" t="s">
+      <c r="AV3" s="257" t="s">
         <v>211</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="260" t="s">
+      <c r="AX3" s="258" t="s">
         <v>212</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="260" t="s">
+      <c r="AZ3" s="258" t="s">
         <v>213</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="260" t="s">
+      <c r="BB3" s="258" t="s">
         <v>214</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="260" t="s">
+      <c r="BD3" s="258" t="s">
         <v>215</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="260" t="s">
+      <c r="BF3" s="258" t="s">
         <v>216</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="260" t="s">
+      <c r="BH3" s="258" t="s">
         <v>217</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="261" t="s">
+      <c r="BJ3" s="262" t="s">
         <v>218</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="261" t="s">
+      <c r="BL3" s="262" t="s">
         <v>219</v>
       </c>
       <c r="BM3" s="253"/>
-      <c r="BN3" s="261" t="s">
+      <c r="BN3" s="262" t="s">
         <v>220</v>
       </c>
       <c r="BO3" s="253"/>
-      <c r="BP3" s="261" t="s">
+      <c r="BP3" s="262" t="s">
         <v>221</v>
       </c>
       <c r="BQ3" s="253"/>
-      <c r="BR3" s="261" t="s">
+      <c r="BR3" s="262" t="s">
         <v>222</v>
       </c>
       <c r="BS3" s="253"/>
-      <c r="BT3" s="261" t="s">
+      <c r="BT3" s="262" t="s">
         <v>223</v>
       </c>
       <c r="BU3" s="253"/>
@@ -11297,27 +11281,27 @@
         <v>229</v>
       </c>
       <c r="CG3" s="253"/>
-      <c r="CH3" s="264" t="s">
+      <c r="CH3" s="259" t="s">
         <v>230</v>
       </c>
       <c r="CI3" s="253"/>
-      <c r="CJ3" s="264" t="s">
+      <c r="CJ3" s="259" t="s">
         <v>231</v>
       </c>
       <c r="CK3" s="253"/>
-      <c r="CL3" s="264" t="s">
+      <c r="CL3" s="259" t="s">
         <v>232</v>
       </c>
       <c r="CM3" s="253"/>
-      <c r="CN3" s="264" t="s">
+      <c r="CN3" s="259" t="s">
         <v>233</v>
       </c>
       <c r="CO3" s="253"/>
-      <c r="CP3" s="264" t="s">
+      <c r="CP3" s="259" t="s">
         <v>234</v>
       </c>
       <c r="CQ3" s="253"/>
-      <c r="CR3" s="264" t="s">
+      <c r="CR3" s="259" t="s">
         <v>235</v>
       </c>
       <c r="CS3" s="253"/>
@@ -11345,75 +11329,75 @@
         <v>241</v>
       </c>
       <c r="DE3" s="253"/>
-      <c r="DF3" s="262" t="s">
+      <c r="DF3" s="267" t="s">
         <v>242</v>
       </c>
       <c r="DG3" s="253"/>
-      <c r="DH3" s="262" t="s">
+      <c r="DH3" s="267" t="s">
         <v>243</v>
       </c>
       <c r="DI3" s="253"/>
-      <c r="DJ3" s="262" t="s">
+      <c r="DJ3" s="267" t="s">
         <v>244</v>
       </c>
       <c r="DK3" s="253"/>
-      <c r="DL3" s="262" t="s">
+      <c r="DL3" s="267" t="s">
         <v>245</v>
       </c>
       <c r="DM3" s="253"/>
-      <c r="DN3" s="262" t="s">
+      <c r="DN3" s="267" t="s">
         <v>246</v>
       </c>
       <c r="DO3" s="253"/>
-      <c r="DP3" s="262" t="s">
+      <c r="DP3" s="267" t="s">
         <v>247</v>
       </c>
       <c r="DQ3" s="253"/>
-      <c r="DR3" s="267" t="s">
+      <c r="DR3" s="266" t="s">
         <v>248</v>
       </c>
       <c r="DS3" s="253"/>
-      <c r="DT3" s="267" t="s">
+      <c r="DT3" s="266" t="s">
         <v>249</v>
       </c>
       <c r="DU3" s="253"/>
-      <c r="DV3" s="267" t="s">
+      <c r="DV3" s="266" t="s">
         <v>250</v>
       </c>
       <c r="DW3" s="253"/>
-      <c r="DX3" s="267" t="s">
+      <c r="DX3" s="266" t="s">
         <v>251</v>
       </c>
       <c r="DY3" s="253"/>
-      <c r="DZ3" s="267" t="s">
+      <c r="DZ3" s="266" t="s">
         <v>252</v>
       </c>
       <c r="EA3" s="253"/>
-      <c r="EB3" s="267" t="s">
+      <c r="EB3" s="266" t="s">
         <v>253</v>
       </c>
       <c r="EC3" s="253"/>
-      <c r="ED3" s="257" t="s">
+      <c r="ED3" s="264" t="s">
         <v>254</v>
       </c>
       <c r="EE3" s="253"/>
-      <c r="EF3" s="257" t="s">
+      <c r="EF3" s="264" t="s">
         <v>255</v>
       </c>
       <c r="EG3" s="253"/>
-      <c r="EH3" s="257" t="s">
+      <c r="EH3" s="264" t="s">
         <v>256</v>
       </c>
       <c r="EI3" s="253"/>
-      <c r="EJ3" s="257" t="s">
+      <c r="EJ3" s="264" t="s">
         <v>257</v>
       </c>
       <c r="EK3" s="253"/>
-      <c r="EL3" s="257" t="s">
+      <c r="EL3" s="264" t="s">
         <v>258</v>
       </c>
       <c r="EM3" s="253"/>
-      <c r="EN3" s="257" t="s">
+      <c r="EN3" s="264" t="s">
         <v>259</v>
       </c>
       <c r="EO3" s="253"/>
@@ -12453,6 +12437,64 @@
     </row>
   </sheetData>
   <mergeCells count="74">
+    <mergeCell ref="BX3:BY3"/>
+    <mergeCell ref="CN3:CO3"/>
+    <mergeCell ref="CZ3:DA3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="A2:EO2"/>
+    <mergeCell ref="EJ3:EK3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="BJ3:BK3"/>
+    <mergeCell ref="AZ3:BA3"/>
+    <mergeCell ref="BL3:BM3"/>
+    <mergeCell ref="DL3:DM3"/>
+    <mergeCell ref="BV3:BW3"/>
+    <mergeCell ref="A1:EO1"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="BF3:BG3"/>
+    <mergeCell ref="BH3:BI3"/>
+    <mergeCell ref="BN3:BO3"/>
+    <mergeCell ref="BP3:BQ3"/>
+    <mergeCell ref="BR3:BS3"/>
+    <mergeCell ref="DP3:DQ3"/>
+    <mergeCell ref="BZ3:CA3"/>
+    <mergeCell ref="CP3:CQ3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="CR3:CS3"/>
+    <mergeCell ref="CB3:CC3"/>
+    <mergeCell ref="DJ3:DK3"/>
+    <mergeCell ref="EL3:EM3"/>
+    <mergeCell ref="CV3:CW3"/>
+    <mergeCell ref="CH3:CI3"/>
+    <mergeCell ref="CD3:CE3"/>
+    <mergeCell ref="DR3:DS3"/>
+    <mergeCell ref="DX3:DY3"/>
+    <mergeCell ref="DD3:DE3"/>
+    <mergeCell ref="DF3:DG3"/>
+    <mergeCell ref="DB3:DC3"/>
+    <mergeCell ref="CT3:CU3"/>
+    <mergeCell ref="DN3:DO3"/>
+    <mergeCell ref="EN3:EO3"/>
+    <mergeCell ref="CX3:CY3"/>
+    <mergeCell ref="DV3:DW3"/>
+    <mergeCell ref="EB3:EC3"/>
+    <mergeCell ref="ED3:EE3"/>
+    <mergeCell ref="EH3:EI3"/>
+    <mergeCell ref="DZ3:EA3"/>
+    <mergeCell ref="EF3:EG3"/>
+    <mergeCell ref="DH3:DI3"/>
+    <mergeCell ref="DT3:DU3"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="AP3:AQ3"/>
     <mergeCell ref="BB3:BC3"/>
@@ -12469,64 +12511,6 @@
     <mergeCell ref="R3:S3"/>
     <mergeCell ref="AR3:AS3"/>
     <mergeCell ref="T3:U3"/>
-    <mergeCell ref="EN3:EO3"/>
-    <mergeCell ref="CX3:CY3"/>
-    <mergeCell ref="DV3:DW3"/>
-    <mergeCell ref="EB3:EC3"/>
-    <mergeCell ref="ED3:EE3"/>
-    <mergeCell ref="EH3:EI3"/>
-    <mergeCell ref="DZ3:EA3"/>
-    <mergeCell ref="EF3:EG3"/>
-    <mergeCell ref="DH3:DI3"/>
-    <mergeCell ref="DT3:DU3"/>
-    <mergeCell ref="CB3:CC3"/>
-    <mergeCell ref="DJ3:DK3"/>
-    <mergeCell ref="EL3:EM3"/>
-    <mergeCell ref="CV3:CW3"/>
-    <mergeCell ref="CH3:CI3"/>
-    <mergeCell ref="CD3:CE3"/>
-    <mergeCell ref="DR3:DS3"/>
-    <mergeCell ref="DX3:DY3"/>
-    <mergeCell ref="DD3:DE3"/>
-    <mergeCell ref="DF3:DG3"/>
-    <mergeCell ref="A1:EO1"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="BF3:BG3"/>
-    <mergeCell ref="BH3:BI3"/>
-    <mergeCell ref="BN3:BO3"/>
-    <mergeCell ref="BP3:BQ3"/>
-    <mergeCell ref="BR3:BS3"/>
-    <mergeCell ref="DP3:DQ3"/>
-    <mergeCell ref="BZ3:CA3"/>
-    <mergeCell ref="CP3:CQ3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="CR3:CS3"/>
-    <mergeCell ref="DB3:DC3"/>
-    <mergeCell ref="CT3:CU3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="A2:EO2"/>
-    <mergeCell ref="EJ3:EK3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="BJ3:BK3"/>
-    <mergeCell ref="AZ3:BA3"/>
-    <mergeCell ref="BL3:BM3"/>
-    <mergeCell ref="DL3:DM3"/>
-    <mergeCell ref="BV3:BW3"/>
-    <mergeCell ref="DN3:DO3"/>
-    <mergeCell ref="BX3:BY3"/>
-    <mergeCell ref="CN3:CO3"/>
-    <mergeCell ref="CZ3:DA3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12545,14 +12529,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="255" t="s">
+      <c r="A1" s="252" t="s">
         <v>265</v>
       </c>
       <c r="B1" s="253"/>
       <c r="C1" s="253"/>
     </row>
     <row r="2" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="256" t="s">
+      <c r="A2" s="268" t="s">
         <v>266</v>
       </c>
       <c r="B2" s="253"/>
@@ -12627,7 +12611,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:74" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="255" t="s">
+      <c r="A1" s="252" t="s">
         <v>270</v>
       </c>
       <c r="B1" s="253"/>
@@ -12705,7 +12689,7 @@
       <c r="BV1" s="253"/>
     </row>
     <row r="2" spans="1:74" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="256" t="s">
+      <c r="A2" s="268" t="s">
         <v>271</v>
       </c>
       <c r="B2" s="253"/>
@@ -13232,13 +13216,13 @@
       <c r="A5" s="81" t="s">
         <v>261</v>
       </c>
-      <c r="B5" s="106">
+      <c r="B5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F3="",'Jogos - Grupos'!G3=""),"-",IF(OR('Apostas - Grupos'!B5="",'Apostas - Grupos'!C5=""),0,IF(AND('Apostas - Grupos'!B5='Jogos - Grupos'!F3,'Apostas - Grupos'!C5='Jogos - Grupos'!G3),5,IF(OR(AND('Jogos - Grupos'!F3='Jogos - Grupos'!G3,'Apostas - Grupos'!B5='Apostas - Grupos'!C5),AND('Jogos - Grupos'!F3&gt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B5&gt;'Apostas - Grupos'!C5),AND('Jogos - Grupos'!F3&lt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B5&lt;'Apostas - Grupos'!C5)),IF(('Apostas - Grupos'!B5-'Apostas - Grupos'!C5)=('Jogos - Grupos'!F3-'Jogos - Grupos'!G3),3,2),0))))</f>
-        <v>0</v>
-      </c>
-      <c r="C5" s="106">
+        <v>-</v>
+      </c>
+      <c r="C5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F4="",'Jogos - Grupos'!G4=""),"-",IF(OR('Apostas - Grupos'!D5="",'Apostas - Grupos'!E5=""),0,IF(AND('Apostas - Grupos'!D5='Jogos - Grupos'!F4,'Apostas - Grupos'!E5='Jogos - Grupos'!G4),5,IF(OR(AND('Jogos - Grupos'!F4='Jogos - Grupos'!G4,'Apostas - Grupos'!D5='Apostas - Grupos'!E5),AND('Jogos - Grupos'!F4&gt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D5&gt;'Apostas - Grupos'!E5),AND('Jogos - Grupos'!F4&lt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D5&lt;'Apostas - Grupos'!E5)),IF(('Apostas - Grupos'!D5-'Apostas - Grupos'!E5)=('Jogos - Grupos'!F4-'Jogos - Grupos'!G4),3,2),0))))</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="D5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F5="",'Jogos - Grupos'!G5=""),"-",IF(OR('Apostas - Grupos'!F5="",'Apostas - Grupos'!G5=""),0,IF(AND('Apostas - Grupos'!F5='Jogos - Grupos'!F5,'Apostas - Grupos'!G5='Jogos - Grupos'!G5),5,IF(OR(AND('Jogos - Grupos'!F5='Jogos - Grupos'!G5,'Apostas - Grupos'!F5='Apostas - Grupos'!G5),AND('Jogos - Grupos'!F5&gt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F5&gt;'Apostas - Grupos'!G5),AND('Jogos - Grupos'!F5&lt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F5&lt;'Apostas - Grupos'!G5)),IF(('Apostas - Grupos'!F5-'Apostas - Grupos'!G5)=('Jogos - Grupos'!F5-'Jogos - Grupos'!G5),3,2),0))))</f>
@@ -13280,13 +13264,13 @@
         <f>IF(OR('Jogos - Grupos'!F14="",'Jogos - Grupos'!G14=""),"-",IF(OR('Apostas - Grupos'!X5="",'Apostas - Grupos'!Y5=""),0,IF(AND('Apostas - Grupos'!X5='Jogos - Grupos'!F14,'Apostas - Grupos'!Y5='Jogos - Grupos'!G14),5,IF(OR(AND('Jogos - Grupos'!F14='Jogos - Grupos'!G14,'Apostas - Grupos'!X5='Apostas - Grupos'!Y5),AND('Jogos - Grupos'!F14&gt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X5&gt;'Apostas - Grupos'!Y5),AND('Jogos - Grupos'!F14&lt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X5&lt;'Apostas - Grupos'!Y5)),IF(('Apostas - Grupos'!X5-'Apostas - Grupos'!Y5)=('Jogos - Grupos'!F14-'Jogos - Grupos'!G14),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="N5" s="106">
+      <c r="N5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F15="",'Jogos - Grupos'!G15=""),"-",IF(OR('Apostas - Grupos'!Z5="",'Apostas - Grupos'!AA5=""),0,IF(AND('Apostas - Grupos'!Z5='Jogos - Grupos'!F15,'Apostas - Grupos'!AA5='Jogos - Grupos'!G15),5,IF(OR(AND('Jogos - Grupos'!F15='Jogos - Grupos'!G15,'Apostas - Grupos'!Z5='Apostas - Grupos'!AA5),AND('Jogos - Grupos'!F15&gt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z5&gt;'Apostas - Grupos'!AA5),AND('Jogos - Grupos'!F15&lt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z5&lt;'Apostas - Grupos'!AA5)),IF(('Apostas - Grupos'!Z5-'Apostas - Grupos'!AA5)=('Jogos - Grupos'!F15-'Jogos - Grupos'!G15),3,2),0))))</f>
-        <v>0</v>
-      </c>
-      <c r="O5" s="106">
+        <v>-</v>
+      </c>
+      <c r="O5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F16="",'Jogos - Grupos'!G16=""),"-",IF(OR('Apostas - Grupos'!AB5="",'Apostas - Grupos'!AC5=""),0,IF(AND('Apostas - Grupos'!AB5='Jogos - Grupos'!F16,'Apostas - Grupos'!AC5='Jogos - Grupos'!G16),5,IF(OR(AND('Jogos - Grupos'!F16='Jogos - Grupos'!G16,'Apostas - Grupos'!AB5='Apostas - Grupos'!AC5),AND('Jogos - Grupos'!F16&gt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB5&gt;'Apostas - Grupos'!AC5),AND('Jogos - Grupos'!F16&lt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB5&lt;'Apostas - Grupos'!AC5)),IF(('Apostas - Grupos'!AB5-'Apostas - Grupos'!AC5)=('Jogos - Grupos'!F16-'Jogos - Grupos'!G16),3,2),0))))</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="P5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F17="",'Jogos - Grupos'!G17=""),"-",IF(OR('Apostas - Grupos'!AD5="",'Apostas - Grupos'!AE5=""),0,IF(AND('Apostas - Grupos'!AD5='Jogos - Grupos'!F17,'Apostas - Grupos'!AE5='Jogos - Grupos'!G17),5,IF(OR(AND('Jogos - Grupos'!F17='Jogos - Grupos'!G17,'Apostas - Grupos'!AD5='Apostas - Grupos'!AE5),AND('Jogos - Grupos'!F17&gt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD5&gt;'Apostas - Grupos'!AE5),AND('Jogos - Grupos'!F17&lt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD5&lt;'Apostas - Grupos'!AE5)),IF(('Apostas - Grupos'!AD5-'Apostas - Grupos'!AE5)=('Jogos - Grupos'!F17-'Jogos - Grupos'!G17),3,2),0))))</f>
@@ -13529,13 +13513,13 @@
       <c r="A6" s="82" t="s">
         <v>262</v>
       </c>
-      <c r="B6" s="108">
+      <c r="B6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F3="",'Jogos - Grupos'!G3=""),"-",IF(OR('Apostas - Grupos'!B6="",'Apostas - Grupos'!C6=""),0,IF(AND('Apostas - Grupos'!B6='Jogos - Grupos'!F3,'Apostas - Grupos'!C6='Jogos - Grupos'!G3),5,IF(OR(AND('Jogos - Grupos'!F3='Jogos - Grupos'!G3,'Apostas - Grupos'!B6='Apostas - Grupos'!C6),AND('Jogos - Grupos'!F3&gt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B6&gt;'Apostas - Grupos'!C6),AND('Jogos - Grupos'!F3&lt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B6&lt;'Apostas - Grupos'!C6)),IF(('Apostas - Grupos'!B6-'Apostas - Grupos'!C6)=('Jogos - Grupos'!F3-'Jogos - Grupos'!G3),3,2),0))))</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="108">
+        <v>-</v>
+      </c>
+      <c r="C6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F4="",'Jogos - Grupos'!G4=""),"-",IF(OR('Apostas - Grupos'!D6="",'Apostas - Grupos'!E6=""),0,IF(AND('Apostas - Grupos'!D6='Jogos - Grupos'!F4,'Apostas - Grupos'!E6='Jogos - Grupos'!G4),5,IF(OR(AND('Jogos - Grupos'!F4='Jogos - Grupos'!G4,'Apostas - Grupos'!D6='Apostas - Grupos'!E6),AND('Jogos - Grupos'!F4&gt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D6&gt;'Apostas - Grupos'!E6),AND('Jogos - Grupos'!F4&lt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D6&lt;'Apostas - Grupos'!E6)),IF(('Apostas - Grupos'!D6-'Apostas - Grupos'!E6)=('Jogos - Grupos'!F4-'Jogos - Grupos'!G4),3,2),0))))</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="D6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F5="",'Jogos - Grupos'!G5=""),"-",IF(OR('Apostas - Grupos'!F6="",'Apostas - Grupos'!G6=""),0,IF(AND('Apostas - Grupos'!F6='Jogos - Grupos'!F5,'Apostas - Grupos'!G6='Jogos - Grupos'!G5),5,IF(OR(AND('Jogos - Grupos'!F5='Jogos - Grupos'!G5,'Apostas - Grupos'!F6='Apostas - Grupos'!G6),AND('Jogos - Grupos'!F5&gt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F6&gt;'Apostas - Grupos'!G6),AND('Jogos - Grupos'!F5&lt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F6&lt;'Apostas - Grupos'!G6)),IF(('Apostas - Grupos'!F6-'Apostas - Grupos'!G6)=('Jogos - Grupos'!F5-'Jogos - Grupos'!G5),3,2),0))))</f>
@@ -13577,13 +13561,13 @@
         <f>IF(OR('Jogos - Grupos'!F14="",'Jogos - Grupos'!G14=""),"-",IF(OR('Apostas - Grupos'!X6="",'Apostas - Grupos'!Y6=""),0,IF(AND('Apostas - Grupos'!X6='Jogos - Grupos'!F14,'Apostas - Grupos'!Y6='Jogos - Grupos'!G14),5,IF(OR(AND('Jogos - Grupos'!F14='Jogos - Grupos'!G14,'Apostas - Grupos'!X6='Apostas - Grupos'!Y6),AND('Jogos - Grupos'!F14&gt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X6&gt;'Apostas - Grupos'!Y6),AND('Jogos - Grupos'!F14&lt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X6&lt;'Apostas - Grupos'!Y6)),IF(('Apostas - Grupos'!X6-'Apostas - Grupos'!Y6)=('Jogos - Grupos'!F14-'Jogos - Grupos'!G14),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="N6" s="108">
+      <c r="N6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F15="",'Jogos - Grupos'!G15=""),"-",IF(OR('Apostas - Grupos'!Z6="",'Apostas - Grupos'!AA6=""),0,IF(AND('Apostas - Grupos'!Z6='Jogos - Grupos'!F15,'Apostas - Grupos'!AA6='Jogos - Grupos'!G15),5,IF(OR(AND('Jogos - Grupos'!F15='Jogos - Grupos'!G15,'Apostas - Grupos'!Z6='Apostas - Grupos'!AA6),AND('Jogos - Grupos'!F15&gt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z6&gt;'Apostas - Grupos'!AA6),AND('Jogos - Grupos'!F15&lt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z6&lt;'Apostas - Grupos'!AA6)),IF(('Apostas - Grupos'!Z6-'Apostas - Grupos'!AA6)=('Jogos - Grupos'!F15-'Jogos - Grupos'!G15),3,2),0))))</f>
-        <v>0</v>
-      </c>
-      <c r="O6" s="108">
+        <v>-</v>
+      </c>
+      <c r="O6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F16="",'Jogos - Grupos'!G16=""),"-",IF(OR('Apostas - Grupos'!AB6="",'Apostas - Grupos'!AC6=""),0,IF(AND('Apostas - Grupos'!AB6='Jogos - Grupos'!F16,'Apostas - Grupos'!AC6='Jogos - Grupos'!G16),5,IF(OR(AND('Jogos - Grupos'!F16='Jogos - Grupos'!G16,'Apostas - Grupos'!AB6='Apostas - Grupos'!AC6),AND('Jogos - Grupos'!F16&gt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB6&gt;'Apostas - Grupos'!AC6),AND('Jogos - Grupos'!F16&lt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB6&lt;'Apostas - Grupos'!AC6)),IF(('Apostas - Grupos'!AB6-'Apostas - Grupos'!AC6)=('Jogos - Grupos'!F16-'Jogos - Grupos'!G16),3,2),0))))</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="P6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F17="",'Jogos - Grupos'!G17=""),"-",IF(OR('Apostas - Grupos'!AD6="",'Apostas - Grupos'!AE6=""),0,IF(AND('Apostas - Grupos'!AD6='Jogos - Grupos'!F17,'Apostas - Grupos'!AE6='Jogos - Grupos'!G17),5,IF(OR(AND('Jogos - Grupos'!F17='Jogos - Grupos'!G17,'Apostas - Grupos'!AD6='Apostas - Grupos'!AE6),AND('Jogos - Grupos'!F17&gt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD6&gt;'Apostas - Grupos'!AE6),AND('Jogos - Grupos'!F17&lt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD6&lt;'Apostas - Grupos'!AE6)),IF(('Apostas - Grupos'!AD6-'Apostas - Grupos'!AE6)=('Jogos - Grupos'!F17-'Jogos - Grupos'!G17),3,2),0))))</f>
@@ -13826,13 +13810,13 @@
       <c r="A7" s="81" t="s">
         <v>263</v>
       </c>
-      <c r="B7" s="106">
+      <c r="B7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F3="",'Jogos - Grupos'!G3=""),"-",IF(OR('Apostas - Grupos'!B7="",'Apostas - Grupos'!C7=""),0,IF(AND('Apostas - Grupos'!B7='Jogos - Grupos'!F3,'Apostas - Grupos'!C7='Jogos - Grupos'!G3),5,IF(OR(AND('Jogos - Grupos'!F3='Jogos - Grupos'!G3,'Apostas - Grupos'!B7='Apostas - Grupos'!C7),AND('Jogos - Grupos'!F3&gt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B7&gt;'Apostas - Grupos'!C7),AND('Jogos - Grupos'!F3&lt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B7&lt;'Apostas - Grupos'!C7)),IF(('Apostas - Grupos'!B7-'Apostas - Grupos'!C7)=('Jogos - Grupos'!F3-'Jogos - Grupos'!G3),3,2),0))))</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="106">
+        <v>-</v>
+      </c>
+      <c r="C7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F4="",'Jogos - Grupos'!G4=""),"-",IF(OR('Apostas - Grupos'!D7="",'Apostas - Grupos'!E7=""),0,IF(AND('Apostas - Grupos'!D7='Jogos - Grupos'!F4,'Apostas - Grupos'!E7='Jogos - Grupos'!G4),5,IF(OR(AND('Jogos - Grupos'!F4='Jogos - Grupos'!G4,'Apostas - Grupos'!D7='Apostas - Grupos'!E7),AND('Jogos - Grupos'!F4&gt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D7&gt;'Apostas - Grupos'!E7),AND('Jogos - Grupos'!F4&lt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D7&lt;'Apostas - Grupos'!E7)),IF(('Apostas - Grupos'!D7-'Apostas - Grupos'!E7)=('Jogos - Grupos'!F4-'Jogos - Grupos'!G4),3,2),0))))</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="D7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F5="",'Jogos - Grupos'!G5=""),"-",IF(OR('Apostas - Grupos'!F7="",'Apostas - Grupos'!G7=""),0,IF(AND('Apostas - Grupos'!F7='Jogos - Grupos'!F5,'Apostas - Grupos'!G7='Jogos - Grupos'!G5),5,IF(OR(AND('Jogos - Grupos'!F5='Jogos - Grupos'!G5,'Apostas - Grupos'!F7='Apostas - Grupos'!G7),AND('Jogos - Grupos'!F5&gt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F7&gt;'Apostas - Grupos'!G7),AND('Jogos - Grupos'!F5&lt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F7&lt;'Apostas - Grupos'!G7)),IF(('Apostas - Grupos'!F7-'Apostas - Grupos'!G7)=('Jogos - Grupos'!F5-'Jogos - Grupos'!G5),3,2),0))))</f>
@@ -13874,13 +13858,13 @@
         <f>IF(OR('Jogos - Grupos'!F14="",'Jogos - Grupos'!G14=""),"-",IF(OR('Apostas - Grupos'!X7="",'Apostas - Grupos'!Y7=""),0,IF(AND('Apostas - Grupos'!X7='Jogos - Grupos'!F14,'Apostas - Grupos'!Y7='Jogos - Grupos'!G14),5,IF(OR(AND('Jogos - Grupos'!F14='Jogos - Grupos'!G14,'Apostas - Grupos'!X7='Apostas - Grupos'!Y7),AND('Jogos - Grupos'!F14&gt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X7&gt;'Apostas - Grupos'!Y7),AND('Jogos - Grupos'!F14&lt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X7&lt;'Apostas - Grupos'!Y7)),IF(('Apostas - Grupos'!X7-'Apostas - Grupos'!Y7)=('Jogos - Grupos'!F14-'Jogos - Grupos'!G14),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="N7" s="106">
+      <c r="N7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F15="",'Jogos - Grupos'!G15=""),"-",IF(OR('Apostas - Grupos'!Z7="",'Apostas - Grupos'!AA7=""),0,IF(AND('Apostas - Grupos'!Z7='Jogos - Grupos'!F15,'Apostas - Grupos'!AA7='Jogos - Grupos'!G15),5,IF(OR(AND('Jogos - Grupos'!F15='Jogos - Grupos'!G15,'Apostas - Grupos'!Z7='Apostas - Grupos'!AA7),AND('Jogos - Grupos'!F15&gt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z7&gt;'Apostas - Grupos'!AA7),AND('Jogos - Grupos'!F15&lt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z7&lt;'Apostas - Grupos'!AA7)),IF(('Apostas - Grupos'!Z7-'Apostas - Grupos'!AA7)=('Jogos - Grupos'!F15-'Jogos - Grupos'!G15),3,2),0))))</f>
-        <v>0</v>
-      </c>
-      <c r="O7" s="106">
+        <v>-</v>
+      </c>
+      <c r="O7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F16="",'Jogos - Grupos'!G16=""),"-",IF(OR('Apostas - Grupos'!AB7="",'Apostas - Grupos'!AC7=""),0,IF(AND('Apostas - Grupos'!AB7='Jogos - Grupos'!F16,'Apostas - Grupos'!AC7='Jogos - Grupos'!G16),5,IF(OR(AND('Jogos - Grupos'!F16='Jogos - Grupos'!G16,'Apostas - Grupos'!AB7='Apostas - Grupos'!AC7),AND('Jogos - Grupos'!F16&gt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB7&gt;'Apostas - Grupos'!AC7),AND('Jogos - Grupos'!F16&lt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB7&lt;'Apostas - Grupos'!AC7)),IF(('Apostas - Grupos'!AB7-'Apostas - Grupos'!AC7)=('Jogos - Grupos'!F16-'Jogos - Grupos'!G16),3,2),0))))</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="P7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F17="",'Jogos - Grupos'!G17=""),"-",IF(OR('Apostas - Grupos'!AD7="",'Apostas - Grupos'!AE7=""),0,IF(AND('Apostas - Grupos'!AD7='Jogos - Grupos'!F17,'Apostas - Grupos'!AE7='Jogos - Grupos'!G17),5,IF(OR(AND('Jogos - Grupos'!F17='Jogos - Grupos'!G17,'Apostas - Grupos'!AD7='Apostas - Grupos'!AE7),AND('Jogos - Grupos'!F17&gt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD7&gt;'Apostas - Grupos'!AE7),AND('Jogos - Grupos'!F17&lt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD7&lt;'Apostas - Grupos'!AE7)),IF(('Apostas - Grupos'!AD7-'Apostas - Grupos'!AE7)=('Jogos - Grupos'!F17-'Jogos - Grupos'!G17),3,2),0))))</f>
@@ -14123,13 +14107,13 @@
       <c r="A8" s="82" t="s">
         <v>264</v>
       </c>
-      <c r="B8" s="108">
+      <c r="B8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F3="",'Jogos - Grupos'!G3=""),"-",IF(OR('Apostas - Grupos'!B8="",'Apostas - Grupos'!C8=""),0,IF(AND('Apostas - Grupos'!B8='Jogos - Grupos'!F3,'Apostas - Grupos'!C8='Jogos - Grupos'!G3),5,IF(OR(AND('Jogos - Grupos'!F3='Jogos - Grupos'!G3,'Apostas - Grupos'!B8='Apostas - Grupos'!C8),AND('Jogos - Grupos'!F3&gt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B8&gt;'Apostas - Grupos'!C8),AND('Jogos - Grupos'!F3&lt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B8&lt;'Apostas - Grupos'!C8)),IF(('Apostas - Grupos'!B8-'Apostas - Grupos'!C8)=('Jogos - Grupos'!F3-'Jogos - Grupos'!G3),3,2),0))))</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="108">
+        <v>-</v>
+      </c>
+      <c r="C8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F4="",'Jogos - Grupos'!G4=""),"-",IF(OR('Apostas - Grupos'!D8="",'Apostas - Grupos'!E8=""),0,IF(AND('Apostas - Grupos'!D8='Jogos - Grupos'!F4,'Apostas - Grupos'!E8='Jogos - Grupos'!G4),5,IF(OR(AND('Jogos - Grupos'!F4='Jogos - Grupos'!G4,'Apostas - Grupos'!D8='Apostas - Grupos'!E8),AND('Jogos - Grupos'!F4&gt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D8&gt;'Apostas - Grupos'!E8),AND('Jogos - Grupos'!F4&lt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D8&lt;'Apostas - Grupos'!E8)),IF(('Apostas - Grupos'!D8-'Apostas - Grupos'!E8)=('Jogos - Grupos'!F4-'Jogos - Grupos'!G4),3,2),0))))</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="D8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F5="",'Jogos - Grupos'!G5=""),"-",IF(OR('Apostas - Grupos'!F8="",'Apostas - Grupos'!G8=""),0,IF(AND('Apostas - Grupos'!F8='Jogos - Grupos'!F5,'Apostas - Grupos'!G8='Jogos - Grupos'!G5),5,IF(OR(AND('Jogos - Grupos'!F5='Jogos - Grupos'!G5,'Apostas - Grupos'!F8='Apostas - Grupos'!G8),AND('Jogos - Grupos'!F5&gt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F8&gt;'Apostas - Grupos'!G8),AND('Jogos - Grupos'!F5&lt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F8&lt;'Apostas - Grupos'!G8)),IF(('Apostas - Grupos'!F8-'Apostas - Grupos'!G8)=('Jogos - Grupos'!F5-'Jogos - Grupos'!G5),3,2),0))))</f>
@@ -14171,13 +14155,13 @@
         <f>IF(OR('Jogos - Grupos'!F14="",'Jogos - Grupos'!G14=""),"-",IF(OR('Apostas - Grupos'!X8="",'Apostas - Grupos'!Y8=""),0,IF(AND('Apostas - Grupos'!X8='Jogos - Grupos'!F14,'Apostas - Grupos'!Y8='Jogos - Grupos'!G14),5,IF(OR(AND('Jogos - Grupos'!F14='Jogos - Grupos'!G14,'Apostas - Grupos'!X8='Apostas - Grupos'!Y8),AND('Jogos - Grupos'!F14&gt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X8&gt;'Apostas - Grupos'!Y8),AND('Jogos - Grupos'!F14&lt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X8&lt;'Apostas - Grupos'!Y8)),IF(('Apostas - Grupos'!X8-'Apostas - Grupos'!Y8)=('Jogos - Grupos'!F14-'Jogos - Grupos'!G14),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="N8" s="108">
+      <c r="N8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F15="",'Jogos - Grupos'!G15=""),"-",IF(OR('Apostas - Grupos'!Z8="",'Apostas - Grupos'!AA8=""),0,IF(AND('Apostas - Grupos'!Z8='Jogos - Grupos'!F15,'Apostas - Grupos'!AA8='Jogos - Grupos'!G15),5,IF(OR(AND('Jogos - Grupos'!F15='Jogos - Grupos'!G15,'Apostas - Grupos'!Z8='Apostas - Grupos'!AA8),AND('Jogos - Grupos'!F15&gt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z8&gt;'Apostas - Grupos'!AA8),AND('Jogos - Grupos'!F15&lt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z8&lt;'Apostas - Grupos'!AA8)),IF(('Apostas - Grupos'!Z8-'Apostas - Grupos'!AA8)=('Jogos - Grupos'!F15-'Jogos - Grupos'!G15),3,2),0))))</f>
-        <v>0</v>
-      </c>
-      <c r="O8" s="108">
+        <v>-</v>
+      </c>
+      <c r="O8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F16="",'Jogos - Grupos'!G16=""),"-",IF(OR('Apostas - Grupos'!AB8="",'Apostas - Grupos'!AC8=""),0,IF(AND('Apostas - Grupos'!AB8='Jogos - Grupos'!F16,'Apostas - Grupos'!AC8='Jogos - Grupos'!G16),5,IF(OR(AND('Jogos - Grupos'!F16='Jogos - Grupos'!G16,'Apostas - Grupos'!AB8='Apostas - Grupos'!AC8),AND('Jogos - Grupos'!F16&gt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB8&gt;'Apostas - Grupos'!AC8),AND('Jogos - Grupos'!F16&lt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB8&lt;'Apostas - Grupos'!AC8)),IF(('Apostas - Grupos'!AB8-'Apostas - Grupos'!AC8)=('Jogos - Grupos'!F16-'Jogos - Grupos'!G16),3,2),0))))</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="P8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F17="",'Jogos - Grupos'!G17=""),"-",IF(OR('Apostas - Grupos'!AD8="",'Apostas - Grupos'!AE8=""),0,IF(AND('Apostas - Grupos'!AD8='Jogos - Grupos'!F17,'Apostas - Grupos'!AE8='Jogos - Grupos'!G17),5,IF(OR(AND('Jogos - Grupos'!F17='Jogos - Grupos'!G17,'Apostas - Grupos'!AD8='Apostas - Grupos'!AE8),AND('Jogos - Grupos'!F17&gt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD8&gt;'Apostas - Grupos'!AE8),AND('Jogos - Grupos'!F17&lt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD8&lt;'Apostas - Grupos'!AE8)),IF(('Apostas - Grupos'!AD8-'Apostas - Grupos'!AE8)=('Jogos - Grupos'!F17-'Jogos - Grupos'!G17),3,2),0))))</f>
@@ -14455,7 +14439,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="255" t="s">
+      <c r="A1" s="252" t="s">
         <v>418</v>
       </c>
       <c r="B1" s="253"/>
@@ -14517,7 +14501,7 @@
       </c>
       <c r="C3" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A3)*('Jogos - Grupos'!$D$3:$D$74=$B3)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74&gt;'Jogos - Grupos'!$G$3:$G$74))+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A3)*('Jogos - Grupos'!$E$3:$E$74=$B3)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$G$3:$G$74&gt;'Jogos - Grupos'!$F$3:$F$74))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A3)*(('Jogos - Grupos'!$D$3:$D$74=$B3)+('Jogos - Grupos'!$E$3:$E$74=$B3))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
@@ -14525,23 +14509,23 @@
       </c>
       <c r="E3" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A3)*('Jogos - Grupos'!$D$3:$D$74=$B3)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A3)*('Jogos - Grupos'!$E$3:$E$74=$B3)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A3)*('Jogos - Grupos'!$D$3:$D$74=$B3)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A3)*('Jogos - Grupos'!$E$3:$E$74=$B3)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="110">
         <f t="shared" ref="G3:G50" si="0">E3-F3</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="8">
         <f t="shared" ref="H3:H50" si="1">3*C3+D3</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" s="110">
         <f t="shared" ref="I3:I50" si="2">H3*1000000000+(G3+200)*1000000+E3*1000+(500-K3)</f>
-        <v>3201002484</v>
+        <v>200000484</v>
       </c>
       <c r="J3" s="8">
         <f>RANK(I3,$I$3:$I$6,0)</f>
@@ -14568,15 +14552,15 @@
       </c>
       <c r="E4" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A4)*('Jogos - Grupos'!$D$3:$D$74=$B4)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A4)*('Jogos - Grupos'!$E$3:$E$74=$B4)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A4)*('Jogos - Grupos'!$D$3:$D$74=$B4)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A4)*('Jogos - Grupos'!$E$3:$E$74=$B4)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" s="110">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" si="1"/>
@@ -14584,7 +14568,7 @@
       </c>
       <c r="I4" s="110">
         <f t="shared" si="2"/>
-        <v>199001437</v>
+        <v>200000437</v>
       </c>
       <c r="J4" s="8">
         <f>RANK(I4,$I$3:$I$6,0)</f>
@@ -14611,15 +14595,15 @@
       </c>
       <c r="E5" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A5)*('Jogos - Grupos'!$D$3:$D$74=$B5)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A5)*('Jogos - Grupos'!$E$3:$E$74=$B5)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A5)*('Jogos - Grupos'!$D$3:$D$74=$B5)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A5)*('Jogos - Grupos'!$E$3:$E$74=$B5)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="110">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="1"/>
@@ -14627,11 +14611,11 @@
       </c>
       <c r="I5" s="110">
         <f t="shared" si="2"/>
-        <v>199001477</v>
+        <v>200000477</v>
       </c>
       <c r="J5" s="8">
         <f>RANK(I5,$I$3:$I$6,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" s="110">
         <v>23</v>
@@ -14646,7 +14630,7 @@
       </c>
       <c r="C6" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$D$3:$D$74=$B6)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74&gt;'Jogos - Grupos'!$G$3:$G$74))+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$E$3:$E$74=$B6)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$G$3:$G$74&gt;'Jogos - Grupos'!$F$3:$F$74))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*(('Jogos - Grupos'!$D$3:$D$74=$B6)+('Jogos - Grupos'!$E$3:$E$74=$B6))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
@@ -14654,27 +14638,27 @@
       </c>
       <c r="E6" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$D$3:$D$74=$B6)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$E$3:$E$74=$B6)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$D$3:$D$74=$B6)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$E$3:$E$74=$B6)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="110">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" s="110">
         <f t="shared" si="2"/>
-        <v>3201002462</v>
+        <v>200000462</v>
       </c>
       <c r="J6" s="8">
         <f>RANK(I6,$I$3:$I$6,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" s="110">
         <v>38</v>
@@ -14861,7 +14845,7 @@
       </c>
       <c r="C11" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$D$3:$D$74=$B11)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74&gt;'Jogos - Grupos'!$G$3:$G$74))+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$E$3:$E$74=$B11)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$G$3:$G$74&gt;'Jogos - Grupos'!$F$3:$F$74))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*(('Jogos - Grupos'!$D$3:$D$74=$B11)+('Jogos - Grupos'!$E$3:$E$74=$B11))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
@@ -14869,7 +14853,7 @@
       </c>
       <c r="E11" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$D$3:$D$74=$B11)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$E$3:$E$74=$B11)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$D$3:$D$74=$B11)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$E$3:$E$74=$B11)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
@@ -14877,15 +14861,15 @@
       </c>
       <c r="G11" s="114">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" s="19">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" s="114">
         <f t="shared" si="2"/>
-        <v>3202002495</v>
+        <v>200000495</v>
       </c>
       <c r="J11" s="19">
         <f>RANK(I11,$I$11:$I$14,0)</f>
@@ -14916,11 +14900,11 @@
       </c>
       <c r="F12" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A12)*('Jogos - Grupos'!$D$3:$D$74=$B12)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A12)*('Jogos - Grupos'!$E$3:$E$74=$B12)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="114">
         <f t="shared" si="0"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H12" s="19">
         <f t="shared" si="1"/>
@@ -14928,11 +14912,11 @@
       </c>
       <c r="I12" s="114">
         <f t="shared" si="2"/>
-        <v>198000486</v>
+        <v>200000486</v>
       </c>
       <c r="J12" s="19">
         <f>RANK(I12,$I$11:$I$14,0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K12" s="114">
         <v>14</v>
@@ -14955,15 +14939,15 @@
       </c>
       <c r="E13" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A13)*('Jogos - Grupos'!$D$3:$D$74=$B13)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A13)*('Jogos - Grupos'!$E$3:$E$74=$B13)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A13)*('Jogos - Grupos'!$D$3:$D$74=$B13)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A13)*('Jogos - Grupos'!$E$3:$E$74=$B13)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" s="114">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="19">
         <f t="shared" si="1"/>
@@ -14971,11 +14955,11 @@
       </c>
       <c r="I13" s="114">
         <f t="shared" si="2"/>
-        <v>199001414</v>
+        <v>200000414</v>
       </c>
       <c r="J13" s="19">
         <f>RANK(I13,$I$11:$I$14,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" s="114">
         <v>86</v>
@@ -14990,7 +14974,7 @@
       </c>
       <c r="C14" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A14)*('Jogos - Grupos'!$D$3:$D$74=$B14)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74&gt;'Jogos - Grupos'!$G$3:$G$74))+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A14)*('Jogos - Grupos'!$E$3:$E$74=$B14)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$G$3:$G$74&gt;'Jogos - Grupos'!$F$3:$F$74))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A14)*(('Jogos - Grupos'!$D$3:$D$74=$B14)+('Jogos - Grupos'!$E$3:$E$74=$B14))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
@@ -14998,27 +14982,27 @@
       </c>
       <c r="E14" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A14)*('Jogos - Grupos'!$D$3:$D$74=$B14)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A14)*('Jogos - Grupos'!$E$3:$E$74=$B14)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F14" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A14)*('Jogos - Grupos'!$D$3:$D$74=$B14)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A14)*('Jogos - Grupos'!$E$3:$E$74=$B14)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="114">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="19">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I14" s="114">
         <f t="shared" si="2"/>
-        <v>3201002473</v>
+        <v>200000473</v>
       </c>
       <c r="J14" s="19">
         <f>RANK(I14,$I$11:$I$14,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="114">
         <v>27</v>
@@ -16599,11 +16583,11 @@
       </c>
       <c r="C53" s="135" t="str">
         <f>IFERROR(INDEX($B$3:$B$6,MATCH(2,$J$3:$J$6,0)),"?")</f>
-        <v>Tchequia</v>
+        <v>Coreia do Sul</v>
       </c>
       <c r="D53" s="135" t="str">
         <f>IFERROR(INDEX($B$3:$B$6,MATCH(3,$J$3:$J$6,0)),"?")</f>
-        <v>Coreia do Sul</v>
+        <v>Tchequia</v>
       </c>
       <c r="E53" s="135" t="str">
         <f>IFERROR(INDEX($B$3:$B$6,MATCH(4,$J$3:$J$6,0)),"?")</f>
@@ -16641,15 +16625,15 @@
       </c>
       <c r="C55" s="135" t="str">
         <f>IFERROR(INDEX($B$11:$B$14,MATCH(2,$J$11:$J$14,0)),"?")</f>
-        <v>Escocia</v>
+        <v>Marrocos</v>
       </c>
       <c r="D55" s="135" t="str">
         <f>IFERROR(INDEX($B$11:$B$14,MATCH(3,$J$11:$J$14,0)),"?")</f>
-        <v>Haiti</v>
+        <v>Escocia</v>
       </c>
       <c r="E55" s="135" t="str">
         <f>IFERROR(INDEX($B$11:$B$14,MATCH(4,$J$11:$J$14,0)),"?")</f>
-        <v>Marrocos</v>
+        <v>Haiti</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -16861,15 +16845,15 @@
       </c>
       <c r="B68" s="149" t="str">
         <f>IFERROR(INDEX($B$3:$B$6,MATCH(3,$J$3:$J$6,0)),"?")</f>
-        <v>Coreia do Sul</v>
+        <v>Tchequia</v>
       </c>
       <c r="C68" s="149">
         <f>IFERROR(INDEX($I$3:$I$6,MATCH(3,$J$3:$J$6,0)),0)</f>
-        <v>199001477</v>
+        <v>200000462</v>
       </c>
       <c r="D68" s="150">
         <f t="shared" ref="D68:D79" si="3">RANK(C68,$C$68:$C$79,0)</f>
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -16886,7 +16870,7 @@
       </c>
       <c r="D69" s="150">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -16895,15 +16879,15 @@
       </c>
       <c r="B70" s="149" t="str">
         <f>IFERROR(INDEX($B$11:$B$14,MATCH(3,$J$11:$J$14,0)),"?")</f>
-        <v>Haiti</v>
+        <v>Escocia</v>
       </c>
       <c r="C70" s="149">
         <f>IFERROR(INDEX($I$11:$I$14,MATCH(3,$J$11:$J$14,0)),0)</f>
-        <v>199001414</v>
+        <v>200000473</v>
       </c>
       <c r="D70" s="150">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -16920,7 +16904,7 @@
       </c>
       <c r="D71" s="150">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -16937,7 +16921,7 @@
       </c>
       <c r="D72" s="150">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -16971,7 +16955,7 @@
       </c>
       <c r="D74" s="150">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -16988,7 +16972,7 @@
       </c>
       <c r="D75" s="150">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -17005,7 +16989,7 @@
       </c>
       <c r="D76" s="150">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -17022,7 +17006,7 @@
       </c>
       <c r="D77" s="150">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -17039,7 +17023,7 @@
       </c>
       <c r="D78" s="150">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -17056,7 +17040,7 @@
       </c>
       <c r="D79" s="150">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
@@ -17082,7 +17066,7 @@
       </c>
       <c r="B83" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(2,$D$68:$D$79,0)),"?")</f>
-        <v>Noruega</v>
+        <v>Escocia</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
@@ -17091,7 +17075,7 @@
       </c>
       <c r="B84" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(3,$D$68:$D$79,0)),"?")</f>
-        <v>Argelia</v>
+        <v>Noruega</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
@@ -17100,7 +17084,7 @@
       </c>
       <c r="B85" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(4,$D$68:$D$79,0)),"?")</f>
-        <v>Turquia</v>
+        <v>Argelia</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
@@ -17109,7 +17093,7 @@
       </c>
       <c r="B86" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(5,$D$68:$D$79,0)),"?")</f>
-        <v>?</v>
+        <v>Turquia</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
@@ -17118,7 +17102,7 @@
       </c>
       <c r="B87" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(6,$D$68:$D$79,0)),"?")</f>
-        <v>Costa do Marfim</v>
+        <v>?</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
@@ -17127,7 +17111,7 @@
       </c>
       <c r="B88" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(7,$D$68:$D$79,0)),"?")</f>
-        <v>Canada</v>
+        <v>Tchequia</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
@@ -17136,7 +17120,7 @@
       </c>
       <c r="B89" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(8,$D$68:$D$79,0)),"?")</f>
-        <v>Gana</v>
+        <v>Costa do Marfim</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
@@ -17145,7 +17129,7 @@
       </c>
       <c r="B92" s="166" t="str">
         <f>IF(D68&lt;=8,"A","")&amp;IF(D69&lt;=8,"B","")&amp;IF(D70&lt;=8,"C","")&amp;IF(D71&lt;=8,"D","")&amp;IF(D72&lt;=8,"E","")&amp;IF(D73&lt;=8,"F","")&amp;IF(D74&lt;=8,"G","")&amp;IF(D75&lt;=8,"H","")&amp;IF(D76&lt;=8,"I","")&amp;IF(D77&lt;=8,"J","")&amp;IF(D78&lt;=8,"K","")&amp;IF(D79&lt;=8,"L","")</f>
-        <v>BDEFGIJL</v>
+        <v>ACDEFGIJ</v>
       </c>
     </row>
   </sheetData>
@@ -17169,7 +17153,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="255" t="s">
+      <c r="A1" s="252" t="s">
         <v>435</v>
       </c>
       <c r="B1" s="253"/>
@@ -31590,7 +31574,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="255" t="s">
+      <c r="A1" s="252" t="s">
         <v>952</v>
       </c>
       <c r="B1" s="253"/>
@@ -43585,7 +43569,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="255" t="s">
+      <c r="A1" s="252" t="s">
         <v>956</v>
       </c>
       <c r="B1" s="253"/>
@@ -43654,7 +43638,7 @@
       </c>
       <c r="D4" s="175" t="str">
         <f>IFERROR('Classif - Grupos'!C53,"Aguardando")</f>
-        <v>Tchequia</v>
+        <v>Coreia do Sul</v>
       </c>
       <c r="E4" s="175" t="str">
         <f>IFERROR('Classif - Grupos'!C54,"Aguardando")</f>
@@ -43718,7 +43702,7 @@
       </c>
       <c r="E6" s="175" t="str">
         <f>IFERROR('Classif - Grupos'!C55,"Aguardando")</f>
-        <v>Escocia</v>
+        <v>Marrocos</v>
       </c>
       <c r="F6" s="249"/>
       <c r="G6" s="249"/>
@@ -43838,7 +43822,7 @@
       </c>
       <c r="E10" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,2,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Costa do Marfim</v>
+        <v>Escocia</v>
       </c>
       <c r="F10" s="249"/>
       <c r="G10" s="249"/>
@@ -43898,7 +43882,7 @@
       </c>
       <c r="E12" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,4,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Canada</v>
+        <v>Argelia</v>
       </c>
       <c r="F12" s="249"/>
       <c r="G12" s="249"/>
@@ -43928,7 +43912,7 @@
       </c>
       <c r="E13" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,6,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Argelia</v>
+        <v>Tchequia</v>
       </c>
       <c r="F13" s="249"/>
       <c r="G13" s="249"/>
@@ -44078,7 +44062,7 @@
       </c>
       <c r="E18" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,8,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Gana</v>
+        <v>Costa do Marfim</v>
       </c>
       <c r="F18" s="249"/>
       <c r="G18" s="249"/>

--- a/gabarito/Bolao_Copa2026_TurimMFO_Master - Copia.xlsx
+++ b/gabarito/Bolao_Copa2026_TurimMFO_Master - Copia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pbrandao\Projetos\bolao-copa-2026\gabarito\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DACC5F-AE09-4446-A8D2-3EE8EF6BBA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5485572D-86F7-44D9-A3AC-1FB006CB9578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regras" sheetId="1" r:id="rId1"/>
@@ -4924,67 +4924,73 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="47" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="41" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="47" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="42" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="44" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4993,22 +4999,13 @@
     <xf numFmtId="164" fontId="46" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5024,6 +5021,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5784,7 +5784,7 @@
       <c r="BM1" s="253"/>
     </row>
     <row r="2" spans="1:65" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>1028</v>
       </c>
       <c r="B2" s="253"/>
@@ -5920,67 +5920,67 @@
         <v>994</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="273" t="s">
+      <c r="AH3" s="270" t="s">
         <v>996</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="273" t="s">
+      <c r="AJ3" s="270" t="s">
         <v>998</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="273" t="s">
+      <c r="AL3" s="270" t="s">
         <v>1000</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="273" t="s">
+      <c r="AN3" s="270" t="s">
         <v>1002</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="273" t="s">
+      <c r="AP3" s="270" t="s">
         <v>1004</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="273" t="s">
+      <c r="AR3" s="270" t="s">
         <v>1006</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="273" t="s">
+      <c r="AT3" s="270" t="s">
         <v>1008</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="273" t="s">
+      <c r="AV3" s="270" t="s">
         <v>1010</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="275" t="s">
+      <c r="AX3" s="274" t="s">
         <v>1012</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="275" t="s">
+      <c r="AZ3" s="274" t="s">
         <v>1014</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="275" t="s">
+      <c r="BB3" s="274" t="s">
         <v>1016</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="275" t="s">
+      <c r="BD3" s="274" t="s">
         <v>1018</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="281" t="s">
+      <c r="BF3" s="277" t="s">
         <v>1020</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="281" t="s">
+      <c r="BH3" s="277" t="s">
         <v>1022</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="279" t="s">
+      <c r="BJ3" s="273" t="s">
         <v>1024</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="280" t="s">
+      <c r="BL3" s="275" t="s">
         <v>1026</v>
       </c>
       <c r="BM3" s="253"/>
@@ -5989,131 +5989,131 @@
       <c r="A4" s="210" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="270">
+      <c r="B4" s="272">
         <v>46201</v>
       </c>
       <c r="C4" s="253"/>
-      <c r="D4" s="270">
+      <c r="D4" s="272">
         <v>46202</v>
       </c>
       <c r="E4" s="253"/>
-      <c r="F4" s="270">
+      <c r="F4" s="272">
         <v>46202</v>
       </c>
       <c r="G4" s="253"/>
-      <c r="H4" s="270">
+      <c r="H4" s="272">
         <v>46202</v>
       </c>
       <c r="I4" s="253"/>
-      <c r="J4" s="270">
+      <c r="J4" s="272">
         <v>46203</v>
       </c>
       <c r="K4" s="253"/>
-      <c r="L4" s="270">
+      <c r="L4" s="272">
         <v>46203</v>
       </c>
       <c r="M4" s="253"/>
-      <c r="N4" s="270">
+      <c r="N4" s="272">
         <v>46203</v>
       </c>
       <c r="O4" s="253"/>
-      <c r="P4" s="270">
+      <c r="P4" s="272">
         <v>46204</v>
       </c>
       <c r="Q4" s="253"/>
-      <c r="R4" s="270">
+      <c r="R4" s="272">
         <v>46204</v>
       </c>
       <c r="S4" s="253"/>
-      <c r="T4" s="270">
+      <c r="T4" s="272">
         <v>46204</v>
       </c>
       <c r="U4" s="253"/>
-      <c r="V4" s="270">
+      <c r="V4" s="272">
         <v>46205</v>
       </c>
       <c r="W4" s="253"/>
-      <c r="X4" s="270">
+      <c r="X4" s="272">
         <v>46205</v>
       </c>
       <c r="Y4" s="253"/>
-      <c r="Z4" s="270">
+      <c r="Z4" s="272">
         <v>46205</v>
       </c>
       <c r="AA4" s="253"/>
-      <c r="AB4" s="270">
+      <c r="AB4" s="272">
         <v>46206</v>
       </c>
       <c r="AC4" s="253"/>
-      <c r="AD4" s="270">
+      <c r="AD4" s="272">
         <v>46206</v>
       </c>
       <c r="AE4" s="253"/>
-      <c r="AF4" s="270">
+      <c r="AF4" s="272">
         <v>46206</v>
       </c>
       <c r="AG4" s="253"/>
-      <c r="AH4" s="274">
+      <c r="AH4" s="276">
         <v>46207</v>
       </c>
       <c r="AI4" s="253"/>
-      <c r="AJ4" s="274">
+      <c r="AJ4" s="276">
         <v>46207</v>
       </c>
       <c r="AK4" s="253"/>
-      <c r="AL4" s="274">
+      <c r="AL4" s="276">
         <v>46208</v>
       </c>
       <c r="AM4" s="253"/>
-      <c r="AN4" s="274">
+      <c r="AN4" s="276">
         <v>46208</v>
       </c>
       <c r="AO4" s="253"/>
-      <c r="AP4" s="274">
+      <c r="AP4" s="276">
         <v>46209</v>
       </c>
       <c r="AQ4" s="253"/>
-      <c r="AR4" s="274">
+      <c r="AR4" s="276">
         <v>46209</v>
       </c>
       <c r="AS4" s="253"/>
-      <c r="AT4" s="274">
+      <c r="AT4" s="276">
         <v>46210</v>
       </c>
       <c r="AU4" s="253"/>
-      <c r="AV4" s="274">
+      <c r="AV4" s="276">
         <v>46210</v>
       </c>
       <c r="AW4" s="253"/>
-      <c r="AX4" s="272">
+      <c r="AX4" s="278">
         <v>46212</v>
       </c>
       <c r="AY4" s="253"/>
-      <c r="AZ4" s="272">
+      <c r="AZ4" s="278">
         <v>46213</v>
       </c>
       <c r="BA4" s="253"/>
-      <c r="BB4" s="272">
+      <c r="BB4" s="278">
         <v>46214</v>
       </c>
       <c r="BC4" s="253"/>
-      <c r="BD4" s="272">
+      <c r="BD4" s="278">
         <v>46214</v>
       </c>
       <c r="BE4" s="253"/>
-      <c r="BF4" s="277">
+      <c r="BF4" s="279">
         <v>46217</v>
       </c>
       <c r="BG4" s="253"/>
-      <c r="BH4" s="277">
+      <c r="BH4" s="279">
         <v>46218</v>
       </c>
       <c r="BI4" s="253"/>
-      <c r="BJ4" s="276">
+      <c r="BJ4" s="281">
         <v>46221</v>
       </c>
       <c r="BK4" s="253"/>
-      <c r="BL4" s="278">
+      <c r="BL4" s="280">
         <v>46222</v>
       </c>
       <c r="BM4" s="253"/>
@@ -7568,6 +7568,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="AX4:AY4"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AR4:AS4"/>
+    <mergeCell ref="AV4:AW4"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="AP3:AQ3"/>
+    <mergeCell ref="BB3:BC3"/>
+    <mergeCell ref="BJ4:BK4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="BH4:BI4"/>
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AP4:AQ4"/>
+    <mergeCell ref="A1:BM1"/>
+    <mergeCell ref="AT4:AU4"/>
+    <mergeCell ref="AZ4:BA4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="BB4:BC4"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="BD4:BE4"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="BF4:BG4"/>
+    <mergeCell ref="BL4:BM4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="X4:Y4"/>
     <mergeCell ref="A2:BM2"/>
     <mergeCell ref="AR3:AS3"/>
     <mergeCell ref="T3:U3"/>
@@ -7584,56 +7634,6 @@
     <mergeCell ref="BF3:BG3"/>
     <mergeCell ref="BH3:BI3"/>
     <mergeCell ref="V4:W4"/>
-    <mergeCell ref="A1:BM1"/>
-    <mergeCell ref="AT4:AU4"/>
-    <mergeCell ref="AZ4:BA4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="BB4:BC4"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="BD4:BE4"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="BF4:BG4"/>
-    <mergeCell ref="BL4:BM4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="BH4:BI4"/>
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AP4:AQ4"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="AP3:AQ3"/>
-    <mergeCell ref="BB3:BC3"/>
-    <mergeCell ref="BJ4:BK4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="AX4:AY4"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AR4:AS4"/>
-    <mergeCell ref="AV4:AW4"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="X3:Y3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7691,7 +7691,7 @@
       <c r="AH1" s="253"/>
     </row>
     <row r="2" spans="1:34" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>1032</v>
       </c>
       <c r="B2" s="253"/>
@@ -8857,7 +8857,7 @@
       <c r="J1" s="253"/>
     </row>
     <row r="2" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>1079</v>
       </c>
       <c r="B2" s="253"/>
@@ -8871,49 +8871,49 @@
       <c r="J2" s="253"/>
     </row>
     <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="284" t="s">
+      <c r="A4" s="289" t="s">
         <v>1080</v>
       </c>
       <c r="B4" s="253"/>
-      <c r="C4" s="284" t="s">
+      <c r="C4" s="289" t="s">
         <v>1081</v>
       </c>
       <c r="D4" s="253"/>
-      <c r="E4" s="284" t="s">
+      <c r="E4" s="289" t="s">
         <v>1082</v>
       </c>
       <c r="F4" s="253"/>
-      <c r="G4" s="284" t="s">
+      <c r="G4" s="289" t="s">
         <v>1083</v>
       </c>
       <c r="H4" s="253"/>
-      <c r="I4" s="284" t="s">
+      <c r="I4" s="289" t="s">
         <v>1084</v>
       </c>
       <c r="J4" s="253"/>
     </row>
     <row r="5" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="286" t="str">
+      <c r="A5" s="285" t="str">
         <f>IFERROR(INDEX(Ranking!$I$4:$I$7,MATCH(1,Ranking!$P$4:$P$7,0)),"?")</f>
         <v>Pedro Brandao</v>
       </c>
       <c r="B5" s="253"/>
-      <c r="C5" s="285">
+      <c r="C5" s="284">
         <f>IFERROR(MAX(Ranking!$M$4:$M$7),0)</f>
         <v>0</v>
       </c>
       <c r="D5" s="253"/>
-      <c r="E5" s="288">
+      <c r="E5" s="287">
         <f>COUNTIF('Jogos - Grupos'!H3:H74,"Finalizado")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F5" s="253"/>
-      <c r="G5" s="287">
+      <c r="G5" s="286">
         <f>COUNTIF('Mata-Mata - Jogos'!I4:I35,"Finalizado")</f>
         <v>0</v>
       </c>
       <c r="H5" s="253"/>
-      <c r="I5" s="289" t="s">
+      <c r="I5" s="288" t="s">
         <v>1077</v>
       </c>
       <c r="J5" s="253"/>
@@ -9064,11 +9064,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="I5:J5"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="A1:J1"/>
@@ -9076,6 +9071,11 @@
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="I5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9151,11 +9151,15 @@
       <c r="E3" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
+      <c r="F3" s="10">
+        <v>3</v>
+      </c>
+      <c r="G3" s="10">
+        <v>1</v>
+      </c>
       <c r="H3" s="11" t="str">
         <f t="shared" ref="H3:H34" si="0">IF(AND(F3="",G3=""),"Aguardando",IF(AND(ISNUMBER(F3),ISNUMBER(G3)),"Finalizado","Verificar"))</f>
-        <v>Aguardando</v>
+        <v>Finalizado</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -9174,11 +9178,15 @@
       <c r="E4" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
+      <c r="F4" s="10">
+        <v>0</v>
+      </c>
+      <c r="G4" s="10">
+        <v>2</v>
+      </c>
       <c r="H4" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>Aguardando</v>
+        <v>Finalizado</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -9289,11 +9297,15 @@
       <c r="E9" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
+      <c r="F9" s="10">
+        <v>2</v>
+      </c>
+      <c r="G9" s="10">
+        <v>1</v>
+      </c>
       <c r="H9" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>Aguardando</v>
+        <v>Finalizado</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -9312,11 +9324,15 @@
       <c r="E10" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
+      <c r="F10" s="10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="10">
+        <v>0</v>
+      </c>
       <c r="H10" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>Aguardando</v>
+        <v>Finalizado</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -9427,11 +9443,15 @@
       <c r="E15" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
+      <c r="F15" s="10">
+        <v>3</v>
+      </c>
+      <c r="G15" s="10">
+        <v>2</v>
+      </c>
       <c r="H15" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>Aguardando</v>
+        <v>Finalizado</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -9450,11 +9470,15 @@
       <c r="E16" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
+      <c r="F16" s="10">
+        <v>1</v>
+      </c>
+      <c r="G16" s="10">
+        <v>0</v>
+      </c>
       <c r="H16" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>Aguardando</v>
+        <v>Finalizado</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -10961,7 +10985,7 @@
       <c r="EO1" s="253"/>
     </row>
     <row r="2" spans="1:145" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>186</v>
       </c>
       <c r="B2" s="253"/>
@@ -11113,219 +11137,219 @@
       <c r="A3" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="B3" s="256" t="s">
+      <c r="B3" s="263" t="s">
         <v>188</v>
       </c>
       <c r="C3" s="253"/>
-      <c r="D3" s="256" t="s">
+      <c r="D3" s="263" t="s">
         <v>189</v>
       </c>
       <c r="E3" s="253"/>
-      <c r="F3" s="256" t="s">
+      <c r="F3" s="263" t="s">
         <v>190</v>
       </c>
       <c r="G3" s="253"/>
-      <c r="H3" s="256" t="s">
+      <c r="H3" s="263" t="s">
         <v>191</v>
       </c>
       <c r="I3" s="253"/>
-      <c r="J3" s="256" t="s">
+      <c r="J3" s="263" t="s">
         <v>192</v>
       </c>
       <c r="K3" s="253"/>
-      <c r="L3" s="256" t="s">
+      <c r="L3" s="263" t="s">
         <v>193</v>
       </c>
       <c r="M3" s="253"/>
-      <c r="N3" s="260" t="s">
+      <c r="N3" s="264" t="s">
         <v>194</v>
       </c>
       <c r="O3" s="253"/>
-      <c r="P3" s="260" t="s">
+      <c r="P3" s="264" t="s">
         <v>195</v>
       </c>
       <c r="Q3" s="253"/>
-      <c r="R3" s="260" t="s">
+      <c r="R3" s="264" t="s">
         <v>196</v>
       </c>
       <c r="S3" s="253"/>
-      <c r="T3" s="260" t="s">
+      <c r="T3" s="264" t="s">
         <v>197</v>
       </c>
       <c r="U3" s="253"/>
-      <c r="V3" s="260" t="s">
+      <c r="V3" s="264" t="s">
         <v>198</v>
       </c>
       <c r="W3" s="253"/>
-      <c r="X3" s="260" t="s">
+      <c r="X3" s="264" t="s">
         <v>199</v>
       </c>
       <c r="Y3" s="253"/>
-      <c r="Z3" s="261" t="s">
+      <c r="Z3" s="259" t="s">
         <v>200</v>
       </c>
       <c r="AA3" s="253"/>
-      <c r="AB3" s="261" t="s">
+      <c r="AB3" s="259" t="s">
         <v>201</v>
       </c>
       <c r="AC3" s="253"/>
-      <c r="AD3" s="261" t="s">
+      <c r="AD3" s="259" t="s">
         <v>202</v>
       </c>
       <c r="AE3" s="253"/>
-      <c r="AF3" s="261" t="s">
+      <c r="AF3" s="259" t="s">
         <v>203</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="261" t="s">
+      <c r="AH3" s="259" t="s">
         <v>204</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="261" t="s">
+      <c r="AJ3" s="259" t="s">
         <v>205</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="257" t="s">
+      <c r="AL3" s="260" t="s">
         <v>206</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="257" t="s">
+      <c r="AN3" s="260" t="s">
         <v>207</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="257" t="s">
+      <c r="AP3" s="260" t="s">
         <v>208</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="257" t="s">
+      <c r="AR3" s="260" t="s">
         <v>209</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="257" t="s">
+      <c r="AT3" s="260" t="s">
         <v>210</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="257" t="s">
+      <c r="AV3" s="260" t="s">
         <v>211</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="258" t="s">
+      <c r="AX3" s="265" t="s">
         <v>212</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="258" t="s">
+      <c r="AZ3" s="265" t="s">
         <v>213</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="258" t="s">
+      <c r="BB3" s="265" t="s">
         <v>214</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="258" t="s">
+      <c r="BD3" s="265" t="s">
         <v>215</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="258" t="s">
+      <c r="BF3" s="265" t="s">
         <v>216</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="258" t="s">
+      <c r="BH3" s="265" t="s">
         <v>217</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="262" t="s">
+      <c r="BJ3" s="266" t="s">
         <v>218</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="262" t="s">
+      <c r="BL3" s="266" t="s">
         <v>219</v>
       </c>
       <c r="BM3" s="253"/>
-      <c r="BN3" s="262" t="s">
+      <c r="BN3" s="266" t="s">
         <v>220</v>
       </c>
       <c r="BO3" s="253"/>
-      <c r="BP3" s="262" t="s">
+      <c r="BP3" s="266" t="s">
         <v>221</v>
       </c>
       <c r="BQ3" s="253"/>
-      <c r="BR3" s="262" t="s">
+      <c r="BR3" s="266" t="s">
         <v>222</v>
       </c>
       <c r="BS3" s="253"/>
-      <c r="BT3" s="262" t="s">
+      <c r="BT3" s="266" t="s">
         <v>223</v>
       </c>
       <c r="BU3" s="253"/>
-      <c r="BV3" s="263" t="s">
+      <c r="BV3" s="256" t="s">
         <v>224</v>
       </c>
       <c r="BW3" s="253"/>
-      <c r="BX3" s="263" t="s">
+      <c r="BX3" s="256" t="s">
         <v>225</v>
       </c>
       <c r="BY3" s="253"/>
-      <c r="BZ3" s="263" t="s">
+      <c r="BZ3" s="256" t="s">
         <v>226</v>
       </c>
       <c r="CA3" s="253"/>
-      <c r="CB3" s="263" t="s">
+      <c r="CB3" s="256" t="s">
         <v>227</v>
       </c>
       <c r="CC3" s="253"/>
-      <c r="CD3" s="263" t="s">
+      <c r="CD3" s="256" t="s">
         <v>228</v>
       </c>
       <c r="CE3" s="253"/>
-      <c r="CF3" s="263" t="s">
+      <c r="CF3" s="256" t="s">
         <v>229</v>
       </c>
       <c r="CG3" s="253"/>
-      <c r="CH3" s="259" t="s">
+      <c r="CH3" s="257" t="s">
         <v>230</v>
       </c>
       <c r="CI3" s="253"/>
-      <c r="CJ3" s="259" t="s">
+      <c r="CJ3" s="257" t="s">
         <v>231</v>
       </c>
       <c r="CK3" s="253"/>
-      <c r="CL3" s="259" t="s">
+      <c r="CL3" s="257" t="s">
         <v>232</v>
       </c>
       <c r="CM3" s="253"/>
-      <c r="CN3" s="259" t="s">
+      <c r="CN3" s="257" t="s">
         <v>233</v>
       </c>
       <c r="CO3" s="253"/>
-      <c r="CP3" s="259" t="s">
+      <c r="CP3" s="257" t="s">
         <v>234</v>
       </c>
       <c r="CQ3" s="253"/>
-      <c r="CR3" s="259" t="s">
+      <c r="CR3" s="257" t="s">
         <v>235</v>
       </c>
       <c r="CS3" s="253"/>
-      <c r="CT3" s="265" t="s">
+      <c r="CT3" s="258" t="s">
         <v>236</v>
       </c>
       <c r="CU3" s="253"/>
-      <c r="CV3" s="265" t="s">
+      <c r="CV3" s="258" t="s">
         <v>237</v>
       </c>
       <c r="CW3" s="253"/>
-      <c r="CX3" s="265" t="s">
+      <c r="CX3" s="258" t="s">
         <v>238</v>
       </c>
       <c r="CY3" s="253"/>
-      <c r="CZ3" s="265" t="s">
+      <c r="CZ3" s="258" t="s">
         <v>239</v>
       </c>
       <c r="DA3" s="253"/>
-      <c r="DB3" s="265" t="s">
+      <c r="DB3" s="258" t="s">
         <v>240</v>
       </c>
       <c r="DC3" s="253"/>
-      <c r="DD3" s="265" t="s">
+      <c r="DD3" s="258" t="s">
         <v>241</v>
       </c>
       <c r="DE3" s="253"/>
@@ -11353,51 +11377,51 @@
         <v>247</v>
       </c>
       <c r="DQ3" s="253"/>
-      <c r="DR3" s="266" t="s">
+      <c r="DR3" s="268" t="s">
         <v>248</v>
       </c>
       <c r="DS3" s="253"/>
-      <c r="DT3" s="266" t="s">
+      <c r="DT3" s="268" t="s">
         <v>249</v>
       </c>
       <c r="DU3" s="253"/>
-      <c r="DV3" s="266" t="s">
+      <c r="DV3" s="268" t="s">
         <v>250</v>
       </c>
       <c r="DW3" s="253"/>
-      <c r="DX3" s="266" t="s">
+      <c r="DX3" s="268" t="s">
         <v>251</v>
       </c>
       <c r="DY3" s="253"/>
-      <c r="DZ3" s="266" t="s">
+      <c r="DZ3" s="268" t="s">
         <v>252</v>
       </c>
       <c r="EA3" s="253"/>
-      <c r="EB3" s="266" t="s">
+      <c r="EB3" s="268" t="s">
         <v>253</v>
       </c>
       <c r="EC3" s="253"/>
-      <c r="ED3" s="264" t="s">
+      <c r="ED3" s="262" t="s">
         <v>254</v>
       </c>
       <c r="EE3" s="253"/>
-      <c r="EF3" s="264" t="s">
+      <c r="EF3" s="262" t="s">
         <v>255</v>
       </c>
       <c r="EG3" s="253"/>
-      <c r="EH3" s="264" t="s">
+      <c r="EH3" s="262" t="s">
         <v>256</v>
       </c>
       <c r="EI3" s="253"/>
-      <c r="EJ3" s="264" t="s">
+      <c r="EJ3" s="262" t="s">
         <v>257</v>
       </c>
       <c r="EK3" s="253"/>
-      <c r="EL3" s="264" t="s">
+      <c r="EL3" s="262" t="s">
         <v>258</v>
       </c>
       <c r="EM3" s="253"/>
-      <c r="EN3" s="264" t="s">
+      <c r="EN3" s="262" t="s">
         <v>259</v>
       </c>
       <c r="EO3" s="253"/>
@@ -12437,25 +12461,38 @@
     </row>
   </sheetData>
   <mergeCells count="74">
-    <mergeCell ref="BX3:BY3"/>
-    <mergeCell ref="CN3:CO3"/>
-    <mergeCell ref="CZ3:DA3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="A2:EO2"/>
-    <mergeCell ref="EJ3:EK3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="BJ3:BK3"/>
-    <mergeCell ref="AZ3:BA3"/>
-    <mergeCell ref="BL3:BM3"/>
-    <mergeCell ref="DL3:DM3"/>
-    <mergeCell ref="BV3:BW3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="AP3:AQ3"/>
+    <mergeCell ref="BB3:BC3"/>
+    <mergeCell ref="CJ3:CK3"/>
+    <mergeCell ref="CL3:CM3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="BT3:BU3"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="CF3:CG3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="AR3:AS3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="EN3:EO3"/>
+    <mergeCell ref="CX3:CY3"/>
+    <mergeCell ref="DV3:DW3"/>
+    <mergeCell ref="EB3:EC3"/>
+    <mergeCell ref="ED3:EE3"/>
+    <mergeCell ref="EH3:EI3"/>
+    <mergeCell ref="DZ3:EA3"/>
+    <mergeCell ref="EF3:EG3"/>
+    <mergeCell ref="DH3:DI3"/>
+    <mergeCell ref="DT3:DU3"/>
+    <mergeCell ref="DR3:DS3"/>
+    <mergeCell ref="DX3:DY3"/>
+    <mergeCell ref="DD3:DE3"/>
+    <mergeCell ref="DF3:DG3"/>
+    <mergeCell ref="DB3:DC3"/>
+    <mergeCell ref="DN3:DO3"/>
     <mergeCell ref="A1:EO1"/>
     <mergeCell ref="AT3:AU3"/>
     <mergeCell ref="N3:O3"/>
@@ -12472,45 +12509,32 @@
     <mergeCell ref="V3:W3"/>
     <mergeCell ref="AB3:AC3"/>
     <mergeCell ref="CR3:CS3"/>
+    <mergeCell ref="A2:EO2"/>
+    <mergeCell ref="EJ3:EK3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="BJ3:BK3"/>
+    <mergeCell ref="AZ3:BA3"/>
+    <mergeCell ref="BL3:BM3"/>
+    <mergeCell ref="DL3:DM3"/>
+    <mergeCell ref="BV3:BW3"/>
     <mergeCell ref="CB3:CC3"/>
     <mergeCell ref="DJ3:DK3"/>
     <mergeCell ref="EL3:EM3"/>
     <mergeCell ref="CV3:CW3"/>
+    <mergeCell ref="BX3:BY3"/>
+    <mergeCell ref="CN3:CO3"/>
+    <mergeCell ref="CZ3:DA3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
     <mergeCell ref="CH3:CI3"/>
     <mergeCell ref="CD3:CE3"/>
-    <mergeCell ref="DR3:DS3"/>
-    <mergeCell ref="DX3:DY3"/>
-    <mergeCell ref="DD3:DE3"/>
-    <mergeCell ref="DF3:DG3"/>
-    <mergeCell ref="DB3:DC3"/>
     <mergeCell ref="CT3:CU3"/>
-    <mergeCell ref="DN3:DO3"/>
-    <mergeCell ref="EN3:EO3"/>
-    <mergeCell ref="CX3:CY3"/>
-    <mergeCell ref="DV3:DW3"/>
-    <mergeCell ref="EB3:EC3"/>
-    <mergeCell ref="ED3:EE3"/>
-    <mergeCell ref="EH3:EI3"/>
-    <mergeCell ref="DZ3:EA3"/>
-    <mergeCell ref="EF3:EG3"/>
-    <mergeCell ref="DH3:DI3"/>
-    <mergeCell ref="DT3:DU3"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="AP3:AQ3"/>
-    <mergeCell ref="BB3:BC3"/>
-    <mergeCell ref="CJ3:CK3"/>
-    <mergeCell ref="CL3:CM3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="BT3:BU3"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="CF3:CG3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="AR3:AS3"/>
-    <mergeCell ref="T3:U3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12536,7 +12560,7 @@
       <c r="C1" s="253"/>
     </row>
     <row r="2" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>266</v>
       </c>
       <c r="B2" s="253"/>
@@ -12689,7 +12713,7 @@
       <c r="BV1" s="253"/>
     </row>
     <row r="2" spans="1:74" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>271</v>
       </c>
       <c r="B2" s="253"/>
@@ -13216,13 +13240,13 @@
       <c r="A5" s="81" t="s">
         <v>261</v>
       </c>
-      <c r="B5" s="106" t="str">
+      <c r="B5" s="106">
         <f>IF(OR('Jogos - Grupos'!F3="",'Jogos - Grupos'!G3=""),"-",IF(OR('Apostas - Grupos'!B5="",'Apostas - Grupos'!C5=""),0,IF(AND('Apostas - Grupos'!B5='Jogos - Grupos'!F3,'Apostas - Grupos'!C5='Jogos - Grupos'!G3),5,IF(OR(AND('Jogos - Grupos'!F3='Jogos - Grupos'!G3,'Apostas - Grupos'!B5='Apostas - Grupos'!C5),AND('Jogos - Grupos'!F3&gt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B5&gt;'Apostas - Grupos'!C5),AND('Jogos - Grupos'!F3&lt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B5&lt;'Apostas - Grupos'!C5)),IF(('Apostas - Grupos'!B5-'Apostas - Grupos'!C5)=('Jogos - Grupos'!F3-'Jogos - Grupos'!G3),3,2),0))))</f>
-        <v>-</v>
-      </c>
-      <c r="C5" s="106" t="str">
+        <v>0</v>
+      </c>
+      <c r="C5" s="106">
         <f>IF(OR('Jogos - Grupos'!F4="",'Jogos - Grupos'!G4=""),"-",IF(OR('Apostas - Grupos'!D5="",'Apostas - Grupos'!E5=""),0,IF(AND('Apostas - Grupos'!D5='Jogos - Grupos'!F4,'Apostas - Grupos'!E5='Jogos - Grupos'!G4),5,IF(OR(AND('Jogos - Grupos'!F4='Jogos - Grupos'!G4,'Apostas - Grupos'!D5='Apostas - Grupos'!E5),AND('Jogos - Grupos'!F4&gt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D5&gt;'Apostas - Grupos'!E5),AND('Jogos - Grupos'!F4&lt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D5&lt;'Apostas - Grupos'!E5)),IF(('Apostas - Grupos'!D5-'Apostas - Grupos'!E5)=('Jogos - Grupos'!F4-'Jogos - Grupos'!G4),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="D5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F5="",'Jogos - Grupos'!G5=""),"-",IF(OR('Apostas - Grupos'!F5="",'Apostas - Grupos'!G5=""),0,IF(AND('Apostas - Grupos'!F5='Jogos - Grupos'!F5,'Apostas - Grupos'!G5='Jogos - Grupos'!G5),5,IF(OR(AND('Jogos - Grupos'!F5='Jogos - Grupos'!G5,'Apostas - Grupos'!F5='Apostas - Grupos'!G5),AND('Jogos - Grupos'!F5&gt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F5&gt;'Apostas - Grupos'!G5),AND('Jogos - Grupos'!F5&lt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F5&lt;'Apostas - Grupos'!G5)),IF(('Apostas - Grupos'!F5-'Apostas - Grupos'!G5)=('Jogos - Grupos'!F5-'Jogos - Grupos'!G5),3,2),0))))</f>
@@ -13240,13 +13264,13 @@
         <f>IF(OR('Jogos - Grupos'!F8="",'Jogos - Grupos'!G8=""),"-",IF(OR('Apostas - Grupos'!L5="",'Apostas - Grupos'!M5=""),0,IF(AND('Apostas - Grupos'!L5='Jogos - Grupos'!F8,'Apostas - Grupos'!M5='Jogos - Grupos'!G8),5,IF(OR(AND('Jogos - Grupos'!F8='Jogos - Grupos'!G8,'Apostas - Grupos'!L5='Apostas - Grupos'!M5),AND('Jogos - Grupos'!F8&gt;'Jogos - Grupos'!G8,'Apostas - Grupos'!L5&gt;'Apostas - Grupos'!M5),AND('Jogos - Grupos'!F8&lt;'Jogos - Grupos'!G8,'Apostas - Grupos'!L5&lt;'Apostas - Grupos'!M5)),IF(('Apostas - Grupos'!L5-'Apostas - Grupos'!M5)=('Jogos - Grupos'!F8-'Jogos - Grupos'!G8),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="H5" s="106" t="str">
+      <c r="H5" s="106">
         <f>IF(OR('Jogos - Grupos'!F9="",'Jogos - Grupos'!G9=""),"-",IF(OR('Apostas - Grupos'!N5="",'Apostas - Grupos'!O5=""),0,IF(AND('Apostas - Grupos'!N5='Jogos - Grupos'!F9,'Apostas - Grupos'!O5='Jogos - Grupos'!G9),5,IF(OR(AND('Jogos - Grupos'!F9='Jogos - Grupos'!G9,'Apostas - Grupos'!N5='Apostas - Grupos'!O5),AND('Jogos - Grupos'!F9&gt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N5&gt;'Apostas - Grupos'!O5),AND('Jogos - Grupos'!F9&lt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N5&lt;'Apostas - Grupos'!O5)),IF(('Apostas - Grupos'!N5-'Apostas - Grupos'!O5)=('Jogos - Grupos'!F9-'Jogos - Grupos'!G9),3,2),0))))</f>
-        <v>-</v>
-      </c>
-      <c r="I5" s="106" t="str">
+        <v>0</v>
+      </c>
+      <c r="I5" s="106">
         <f>IF(OR('Jogos - Grupos'!F10="",'Jogos - Grupos'!G10=""),"-",IF(OR('Apostas - Grupos'!P5="",'Apostas - Grupos'!Q5=""),0,IF(AND('Apostas - Grupos'!P5='Jogos - Grupos'!F10,'Apostas - Grupos'!Q5='Jogos - Grupos'!G10),5,IF(OR(AND('Jogos - Grupos'!F10='Jogos - Grupos'!G10,'Apostas - Grupos'!P5='Apostas - Grupos'!Q5),AND('Jogos - Grupos'!F10&gt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P5&gt;'Apostas - Grupos'!Q5),AND('Jogos - Grupos'!F10&lt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P5&lt;'Apostas - Grupos'!Q5)),IF(('Apostas - Grupos'!P5-'Apostas - Grupos'!Q5)=('Jogos - Grupos'!F10-'Jogos - Grupos'!G10),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="J5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F11="",'Jogos - Grupos'!G11=""),"-",IF(OR('Apostas - Grupos'!R5="",'Apostas - Grupos'!S5=""),0,IF(AND('Apostas - Grupos'!R5='Jogos - Grupos'!F11,'Apostas - Grupos'!S5='Jogos - Grupos'!G11),5,IF(OR(AND('Jogos - Grupos'!F11='Jogos - Grupos'!G11,'Apostas - Grupos'!R5='Apostas - Grupos'!S5),AND('Jogos - Grupos'!F11&gt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R5&gt;'Apostas - Grupos'!S5),AND('Jogos - Grupos'!F11&lt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R5&lt;'Apostas - Grupos'!S5)),IF(('Apostas - Grupos'!R5-'Apostas - Grupos'!S5)=('Jogos - Grupos'!F11-'Jogos - Grupos'!G11),3,2),0))))</f>
@@ -13264,13 +13288,13 @@
         <f>IF(OR('Jogos - Grupos'!F14="",'Jogos - Grupos'!G14=""),"-",IF(OR('Apostas - Grupos'!X5="",'Apostas - Grupos'!Y5=""),0,IF(AND('Apostas - Grupos'!X5='Jogos - Grupos'!F14,'Apostas - Grupos'!Y5='Jogos - Grupos'!G14),5,IF(OR(AND('Jogos - Grupos'!F14='Jogos - Grupos'!G14,'Apostas - Grupos'!X5='Apostas - Grupos'!Y5),AND('Jogos - Grupos'!F14&gt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X5&gt;'Apostas - Grupos'!Y5),AND('Jogos - Grupos'!F14&lt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X5&lt;'Apostas - Grupos'!Y5)),IF(('Apostas - Grupos'!X5-'Apostas - Grupos'!Y5)=('Jogos - Grupos'!F14-'Jogos - Grupos'!G14),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="N5" s="106" t="str">
+      <c r="N5" s="106">
         <f>IF(OR('Jogos - Grupos'!F15="",'Jogos - Grupos'!G15=""),"-",IF(OR('Apostas - Grupos'!Z5="",'Apostas - Grupos'!AA5=""),0,IF(AND('Apostas - Grupos'!Z5='Jogos - Grupos'!F15,'Apostas - Grupos'!AA5='Jogos - Grupos'!G15),5,IF(OR(AND('Jogos - Grupos'!F15='Jogos - Grupos'!G15,'Apostas - Grupos'!Z5='Apostas - Grupos'!AA5),AND('Jogos - Grupos'!F15&gt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z5&gt;'Apostas - Grupos'!AA5),AND('Jogos - Grupos'!F15&lt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z5&lt;'Apostas - Grupos'!AA5)),IF(('Apostas - Grupos'!Z5-'Apostas - Grupos'!AA5)=('Jogos - Grupos'!F15-'Jogos - Grupos'!G15),3,2),0))))</f>
-        <v>-</v>
-      </c>
-      <c r="O5" s="106" t="str">
+        <v>0</v>
+      </c>
+      <c r="O5" s="106">
         <f>IF(OR('Jogos - Grupos'!F16="",'Jogos - Grupos'!G16=""),"-",IF(OR('Apostas - Grupos'!AB5="",'Apostas - Grupos'!AC5=""),0,IF(AND('Apostas - Grupos'!AB5='Jogos - Grupos'!F16,'Apostas - Grupos'!AC5='Jogos - Grupos'!G16),5,IF(OR(AND('Jogos - Grupos'!F16='Jogos - Grupos'!G16,'Apostas - Grupos'!AB5='Apostas - Grupos'!AC5),AND('Jogos - Grupos'!F16&gt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB5&gt;'Apostas - Grupos'!AC5),AND('Jogos - Grupos'!F16&lt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB5&lt;'Apostas - Grupos'!AC5)),IF(('Apostas - Grupos'!AB5-'Apostas - Grupos'!AC5)=('Jogos - Grupos'!F16-'Jogos - Grupos'!G16),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="P5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F17="",'Jogos - Grupos'!G17=""),"-",IF(OR('Apostas - Grupos'!AD5="",'Apostas - Grupos'!AE5=""),0,IF(AND('Apostas - Grupos'!AD5='Jogos - Grupos'!F17,'Apostas - Grupos'!AE5='Jogos - Grupos'!G17),5,IF(OR(AND('Jogos - Grupos'!F17='Jogos - Grupos'!G17,'Apostas - Grupos'!AD5='Apostas - Grupos'!AE5),AND('Jogos - Grupos'!F17&gt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD5&gt;'Apostas - Grupos'!AE5),AND('Jogos - Grupos'!F17&lt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD5&lt;'Apostas - Grupos'!AE5)),IF(('Apostas - Grupos'!AD5-'Apostas - Grupos'!AE5)=('Jogos - Grupos'!F17-'Jogos - Grupos'!G17),3,2),0))))</f>
@@ -13513,13 +13537,13 @@
       <c r="A6" s="82" t="s">
         <v>262</v>
       </c>
-      <c r="B6" s="108" t="str">
+      <c r="B6" s="108">
         <f>IF(OR('Jogos - Grupos'!F3="",'Jogos - Grupos'!G3=""),"-",IF(OR('Apostas - Grupos'!B6="",'Apostas - Grupos'!C6=""),0,IF(AND('Apostas - Grupos'!B6='Jogos - Grupos'!F3,'Apostas - Grupos'!C6='Jogos - Grupos'!G3),5,IF(OR(AND('Jogos - Grupos'!F3='Jogos - Grupos'!G3,'Apostas - Grupos'!B6='Apostas - Grupos'!C6),AND('Jogos - Grupos'!F3&gt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B6&gt;'Apostas - Grupos'!C6),AND('Jogos - Grupos'!F3&lt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B6&lt;'Apostas - Grupos'!C6)),IF(('Apostas - Grupos'!B6-'Apostas - Grupos'!C6)=('Jogos - Grupos'!F3-'Jogos - Grupos'!G3),3,2),0))))</f>
-        <v>-</v>
-      </c>
-      <c r="C6" s="108" t="str">
+        <v>0</v>
+      </c>
+      <c r="C6" s="108">
         <f>IF(OR('Jogos - Grupos'!F4="",'Jogos - Grupos'!G4=""),"-",IF(OR('Apostas - Grupos'!D6="",'Apostas - Grupos'!E6=""),0,IF(AND('Apostas - Grupos'!D6='Jogos - Grupos'!F4,'Apostas - Grupos'!E6='Jogos - Grupos'!G4),5,IF(OR(AND('Jogos - Grupos'!F4='Jogos - Grupos'!G4,'Apostas - Grupos'!D6='Apostas - Grupos'!E6),AND('Jogos - Grupos'!F4&gt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D6&gt;'Apostas - Grupos'!E6),AND('Jogos - Grupos'!F4&lt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D6&lt;'Apostas - Grupos'!E6)),IF(('Apostas - Grupos'!D6-'Apostas - Grupos'!E6)=('Jogos - Grupos'!F4-'Jogos - Grupos'!G4),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="D6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F5="",'Jogos - Grupos'!G5=""),"-",IF(OR('Apostas - Grupos'!F6="",'Apostas - Grupos'!G6=""),0,IF(AND('Apostas - Grupos'!F6='Jogos - Grupos'!F5,'Apostas - Grupos'!G6='Jogos - Grupos'!G5),5,IF(OR(AND('Jogos - Grupos'!F5='Jogos - Grupos'!G5,'Apostas - Grupos'!F6='Apostas - Grupos'!G6),AND('Jogos - Grupos'!F5&gt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F6&gt;'Apostas - Grupos'!G6),AND('Jogos - Grupos'!F5&lt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F6&lt;'Apostas - Grupos'!G6)),IF(('Apostas - Grupos'!F6-'Apostas - Grupos'!G6)=('Jogos - Grupos'!F5-'Jogos - Grupos'!G5),3,2),0))))</f>
@@ -13537,13 +13561,13 @@
         <f>IF(OR('Jogos - Grupos'!F8="",'Jogos - Grupos'!G8=""),"-",IF(OR('Apostas - Grupos'!L6="",'Apostas - Grupos'!M6=""),0,IF(AND('Apostas - Grupos'!L6='Jogos - Grupos'!F8,'Apostas - Grupos'!M6='Jogos - Grupos'!G8),5,IF(OR(AND('Jogos - Grupos'!F8='Jogos - Grupos'!G8,'Apostas - Grupos'!L6='Apostas - Grupos'!M6),AND('Jogos - Grupos'!F8&gt;'Jogos - Grupos'!G8,'Apostas - Grupos'!L6&gt;'Apostas - Grupos'!M6),AND('Jogos - Grupos'!F8&lt;'Jogos - Grupos'!G8,'Apostas - Grupos'!L6&lt;'Apostas - Grupos'!M6)),IF(('Apostas - Grupos'!L6-'Apostas - Grupos'!M6)=('Jogos - Grupos'!F8-'Jogos - Grupos'!G8),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="H6" s="108" t="str">
+      <c r="H6" s="108">
         <f>IF(OR('Jogos - Grupos'!F9="",'Jogos - Grupos'!G9=""),"-",IF(OR('Apostas - Grupos'!N6="",'Apostas - Grupos'!O6=""),0,IF(AND('Apostas - Grupos'!N6='Jogos - Grupos'!F9,'Apostas - Grupos'!O6='Jogos - Grupos'!G9),5,IF(OR(AND('Jogos - Grupos'!F9='Jogos - Grupos'!G9,'Apostas - Grupos'!N6='Apostas - Grupos'!O6),AND('Jogos - Grupos'!F9&gt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N6&gt;'Apostas - Grupos'!O6),AND('Jogos - Grupos'!F9&lt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N6&lt;'Apostas - Grupos'!O6)),IF(('Apostas - Grupos'!N6-'Apostas - Grupos'!O6)=('Jogos - Grupos'!F9-'Jogos - Grupos'!G9),3,2),0))))</f>
-        <v>-</v>
-      </c>
-      <c r="I6" s="108" t="str">
+        <v>0</v>
+      </c>
+      <c r="I6" s="108">
         <f>IF(OR('Jogos - Grupos'!F10="",'Jogos - Grupos'!G10=""),"-",IF(OR('Apostas - Grupos'!P6="",'Apostas - Grupos'!Q6=""),0,IF(AND('Apostas - Grupos'!P6='Jogos - Grupos'!F10,'Apostas - Grupos'!Q6='Jogos - Grupos'!G10),5,IF(OR(AND('Jogos - Grupos'!F10='Jogos - Grupos'!G10,'Apostas - Grupos'!P6='Apostas - Grupos'!Q6),AND('Jogos - Grupos'!F10&gt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P6&gt;'Apostas - Grupos'!Q6),AND('Jogos - Grupos'!F10&lt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P6&lt;'Apostas - Grupos'!Q6)),IF(('Apostas - Grupos'!P6-'Apostas - Grupos'!Q6)=('Jogos - Grupos'!F10-'Jogos - Grupos'!G10),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="J6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F11="",'Jogos - Grupos'!G11=""),"-",IF(OR('Apostas - Grupos'!R6="",'Apostas - Grupos'!S6=""),0,IF(AND('Apostas - Grupos'!R6='Jogos - Grupos'!F11,'Apostas - Grupos'!S6='Jogos - Grupos'!G11),5,IF(OR(AND('Jogos - Grupos'!F11='Jogos - Grupos'!G11,'Apostas - Grupos'!R6='Apostas - Grupos'!S6),AND('Jogos - Grupos'!F11&gt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R6&gt;'Apostas - Grupos'!S6),AND('Jogos - Grupos'!F11&lt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R6&lt;'Apostas - Grupos'!S6)),IF(('Apostas - Grupos'!R6-'Apostas - Grupos'!S6)=('Jogos - Grupos'!F11-'Jogos - Grupos'!G11),3,2),0))))</f>
@@ -13561,13 +13585,13 @@
         <f>IF(OR('Jogos - Grupos'!F14="",'Jogos - Grupos'!G14=""),"-",IF(OR('Apostas - Grupos'!X6="",'Apostas - Grupos'!Y6=""),0,IF(AND('Apostas - Grupos'!X6='Jogos - Grupos'!F14,'Apostas - Grupos'!Y6='Jogos - Grupos'!G14),5,IF(OR(AND('Jogos - Grupos'!F14='Jogos - Grupos'!G14,'Apostas - Grupos'!X6='Apostas - Grupos'!Y6),AND('Jogos - Grupos'!F14&gt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X6&gt;'Apostas - Grupos'!Y6),AND('Jogos - Grupos'!F14&lt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X6&lt;'Apostas - Grupos'!Y6)),IF(('Apostas - Grupos'!X6-'Apostas - Grupos'!Y6)=('Jogos - Grupos'!F14-'Jogos - Grupos'!G14),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="N6" s="108" t="str">
+      <c r="N6" s="108">
         <f>IF(OR('Jogos - Grupos'!F15="",'Jogos - Grupos'!G15=""),"-",IF(OR('Apostas - Grupos'!Z6="",'Apostas - Grupos'!AA6=""),0,IF(AND('Apostas - Grupos'!Z6='Jogos - Grupos'!F15,'Apostas - Grupos'!AA6='Jogos - Grupos'!G15),5,IF(OR(AND('Jogos - Grupos'!F15='Jogos - Grupos'!G15,'Apostas - Grupos'!Z6='Apostas - Grupos'!AA6),AND('Jogos - Grupos'!F15&gt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z6&gt;'Apostas - Grupos'!AA6),AND('Jogos - Grupos'!F15&lt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z6&lt;'Apostas - Grupos'!AA6)),IF(('Apostas - Grupos'!Z6-'Apostas - Grupos'!AA6)=('Jogos - Grupos'!F15-'Jogos - Grupos'!G15),3,2),0))))</f>
-        <v>-</v>
-      </c>
-      <c r="O6" s="108" t="str">
+        <v>0</v>
+      </c>
+      <c r="O6" s="108">
         <f>IF(OR('Jogos - Grupos'!F16="",'Jogos - Grupos'!G16=""),"-",IF(OR('Apostas - Grupos'!AB6="",'Apostas - Grupos'!AC6=""),0,IF(AND('Apostas - Grupos'!AB6='Jogos - Grupos'!F16,'Apostas - Grupos'!AC6='Jogos - Grupos'!G16),5,IF(OR(AND('Jogos - Grupos'!F16='Jogos - Grupos'!G16,'Apostas - Grupos'!AB6='Apostas - Grupos'!AC6),AND('Jogos - Grupos'!F16&gt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB6&gt;'Apostas - Grupos'!AC6),AND('Jogos - Grupos'!F16&lt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB6&lt;'Apostas - Grupos'!AC6)),IF(('Apostas - Grupos'!AB6-'Apostas - Grupos'!AC6)=('Jogos - Grupos'!F16-'Jogos - Grupos'!G16),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="P6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F17="",'Jogos - Grupos'!G17=""),"-",IF(OR('Apostas - Grupos'!AD6="",'Apostas - Grupos'!AE6=""),0,IF(AND('Apostas - Grupos'!AD6='Jogos - Grupos'!F17,'Apostas - Grupos'!AE6='Jogos - Grupos'!G17),5,IF(OR(AND('Jogos - Grupos'!F17='Jogos - Grupos'!G17,'Apostas - Grupos'!AD6='Apostas - Grupos'!AE6),AND('Jogos - Grupos'!F17&gt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD6&gt;'Apostas - Grupos'!AE6),AND('Jogos - Grupos'!F17&lt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD6&lt;'Apostas - Grupos'!AE6)),IF(('Apostas - Grupos'!AD6-'Apostas - Grupos'!AE6)=('Jogos - Grupos'!F17-'Jogos - Grupos'!G17),3,2),0))))</f>
@@ -13810,13 +13834,13 @@
       <c r="A7" s="81" t="s">
         <v>263</v>
       </c>
-      <c r="B7" s="106" t="str">
+      <c r="B7" s="106">
         <f>IF(OR('Jogos - Grupos'!F3="",'Jogos - Grupos'!G3=""),"-",IF(OR('Apostas - Grupos'!B7="",'Apostas - Grupos'!C7=""),0,IF(AND('Apostas - Grupos'!B7='Jogos - Grupos'!F3,'Apostas - Grupos'!C7='Jogos - Grupos'!G3),5,IF(OR(AND('Jogos - Grupos'!F3='Jogos - Grupos'!G3,'Apostas - Grupos'!B7='Apostas - Grupos'!C7),AND('Jogos - Grupos'!F3&gt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B7&gt;'Apostas - Grupos'!C7),AND('Jogos - Grupos'!F3&lt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B7&lt;'Apostas - Grupos'!C7)),IF(('Apostas - Grupos'!B7-'Apostas - Grupos'!C7)=('Jogos - Grupos'!F3-'Jogos - Grupos'!G3),3,2),0))))</f>
-        <v>-</v>
-      </c>
-      <c r="C7" s="106" t="str">
+        <v>0</v>
+      </c>
+      <c r="C7" s="106">
         <f>IF(OR('Jogos - Grupos'!F4="",'Jogos - Grupos'!G4=""),"-",IF(OR('Apostas - Grupos'!D7="",'Apostas - Grupos'!E7=""),0,IF(AND('Apostas - Grupos'!D7='Jogos - Grupos'!F4,'Apostas - Grupos'!E7='Jogos - Grupos'!G4),5,IF(OR(AND('Jogos - Grupos'!F4='Jogos - Grupos'!G4,'Apostas - Grupos'!D7='Apostas - Grupos'!E7),AND('Jogos - Grupos'!F4&gt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D7&gt;'Apostas - Grupos'!E7),AND('Jogos - Grupos'!F4&lt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D7&lt;'Apostas - Grupos'!E7)),IF(('Apostas - Grupos'!D7-'Apostas - Grupos'!E7)=('Jogos - Grupos'!F4-'Jogos - Grupos'!G4),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="D7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F5="",'Jogos - Grupos'!G5=""),"-",IF(OR('Apostas - Grupos'!F7="",'Apostas - Grupos'!G7=""),0,IF(AND('Apostas - Grupos'!F7='Jogos - Grupos'!F5,'Apostas - Grupos'!G7='Jogos - Grupos'!G5),5,IF(OR(AND('Jogos - Grupos'!F5='Jogos - Grupos'!G5,'Apostas - Grupos'!F7='Apostas - Grupos'!G7),AND('Jogos - Grupos'!F5&gt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F7&gt;'Apostas - Grupos'!G7),AND('Jogos - Grupos'!F5&lt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F7&lt;'Apostas - Grupos'!G7)),IF(('Apostas - Grupos'!F7-'Apostas - Grupos'!G7)=('Jogos - Grupos'!F5-'Jogos - Grupos'!G5),3,2),0))))</f>
@@ -13834,13 +13858,13 @@
         <f>IF(OR('Jogos - Grupos'!F8="",'Jogos - Grupos'!G8=""),"-",IF(OR('Apostas - Grupos'!L7="",'Apostas - Grupos'!M7=""),0,IF(AND('Apostas - Grupos'!L7='Jogos - Grupos'!F8,'Apostas - Grupos'!M7='Jogos - Grupos'!G8),5,IF(OR(AND('Jogos - Grupos'!F8='Jogos - Grupos'!G8,'Apostas - Grupos'!L7='Apostas - Grupos'!M7),AND('Jogos - Grupos'!F8&gt;'Jogos - Grupos'!G8,'Apostas - Grupos'!L7&gt;'Apostas - Grupos'!M7),AND('Jogos - Grupos'!F8&lt;'Jogos - Grupos'!G8,'Apostas - Grupos'!L7&lt;'Apostas - Grupos'!M7)),IF(('Apostas - Grupos'!L7-'Apostas - Grupos'!M7)=('Jogos - Grupos'!F8-'Jogos - Grupos'!G8),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="H7" s="106" t="str">
+      <c r="H7" s="106">
         <f>IF(OR('Jogos - Grupos'!F9="",'Jogos - Grupos'!G9=""),"-",IF(OR('Apostas - Grupos'!N7="",'Apostas - Grupos'!O7=""),0,IF(AND('Apostas - Grupos'!N7='Jogos - Grupos'!F9,'Apostas - Grupos'!O7='Jogos - Grupos'!G9),5,IF(OR(AND('Jogos - Grupos'!F9='Jogos - Grupos'!G9,'Apostas - Grupos'!N7='Apostas - Grupos'!O7),AND('Jogos - Grupos'!F9&gt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N7&gt;'Apostas - Grupos'!O7),AND('Jogos - Grupos'!F9&lt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N7&lt;'Apostas - Grupos'!O7)),IF(('Apostas - Grupos'!N7-'Apostas - Grupos'!O7)=('Jogos - Grupos'!F9-'Jogos - Grupos'!G9),3,2),0))))</f>
-        <v>-</v>
-      </c>
-      <c r="I7" s="106" t="str">
+        <v>0</v>
+      </c>
+      <c r="I7" s="106">
         <f>IF(OR('Jogos - Grupos'!F10="",'Jogos - Grupos'!G10=""),"-",IF(OR('Apostas - Grupos'!P7="",'Apostas - Grupos'!Q7=""),0,IF(AND('Apostas - Grupos'!P7='Jogos - Grupos'!F10,'Apostas - Grupos'!Q7='Jogos - Grupos'!G10),5,IF(OR(AND('Jogos - Grupos'!F10='Jogos - Grupos'!G10,'Apostas - Grupos'!P7='Apostas - Grupos'!Q7),AND('Jogos - Grupos'!F10&gt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P7&gt;'Apostas - Grupos'!Q7),AND('Jogos - Grupos'!F10&lt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P7&lt;'Apostas - Grupos'!Q7)),IF(('Apostas - Grupos'!P7-'Apostas - Grupos'!Q7)=('Jogos - Grupos'!F10-'Jogos - Grupos'!G10),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="J7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F11="",'Jogos - Grupos'!G11=""),"-",IF(OR('Apostas - Grupos'!R7="",'Apostas - Grupos'!S7=""),0,IF(AND('Apostas - Grupos'!R7='Jogos - Grupos'!F11,'Apostas - Grupos'!S7='Jogos - Grupos'!G11),5,IF(OR(AND('Jogos - Grupos'!F11='Jogos - Grupos'!G11,'Apostas - Grupos'!R7='Apostas - Grupos'!S7),AND('Jogos - Grupos'!F11&gt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R7&gt;'Apostas - Grupos'!S7),AND('Jogos - Grupos'!F11&lt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R7&lt;'Apostas - Grupos'!S7)),IF(('Apostas - Grupos'!R7-'Apostas - Grupos'!S7)=('Jogos - Grupos'!F11-'Jogos - Grupos'!G11),3,2),0))))</f>
@@ -13858,13 +13882,13 @@
         <f>IF(OR('Jogos - Grupos'!F14="",'Jogos - Grupos'!G14=""),"-",IF(OR('Apostas - Grupos'!X7="",'Apostas - Grupos'!Y7=""),0,IF(AND('Apostas - Grupos'!X7='Jogos - Grupos'!F14,'Apostas - Grupos'!Y7='Jogos - Grupos'!G14),5,IF(OR(AND('Jogos - Grupos'!F14='Jogos - Grupos'!G14,'Apostas - Grupos'!X7='Apostas - Grupos'!Y7),AND('Jogos - Grupos'!F14&gt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X7&gt;'Apostas - Grupos'!Y7),AND('Jogos - Grupos'!F14&lt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X7&lt;'Apostas - Grupos'!Y7)),IF(('Apostas - Grupos'!X7-'Apostas - Grupos'!Y7)=('Jogos - Grupos'!F14-'Jogos - Grupos'!G14),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="N7" s="106" t="str">
+      <c r="N7" s="106">
         <f>IF(OR('Jogos - Grupos'!F15="",'Jogos - Grupos'!G15=""),"-",IF(OR('Apostas - Grupos'!Z7="",'Apostas - Grupos'!AA7=""),0,IF(AND('Apostas - Grupos'!Z7='Jogos - Grupos'!F15,'Apostas - Grupos'!AA7='Jogos - Grupos'!G15),5,IF(OR(AND('Jogos - Grupos'!F15='Jogos - Grupos'!G15,'Apostas - Grupos'!Z7='Apostas - Grupos'!AA7),AND('Jogos - Grupos'!F15&gt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z7&gt;'Apostas - Grupos'!AA7),AND('Jogos - Grupos'!F15&lt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z7&lt;'Apostas - Grupos'!AA7)),IF(('Apostas - Grupos'!Z7-'Apostas - Grupos'!AA7)=('Jogos - Grupos'!F15-'Jogos - Grupos'!G15),3,2),0))))</f>
-        <v>-</v>
-      </c>
-      <c r="O7" s="106" t="str">
+        <v>0</v>
+      </c>
+      <c r="O7" s="106">
         <f>IF(OR('Jogos - Grupos'!F16="",'Jogos - Grupos'!G16=""),"-",IF(OR('Apostas - Grupos'!AB7="",'Apostas - Grupos'!AC7=""),0,IF(AND('Apostas - Grupos'!AB7='Jogos - Grupos'!F16,'Apostas - Grupos'!AC7='Jogos - Grupos'!G16),5,IF(OR(AND('Jogos - Grupos'!F16='Jogos - Grupos'!G16,'Apostas - Grupos'!AB7='Apostas - Grupos'!AC7),AND('Jogos - Grupos'!F16&gt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB7&gt;'Apostas - Grupos'!AC7),AND('Jogos - Grupos'!F16&lt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB7&lt;'Apostas - Grupos'!AC7)),IF(('Apostas - Grupos'!AB7-'Apostas - Grupos'!AC7)=('Jogos - Grupos'!F16-'Jogos - Grupos'!G16),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="P7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F17="",'Jogos - Grupos'!G17=""),"-",IF(OR('Apostas - Grupos'!AD7="",'Apostas - Grupos'!AE7=""),0,IF(AND('Apostas - Grupos'!AD7='Jogos - Grupos'!F17,'Apostas - Grupos'!AE7='Jogos - Grupos'!G17),5,IF(OR(AND('Jogos - Grupos'!F17='Jogos - Grupos'!G17,'Apostas - Grupos'!AD7='Apostas - Grupos'!AE7),AND('Jogos - Grupos'!F17&gt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD7&gt;'Apostas - Grupos'!AE7),AND('Jogos - Grupos'!F17&lt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD7&lt;'Apostas - Grupos'!AE7)),IF(('Apostas - Grupos'!AD7-'Apostas - Grupos'!AE7)=('Jogos - Grupos'!F17-'Jogos - Grupos'!G17),3,2),0))))</f>
@@ -14107,13 +14131,13 @@
       <c r="A8" s="82" t="s">
         <v>264</v>
       </c>
-      <c r="B8" s="108" t="str">
+      <c r="B8" s="108">
         <f>IF(OR('Jogos - Grupos'!F3="",'Jogos - Grupos'!G3=""),"-",IF(OR('Apostas - Grupos'!B8="",'Apostas - Grupos'!C8=""),0,IF(AND('Apostas - Grupos'!B8='Jogos - Grupos'!F3,'Apostas - Grupos'!C8='Jogos - Grupos'!G3),5,IF(OR(AND('Jogos - Grupos'!F3='Jogos - Grupos'!G3,'Apostas - Grupos'!B8='Apostas - Grupos'!C8),AND('Jogos - Grupos'!F3&gt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B8&gt;'Apostas - Grupos'!C8),AND('Jogos - Grupos'!F3&lt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B8&lt;'Apostas - Grupos'!C8)),IF(('Apostas - Grupos'!B8-'Apostas - Grupos'!C8)=('Jogos - Grupos'!F3-'Jogos - Grupos'!G3),3,2),0))))</f>
-        <v>-</v>
-      </c>
-      <c r="C8" s="108" t="str">
+        <v>0</v>
+      </c>
+      <c r="C8" s="108">
         <f>IF(OR('Jogos - Grupos'!F4="",'Jogos - Grupos'!G4=""),"-",IF(OR('Apostas - Grupos'!D8="",'Apostas - Grupos'!E8=""),0,IF(AND('Apostas - Grupos'!D8='Jogos - Grupos'!F4,'Apostas - Grupos'!E8='Jogos - Grupos'!G4),5,IF(OR(AND('Jogos - Grupos'!F4='Jogos - Grupos'!G4,'Apostas - Grupos'!D8='Apostas - Grupos'!E8),AND('Jogos - Grupos'!F4&gt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D8&gt;'Apostas - Grupos'!E8),AND('Jogos - Grupos'!F4&lt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D8&lt;'Apostas - Grupos'!E8)),IF(('Apostas - Grupos'!D8-'Apostas - Grupos'!E8)=('Jogos - Grupos'!F4-'Jogos - Grupos'!G4),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="D8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F5="",'Jogos - Grupos'!G5=""),"-",IF(OR('Apostas - Grupos'!F8="",'Apostas - Grupos'!G8=""),0,IF(AND('Apostas - Grupos'!F8='Jogos - Grupos'!F5,'Apostas - Grupos'!G8='Jogos - Grupos'!G5),5,IF(OR(AND('Jogos - Grupos'!F5='Jogos - Grupos'!G5,'Apostas - Grupos'!F8='Apostas - Grupos'!G8),AND('Jogos - Grupos'!F5&gt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F8&gt;'Apostas - Grupos'!G8),AND('Jogos - Grupos'!F5&lt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F8&lt;'Apostas - Grupos'!G8)),IF(('Apostas - Grupos'!F8-'Apostas - Grupos'!G8)=('Jogos - Grupos'!F5-'Jogos - Grupos'!G5),3,2),0))))</f>
@@ -14131,13 +14155,13 @@
         <f>IF(OR('Jogos - Grupos'!F8="",'Jogos - Grupos'!G8=""),"-",IF(OR('Apostas - Grupos'!L8="",'Apostas - Grupos'!M8=""),0,IF(AND('Apostas - Grupos'!L8='Jogos - Grupos'!F8,'Apostas - Grupos'!M8='Jogos - Grupos'!G8),5,IF(OR(AND('Jogos - Grupos'!F8='Jogos - Grupos'!G8,'Apostas - Grupos'!L8='Apostas - Grupos'!M8),AND('Jogos - Grupos'!F8&gt;'Jogos - Grupos'!G8,'Apostas - Grupos'!L8&gt;'Apostas - Grupos'!M8),AND('Jogos - Grupos'!F8&lt;'Jogos - Grupos'!G8,'Apostas - Grupos'!L8&lt;'Apostas - Grupos'!M8)),IF(('Apostas - Grupos'!L8-'Apostas - Grupos'!M8)=('Jogos - Grupos'!F8-'Jogos - Grupos'!G8),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="H8" s="108" t="str">
+      <c r="H8" s="108">
         <f>IF(OR('Jogos - Grupos'!F9="",'Jogos - Grupos'!G9=""),"-",IF(OR('Apostas - Grupos'!N8="",'Apostas - Grupos'!O8=""),0,IF(AND('Apostas - Grupos'!N8='Jogos - Grupos'!F9,'Apostas - Grupos'!O8='Jogos - Grupos'!G9),5,IF(OR(AND('Jogos - Grupos'!F9='Jogos - Grupos'!G9,'Apostas - Grupos'!N8='Apostas - Grupos'!O8),AND('Jogos - Grupos'!F9&gt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N8&gt;'Apostas - Grupos'!O8),AND('Jogos - Grupos'!F9&lt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N8&lt;'Apostas - Grupos'!O8)),IF(('Apostas - Grupos'!N8-'Apostas - Grupos'!O8)=('Jogos - Grupos'!F9-'Jogos - Grupos'!G9),3,2),0))))</f>
-        <v>-</v>
-      </c>
-      <c r="I8" s="108" t="str">
+        <v>0</v>
+      </c>
+      <c r="I8" s="108">
         <f>IF(OR('Jogos - Grupos'!F10="",'Jogos - Grupos'!G10=""),"-",IF(OR('Apostas - Grupos'!P8="",'Apostas - Grupos'!Q8=""),0,IF(AND('Apostas - Grupos'!P8='Jogos - Grupos'!F10,'Apostas - Grupos'!Q8='Jogos - Grupos'!G10),5,IF(OR(AND('Jogos - Grupos'!F10='Jogos - Grupos'!G10,'Apostas - Grupos'!P8='Apostas - Grupos'!Q8),AND('Jogos - Grupos'!F10&gt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P8&gt;'Apostas - Grupos'!Q8),AND('Jogos - Grupos'!F10&lt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P8&lt;'Apostas - Grupos'!Q8)),IF(('Apostas - Grupos'!P8-'Apostas - Grupos'!Q8)=('Jogos - Grupos'!F10-'Jogos - Grupos'!G10),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="J8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F11="",'Jogos - Grupos'!G11=""),"-",IF(OR('Apostas - Grupos'!R8="",'Apostas - Grupos'!S8=""),0,IF(AND('Apostas - Grupos'!R8='Jogos - Grupos'!F11,'Apostas - Grupos'!S8='Jogos - Grupos'!G11),5,IF(OR(AND('Jogos - Grupos'!F11='Jogos - Grupos'!G11,'Apostas - Grupos'!R8='Apostas - Grupos'!S8),AND('Jogos - Grupos'!F11&gt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R8&gt;'Apostas - Grupos'!S8),AND('Jogos - Grupos'!F11&lt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R8&lt;'Apostas - Grupos'!S8)),IF(('Apostas - Grupos'!R8-'Apostas - Grupos'!S8)=('Jogos - Grupos'!F11-'Jogos - Grupos'!G11),3,2),0))))</f>
@@ -14155,13 +14179,13 @@
         <f>IF(OR('Jogos - Grupos'!F14="",'Jogos - Grupos'!G14=""),"-",IF(OR('Apostas - Grupos'!X8="",'Apostas - Grupos'!Y8=""),0,IF(AND('Apostas - Grupos'!X8='Jogos - Grupos'!F14,'Apostas - Grupos'!Y8='Jogos - Grupos'!G14),5,IF(OR(AND('Jogos - Grupos'!F14='Jogos - Grupos'!G14,'Apostas - Grupos'!X8='Apostas - Grupos'!Y8),AND('Jogos - Grupos'!F14&gt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X8&gt;'Apostas - Grupos'!Y8),AND('Jogos - Grupos'!F14&lt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X8&lt;'Apostas - Grupos'!Y8)),IF(('Apostas - Grupos'!X8-'Apostas - Grupos'!Y8)=('Jogos - Grupos'!F14-'Jogos - Grupos'!G14),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="N8" s="108" t="str">
+      <c r="N8" s="108">
         <f>IF(OR('Jogos - Grupos'!F15="",'Jogos - Grupos'!G15=""),"-",IF(OR('Apostas - Grupos'!Z8="",'Apostas - Grupos'!AA8=""),0,IF(AND('Apostas - Grupos'!Z8='Jogos - Grupos'!F15,'Apostas - Grupos'!AA8='Jogos - Grupos'!G15),5,IF(OR(AND('Jogos - Grupos'!F15='Jogos - Grupos'!G15,'Apostas - Grupos'!Z8='Apostas - Grupos'!AA8),AND('Jogos - Grupos'!F15&gt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z8&gt;'Apostas - Grupos'!AA8),AND('Jogos - Grupos'!F15&lt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z8&lt;'Apostas - Grupos'!AA8)),IF(('Apostas - Grupos'!Z8-'Apostas - Grupos'!AA8)=('Jogos - Grupos'!F15-'Jogos - Grupos'!G15),3,2),0))))</f>
-        <v>-</v>
-      </c>
-      <c r="O8" s="108" t="str">
+        <v>0</v>
+      </c>
+      <c r="O8" s="108">
         <f>IF(OR('Jogos - Grupos'!F16="",'Jogos - Grupos'!G16=""),"-",IF(OR('Apostas - Grupos'!AB8="",'Apostas - Grupos'!AC8=""),0,IF(AND('Apostas - Grupos'!AB8='Jogos - Grupos'!F16,'Apostas - Grupos'!AC8='Jogos - Grupos'!G16),5,IF(OR(AND('Jogos - Grupos'!F16='Jogos - Grupos'!G16,'Apostas - Grupos'!AB8='Apostas - Grupos'!AC8),AND('Jogos - Grupos'!F16&gt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB8&gt;'Apostas - Grupos'!AC8),AND('Jogos - Grupos'!F16&lt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB8&lt;'Apostas - Grupos'!AC8)),IF(('Apostas - Grupos'!AB8-'Apostas - Grupos'!AC8)=('Jogos - Grupos'!F16-'Jogos - Grupos'!G16),3,2),0))))</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="P8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F17="",'Jogos - Grupos'!G17=""),"-",IF(OR('Apostas - Grupos'!AD8="",'Apostas - Grupos'!AE8=""),0,IF(AND('Apostas - Grupos'!AD8='Jogos - Grupos'!F17,'Apostas - Grupos'!AE8='Jogos - Grupos'!G17),5,IF(OR(AND('Jogos - Grupos'!F17='Jogos - Grupos'!G17,'Apostas - Grupos'!AD8='Apostas - Grupos'!AE8),AND('Jogos - Grupos'!F17&gt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD8&gt;'Apostas - Grupos'!AE8),AND('Jogos - Grupos'!F17&lt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD8&lt;'Apostas - Grupos'!AE8)),IF(('Apostas - Grupos'!AD8-'Apostas - Grupos'!AE8)=('Jogos - Grupos'!F17-'Jogos - Grupos'!G17),3,2),0))))</f>
@@ -14501,7 +14525,7 @@
       </c>
       <c r="C3" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A3)*('Jogos - Grupos'!$D$3:$D$74=$B3)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74&gt;'Jogos - Grupos'!$G$3:$G$74))+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A3)*('Jogos - Grupos'!$E$3:$E$74=$B3)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$G$3:$G$74&gt;'Jogos - Grupos'!$F$3:$F$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A3)*(('Jogos - Grupos'!$D$3:$D$74=$B3)+('Jogos - Grupos'!$E$3:$E$74=$B3))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
@@ -14509,23 +14533,23 @@
       </c>
       <c r="E3" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A3)*('Jogos - Grupos'!$D$3:$D$74=$B3)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A3)*('Jogos - Grupos'!$E$3:$E$74=$B3)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A3)*('Jogos - Grupos'!$D$3:$D$74=$B3)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A3)*('Jogos - Grupos'!$E$3:$E$74=$B3)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="110">
         <f t="shared" ref="G3:G50" si="0">E3-F3</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" s="8">
         <f t="shared" ref="H3:H50" si="1">3*C3+D3</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" s="110">
         <f t="shared" ref="I3:I50" si="2">H3*1000000000+(G3+200)*1000000+E3*1000+(500-K3)</f>
-        <v>200000484</v>
+        <v>3202003484</v>
       </c>
       <c r="J3" s="8">
         <f>RANK(I3,$I$3:$I$6,0)</f>
@@ -14552,15 +14576,15 @@
       </c>
       <c r="E4" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A4)*('Jogos - Grupos'!$D$3:$D$74=$B4)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A4)*('Jogos - Grupos'!$E$3:$E$74=$B4)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A4)*('Jogos - Grupos'!$D$3:$D$74=$B4)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A4)*('Jogos - Grupos'!$E$3:$E$74=$B4)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" s="110">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" si="1"/>
@@ -14568,11 +14592,11 @@
       </c>
       <c r="I4" s="110">
         <f t="shared" si="2"/>
-        <v>200000437</v>
+        <v>198001437</v>
       </c>
       <c r="J4" s="8">
         <f>RANK(I4,$I$3:$I$6,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K4" s="110">
         <v>63</v>
@@ -14599,11 +14623,11 @@
       </c>
       <c r="F5" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A5)*('Jogos - Grupos'!$D$3:$D$74=$B5)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A5)*('Jogos - Grupos'!$E$3:$E$74=$B5)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="110">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="1"/>
@@ -14611,11 +14635,11 @@
       </c>
       <c r="I5" s="110">
         <f t="shared" si="2"/>
-        <v>200000477</v>
+        <v>198000477</v>
       </c>
       <c r="J5" s="8">
         <f>RANK(I5,$I$3:$I$6,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5" s="110">
         <v>23</v>
@@ -14630,7 +14654,7 @@
       </c>
       <c r="C6" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$D$3:$D$74=$B6)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74&gt;'Jogos - Grupos'!$G$3:$G$74))+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$E$3:$E$74=$B6)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$G$3:$G$74&gt;'Jogos - Grupos'!$F$3:$F$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*(('Jogos - Grupos'!$D$3:$D$74=$B6)+('Jogos - Grupos'!$E$3:$E$74=$B6))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
@@ -14638,7 +14662,7 @@
       </c>
       <c r="E6" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$D$3:$D$74=$B6)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$E$3:$E$74=$B6)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$D$3:$D$74=$B6)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$E$3:$E$74=$B6)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
@@ -14646,19 +14670,19 @@
       </c>
       <c r="G6" s="110">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" s="110">
         <f t="shared" si="2"/>
-        <v>200000462</v>
+        <v>3202002462</v>
       </c>
       <c r="J6" s="8">
         <f>RANK(I6,$I$3:$I$6,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K6" s="110">
         <v>38</v>
@@ -14673,7 +14697,7 @@
       </c>
       <c r="C7" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A7)*('Jogos - Grupos'!$D$3:$D$74=$B7)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74&gt;'Jogos - Grupos'!$G$3:$G$74))+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A7)*('Jogos - Grupos'!$E$3:$E$74=$B7)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$G$3:$G$74&gt;'Jogos - Grupos'!$F$3:$F$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A7)*(('Jogos - Grupos'!$D$3:$D$74=$B7)+('Jogos - Grupos'!$E$3:$E$74=$B7))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
@@ -14681,27 +14705,27 @@
       </c>
       <c r="E7" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A7)*('Jogos - Grupos'!$D$3:$D$74=$B7)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A7)*('Jogos - Grupos'!$E$3:$E$74=$B7)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A7)*('Jogos - Grupos'!$D$3:$D$74=$B7)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A7)*('Jogos - Grupos'!$E$3:$E$74=$B7)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="112">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" s="112">
         <f t="shared" si="2"/>
-        <v>200000456</v>
+        <v>3201002456</v>
       </c>
       <c r="J7" s="14">
         <f>RANK(I7,$I$7:$I$10,0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K7" s="112">
         <v>44</v>
@@ -14724,15 +14748,15 @@
       </c>
       <c r="E8" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A8)*('Jogos - Grupos'!$D$3:$D$74=$B8)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A8)*('Jogos - Grupos'!$E$3:$E$74=$B8)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A8)*('Jogos - Grupos'!$D$3:$D$74=$B8)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A8)*('Jogos - Grupos'!$E$3:$E$74=$B8)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="112">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H8" s="14">
         <f t="shared" si="1"/>
@@ -14740,11 +14764,11 @@
       </c>
       <c r="I8" s="112">
         <f t="shared" si="2"/>
-        <v>200000445</v>
+        <v>199001445</v>
       </c>
       <c r="J8" s="14">
         <f>RANK(I8,$I$7:$I$10,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K8" s="112">
         <v>55</v>
@@ -14759,7 +14783,7 @@
       </c>
       <c r="C9" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A9)*('Jogos - Grupos'!$D$3:$D$74=$B9)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74&gt;'Jogos - Grupos'!$G$3:$G$74))+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A9)*('Jogos - Grupos'!$E$3:$E$74=$B9)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$G$3:$G$74&gt;'Jogos - Grupos'!$F$3:$F$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A9)*(('Jogos - Grupos'!$D$3:$D$74=$B9)+('Jogos - Grupos'!$E$3:$E$74=$B9))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
@@ -14767,7 +14791,7 @@
       </c>
       <c r="E9" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A9)*('Jogos - Grupos'!$D$3:$D$74=$B9)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A9)*('Jogos - Grupos'!$E$3:$E$74=$B9)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A9)*('Jogos - Grupos'!$D$3:$D$74=$B9)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A9)*('Jogos - Grupos'!$E$3:$E$74=$B9)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
@@ -14775,15 +14799,15 @@
       </c>
       <c r="G9" s="112">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" s="112">
         <f t="shared" si="2"/>
-        <v>200000462</v>
+        <v>3201001462</v>
       </c>
       <c r="J9" s="14">
         <f>RANK(I9,$I$7:$I$10,0)</f>
@@ -14814,11 +14838,11 @@
       </c>
       <c r="F10" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A10)*('Jogos - Grupos'!$D$3:$D$74=$B10)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A10)*('Jogos - Grupos'!$E$3:$E$74=$B10)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="112">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H10" s="14">
         <f t="shared" si="1"/>
@@ -14826,11 +14850,11 @@
       </c>
       <c r="I10" s="112">
         <f t="shared" si="2"/>
-        <v>200000480</v>
+        <v>199000480</v>
       </c>
       <c r="J10" s="14">
         <f>RANK(I10,$I$7:$I$10,0)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K10" s="112">
         <v>20</v>
@@ -14845,7 +14869,7 @@
       </c>
       <c r="C11" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$D$3:$D$74=$B11)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74&gt;'Jogos - Grupos'!$G$3:$G$74))+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$E$3:$E$74=$B11)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$G$3:$G$74&gt;'Jogos - Grupos'!$F$3:$F$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*(('Jogos - Grupos'!$D$3:$D$74=$B11)+('Jogos - Grupos'!$E$3:$E$74=$B11))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
@@ -14853,23 +14877,23 @@
       </c>
       <c r="E11" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$D$3:$D$74=$B11)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$E$3:$E$74=$B11)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$D$3:$D$74=$B11)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$E$3:$E$74=$B11)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="114">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="19">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" s="114">
         <f t="shared" si="2"/>
-        <v>200000495</v>
+        <v>3201003495</v>
       </c>
       <c r="J11" s="19">
         <f>RANK(I11,$I$11:$I$14,0)</f>
@@ -14896,15 +14920,15 @@
       </c>
       <c r="E12" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A12)*('Jogos - Grupos'!$D$3:$D$74=$B12)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A12)*('Jogos - Grupos'!$E$3:$E$74=$B12)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A12)*('Jogos - Grupos'!$D$3:$D$74=$B12)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A12)*('Jogos - Grupos'!$E$3:$E$74=$B12)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G12" s="114">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H12" s="19">
         <f t="shared" si="1"/>
@@ -14912,11 +14936,11 @@
       </c>
       <c r="I12" s="114">
         <f t="shared" si="2"/>
-        <v>200000486</v>
+        <v>199002486</v>
       </c>
       <c r="J12" s="19">
         <f>RANK(I12,$I$11:$I$14,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12" s="114">
         <v>14</v>
@@ -14931,7 +14955,7 @@
       </c>
       <c r="C13" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A13)*('Jogos - Grupos'!$D$3:$D$74=$B13)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74&gt;'Jogos - Grupos'!$G$3:$G$74))+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A13)*('Jogos - Grupos'!$E$3:$E$74=$B13)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$G$3:$G$74&gt;'Jogos - Grupos'!$F$3:$F$74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A13)*(('Jogos - Grupos'!$D$3:$D$74=$B13)+('Jogos - Grupos'!$E$3:$E$74=$B13))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
@@ -14939,7 +14963,7 @@
       </c>
       <c r="E13" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A13)*('Jogos - Grupos'!$D$3:$D$74=$B13)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A13)*('Jogos - Grupos'!$E$3:$E$74=$B13)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A13)*('Jogos - Grupos'!$D$3:$D$74=$B13)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A13)*('Jogos - Grupos'!$E$3:$E$74=$B13)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
@@ -14947,19 +14971,19 @@
       </c>
       <c r="G13" s="114">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="19">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" s="114">
         <f t="shared" si="2"/>
-        <v>200000414</v>
+        <v>3201001414</v>
       </c>
       <c r="J13" s="19">
         <f>RANK(I13,$I$11:$I$14,0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K13" s="114">
         <v>86</v>
@@ -14986,11 +15010,11 @@
       </c>
       <c r="F14" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A14)*('Jogos - Grupos'!$D$3:$D$74=$B14)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A14)*('Jogos - Grupos'!$E$3:$E$74=$B14)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="114">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H14" s="19">
         <f t="shared" si="1"/>
@@ -14998,11 +15022,11 @@
       </c>
       <c r="I14" s="114">
         <f t="shared" si="2"/>
-        <v>200000473</v>
+        <v>199000473</v>
       </c>
       <c r="J14" s="19">
         <f>RANK(I14,$I$11:$I$14,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" s="114">
         <v>27</v>
@@ -16583,15 +16607,15 @@
       </c>
       <c r="C53" s="135" t="str">
         <f>IFERROR(INDEX($B$3:$B$6,MATCH(2,$J$3:$J$6,0)),"?")</f>
-        <v>Coreia do Sul</v>
+        <v>Tchequia</v>
       </c>
       <c r="D53" s="135" t="str">
         <f>IFERROR(INDEX($B$3:$B$6,MATCH(3,$J$3:$J$6,0)),"?")</f>
-        <v>Tchequia</v>
+        <v>Africa do Sul</v>
       </c>
       <c r="E53" s="135" t="str">
         <f>IFERROR(INDEX($B$3:$B$6,MATCH(4,$J$3:$J$6,0)),"?")</f>
-        <v>Africa do Sul</v>
+        <v>Coreia do Sul</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
@@ -16600,7 +16624,7 @@
       </c>
       <c r="B54" s="135" t="str">
         <f>IFERROR(INDEX($B$7:$B$10,MATCH(1,$J$7:$J$10,0)),"?")</f>
-        <v>Suica</v>
+        <v>Canada</v>
       </c>
       <c r="C54" s="135" t="str">
         <f>IFERROR(INDEX($B$7:$B$10,MATCH(2,$J$7:$J$10,0)),"?")</f>
@@ -16608,11 +16632,11 @@
       </c>
       <c r="D54" s="135" t="str">
         <f>IFERROR(INDEX($B$7:$B$10,MATCH(3,$J$7:$J$10,0)),"?")</f>
-        <v>Canada</v>
+        <v>Bosnia e Herzegovina</v>
       </c>
       <c r="E54" s="135" t="str">
         <f>IFERROR(INDEX($B$7:$B$10,MATCH(4,$J$7:$J$10,0)),"?")</f>
-        <v>Bosnia e Herzegovina</v>
+        <v>Suica</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
@@ -16625,15 +16649,15 @@
       </c>
       <c r="C55" s="135" t="str">
         <f>IFERROR(INDEX($B$11:$B$14,MATCH(2,$J$11:$J$14,0)),"?")</f>
-        <v>Marrocos</v>
+        <v>Haiti</v>
       </c>
       <c r="D55" s="135" t="str">
         <f>IFERROR(INDEX($B$11:$B$14,MATCH(3,$J$11:$J$14,0)),"?")</f>
-        <v>Escocia</v>
+        <v>Marrocos</v>
       </c>
       <c r="E55" s="135" t="str">
         <f>IFERROR(INDEX($B$11:$B$14,MATCH(4,$J$11:$J$14,0)),"?")</f>
-        <v>Haiti</v>
+        <v>Escocia</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -16845,15 +16869,15 @@
       </c>
       <c r="B68" s="149" t="str">
         <f>IFERROR(INDEX($B$3:$B$6,MATCH(3,$J$3:$J$6,0)),"?")</f>
-        <v>Tchequia</v>
+        <v>Africa do Sul</v>
       </c>
       <c r="C68" s="149">
         <f>IFERROR(INDEX($I$3:$I$6,MATCH(3,$J$3:$J$6,0)),0)</f>
-        <v>200000462</v>
+        <v>198001437</v>
       </c>
       <c r="D68" s="150">
         <f t="shared" ref="D68:D79" si="3">RANK(C68,$C$68:$C$79,0)</f>
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -16862,15 +16886,15 @@
       </c>
       <c r="B69" s="149" t="str">
         <f>IFERROR(INDEX($B$7:$B$10,MATCH(3,$J$7:$J$10,0)),"?")</f>
-        <v>Canada</v>
+        <v>Bosnia e Herzegovina</v>
       </c>
       <c r="C69" s="149">
         <f>IFERROR(INDEX($I$7:$I$10,MATCH(3,$J$7:$J$10,0)),0)</f>
-        <v>200000456</v>
+        <v>199001445</v>
       </c>
       <c r="D69" s="150">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -16879,15 +16903,15 @@
       </c>
       <c r="B70" s="149" t="str">
         <f>IFERROR(INDEX($B$11:$B$14,MATCH(3,$J$11:$J$14,0)),"?")</f>
-        <v>Escocia</v>
+        <v>Marrocos</v>
       </c>
       <c r="C70" s="149">
         <f>IFERROR(INDEX($I$11:$I$14,MATCH(3,$J$11:$J$14,0)),0)</f>
-        <v>200000473</v>
+        <v>199002486</v>
       </c>
       <c r="D70" s="150">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -16904,7 +16928,7 @@
       </c>
       <c r="D71" s="150">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -16921,7 +16945,7 @@
       </c>
       <c r="D72" s="150">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -16955,7 +16979,7 @@
       </c>
       <c r="D74" s="150">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -16972,7 +16996,7 @@
       </c>
       <c r="D75" s="150">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -16989,7 +17013,7 @@
       </c>
       <c r="D76" s="150">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -17006,7 +17030,7 @@
       </c>
       <c r="D77" s="150">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -17023,7 +17047,7 @@
       </c>
       <c r="D78" s="150">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -17040,7 +17064,7 @@
       </c>
       <c r="D79" s="150">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
@@ -17066,7 +17090,7 @@
       </c>
       <c r="B83" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(2,$D$68:$D$79,0)),"?")</f>
-        <v>Escocia</v>
+        <v>Noruega</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
@@ -17075,7 +17099,7 @@
       </c>
       <c r="B84" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(3,$D$68:$D$79,0)),"?")</f>
-        <v>Noruega</v>
+        <v>Argelia</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
@@ -17084,7 +17108,7 @@
       </c>
       <c r="B85" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(4,$D$68:$D$79,0)),"?")</f>
-        <v>Argelia</v>
+        <v>Turquia</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
@@ -17093,7 +17117,7 @@
       </c>
       <c r="B86" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(5,$D$68:$D$79,0)),"?")</f>
-        <v>Turquia</v>
+        <v>?</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
@@ -17102,7 +17126,7 @@
       </c>
       <c r="B87" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(6,$D$68:$D$79,0)),"?")</f>
-        <v>?</v>
+        <v>Costa do Marfim</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
@@ -17111,7 +17135,7 @@
       </c>
       <c r="B88" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(7,$D$68:$D$79,0)),"?")</f>
-        <v>Tchequia</v>
+        <v>Gana</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
@@ -17120,7 +17144,7 @@
       </c>
       <c r="B89" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(8,$D$68:$D$79,0)),"?")</f>
-        <v>Costa do Marfim</v>
+        <v>Arabia Saudita</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
@@ -17129,7 +17153,7 @@
       </c>
       <c r="B92" s="166" t="str">
         <f>IF(D68&lt;=8,"A","")&amp;IF(D69&lt;=8,"B","")&amp;IF(D70&lt;=8,"C","")&amp;IF(D71&lt;=8,"D","")&amp;IF(D72&lt;=8,"E","")&amp;IF(D73&lt;=8,"F","")&amp;IF(D74&lt;=8,"G","")&amp;IF(D75&lt;=8,"H","")&amp;IF(D76&lt;=8,"I","")&amp;IF(D77&lt;=8,"J","")&amp;IF(D78&lt;=8,"K","")&amp;IF(D79&lt;=8,"L","")</f>
-        <v>ACDEFGIJ</v>
+        <v>DEFGHIJKL</v>
       </c>
     </row>
   </sheetData>
@@ -43638,7 +43662,7 @@
       </c>
       <c r="D4" s="175" t="str">
         <f>IFERROR('Classif - Grupos'!C53,"Aguardando")</f>
-        <v>Coreia do Sul</v>
+        <v>Tchequia</v>
       </c>
       <c r="E4" s="175" t="str">
         <f>IFERROR('Classif - Grupos'!C54,"Aguardando")</f>
@@ -43672,7 +43696,7 @@
       </c>
       <c r="E5" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,5,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Turquia</v>
+        <v>Aguardando</v>
       </c>
       <c r="F5" s="249"/>
       <c r="G5" s="249"/>
@@ -43702,7 +43726,7 @@
       </c>
       <c r="E6" s="175" t="str">
         <f>IFERROR('Classif - Grupos'!C55,"Aguardando")</f>
-        <v>Marrocos</v>
+        <v>Haiti</v>
       </c>
       <c r="F6" s="249"/>
       <c r="G6" s="249"/>
@@ -43762,7 +43786,7 @@
       </c>
       <c r="E8" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,7,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Suecia</v>
+        <v>Aguardando</v>
       </c>
       <c r="F8" s="249"/>
       <c r="G8" s="249"/>
@@ -43822,7 +43846,7 @@
       </c>
       <c r="E10" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,2,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Escocia</v>
+        <v>Aguardando</v>
       </c>
       <c r="F10" s="249"/>
       <c r="G10" s="249"/>
@@ -43852,7 +43876,7 @@
       </c>
       <c r="E11" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,9,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Noruega</v>
+        <v>Aguardando</v>
       </c>
       <c r="F11" s="249"/>
       <c r="G11" s="249"/>
@@ -43882,7 +43906,7 @@
       </c>
       <c r="E12" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,4,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Argelia</v>
+        <v>Aguardando</v>
       </c>
       <c r="F12" s="249"/>
       <c r="G12" s="249"/>
@@ -43912,7 +43936,7 @@
       </c>
       <c r="E13" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,6,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Tchequia</v>
+        <v>Aguardando</v>
       </c>
       <c r="F13" s="249"/>
       <c r="G13" s="249"/>
@@ -43998,11 +44022,11 @@
       </c>
       <c r="D16" s="175" t="str">
         <f>IFERROR('Classif - Grupos'!B54,"Aguardando")</f>
-        <v>Suica</v>
+        <v>Canada</v>
       </c>
       <c r="E16" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,3,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Egito</v>
+        <v>Aguardando</v>
       </c>
       <c r="F16" s="249"/>
       <c r="G16" s="249"/>
@@ -44062,7 +44086,7 @@
       </c>
       <c r="E18" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,8,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Costa do Marfim</v>
+        <v>Aguardando</v>
       </c>
       <c r="F18" s="249"/>
       <c r="G18" s="249"/>

--- a/gabarito/Bolao_Copa2026_TurimMFO_Master - Copia.xlsx
+++ b/gabarito/Bolao_Copa2026_TurimMFO_Master - Copia.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5485572D-86F7-44D9-A3AC-1FB006CB9578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regras" sheetId="1" r:id="rId1"/>
@@ -4924,73 +4924,67 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="46" fillId="41" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="47" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="41" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="42" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="44" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4999,13 +4993,22 @@
     <xf numFmtId="164" fontId="46" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5021,9 +5024,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5784,7 +5784,7 @@
       <c r="BM1" s="253"/>
     </row>
     <row r="2" spans="1:65" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>1028</v>
       </c>
       <c r="B2" s="253"/>
@@ -5920,67 +5920,67 @@
         <v>994</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="270" t="s">
+      <c r="AH3" s="273" t="s">
         <v>996</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="270" t="s">
+      <c r="AJ3" s="273" t="s">
         <v>998</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="270" t="s">
+      <c r="AL3" s="273" t="s">
         <v>1000</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="270" t="s">
+      <c r="AN3" s="273" t="s">
         <v>1002</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="270" t="s">
+      <c r="AP3" s="273" t="s">
         <v>1004</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="270" t="s">
+      <c r="AR3" s="273" t="s">
         <v>1006</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="270" t="s">
+      <c r="AT3" s="273" t="s">
         <v>1008</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="270" t="s">
+      <c r="AV3" s="273" t="s">
         <v>1010</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="274" t="s">
+      <c r="AX3" s="275" t="s">
         <v>1012</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="274" t="s">
+      <c r="AZ3" s="275" t="s">
         <v>1014</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="274" t="s">
+      <c r="BB3" s="275" t="s">
         <v>1016</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="274" t="s">
+      <c r="BD3" s="275" t="s">
         <v>1018</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="277" t="s">
+      <c r="BF3" s="281" t="s">
         <v>1020</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="277" t="s">
+      <c r="BH3" s="281" t="s">
         <v>1022</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="273" t="s">
+      <c r="BJ3" s="279" t="s">
         <v>1024</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="275" t="s">
+      <c r="BL3" s="280" t="s">
         <v>1026</v>
       </c>
       <c r="BM3" s="253"/>
@@ -5989,131 +5989,131 @@
       <c r="A4" s="210" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="272">
+      <c r="B4" s="270">
         <v>46201</v>
       </c>
       <c r="C4" s="253"/>
-      <c r="D4" s="272">
+      <c r="D4" s="270">
         <v>46202</v>
       </c>
       <c r="E4" s="253"/>
-      <c r="F4" s="272">
+      <c r="F4" s="270">
         <v>46202</v>
       </c>
       <c r="G4" s="253"/>
-      <c r="H4" s="272">
+      <c r="H4" s="270">
         <v>46202</v>
       </c>
       <c r="I4" s="253"/>
-      <c r="J4" s="272">
+      <c r="J4" s="270">
         <v>46203</v>
       </c>
       <c r="K4" s="253"/>
-      <c r="L4" s="272">
+      <c r="L4" s="270">
         <v>46203</v>
       </c>
       <c r="M4" s="253"/>
-      <c r="N4" s="272">
+      <c r="N4" s="270">
         <v>46203</v>
       </c>
       <c r="O4" s="253"/>
-      <c r="P4" s="272">
+      <c r="P4" s="270">
         <v>46204</v>
       </c>
       <c r="Q4" s="253"/>
-      <c r="R4" s="272">
+      <c r="R4" s="270">
         <v>46204</v>
       </c>
       <c r="S4" s="253"/>
-      <c r="T4" s="272">
+      <c r="T4" s="270">
         <v>46204</v>
       </c>
       <c r="U4" s="253"/>
-      <c r="V4" s="272">
+      <c r="V4" s="270">
         <v>46205</v>
       </c>
       <c r="W4" s="253"/>
-      <c r="X4" s="272">
+      <c r="X4" s="270">
         <v>46205</v>
       </c>
       <c r="Y4" s="253"/>
-      <c r="Z4" s="272">
+      <c r="Z4" s="270">
         <v>46205</v>
       </c>
       <c r="AA4" s="253"/>
-      <c r="AB4" s="272">
+      <c r="AB4" s="270">
         <v>46206</v>
       </c>
       <c r="AC4" s="253"/>
-      <c r="AD4" s="272">
+      <c r="AD4" s="270">
         <v>46206</v>
       </c>
       <c r="AE4" s="253"/>
-      <c r="AF4" s="272">
+      <c r="AF4" s="270">
         <v>46206</v>
       </c>
       <c r="AG4" s="253"/>
-      <c r="AH4" s="276">
+      <c r="AH4" s="274">
         <v>46207</v>
       </c>
       <c r="AI4" s="253"/>
-      <c r="AJ4" s="276">
+      <c r="AJ4" s="274">
         <v>46207</v>
       </c>
       <c r="AK4" s="253"/>
-      <c r="AL4" s="276">
+      <c r="AL4" s="274">
         <v>46208</v>
       </c>
       <c r="AM4" s="253"/>
-      <c r="AN4" s="276">
+      <c r="AN4" s="274">
         <v>46208</v>
       </c>
       <c r="AO4" s="253"/>
-      <c r="AP4" s="276">
+      <c r="AP4" s="274">
         <v>46209</v>
       </c>
       <c r="AQ4" s="253"/>
-      <c r="AR4" s="276">
+      <c r="AR4" s="274">
         <v>46209</v>
       </c>
       <c r="AS4" s="253"/>
-      <c r="AT4" s="276">
+      <c r="AT4" s="274">
         <v>46210</v>
       </c>
       <c r="AU4" s="253"/>
-      <c r="AV4" s="276">
+      <c r="AV4" s="274">
         <v>46210</v>
       </c>
       <c r="AW4" s="253"/>
-      <c r="AX4" s="278">
+      <c r="AX4" s="272">
         <v>46212</v>
       </c>
       <c r="AY4" s="253"/>
-      <c r="AZ4" s="278">
+      <c r="AZ4" s="272">
         <v>46213</v>
       </c>
       <c r="BA4" s="253"/>
-      <c r="BB4" s="278">
+      <c r="BB4" s="272">
         <v>46214</v>
       </c>
       <c r="BC4" s="253"/>
-      <c r="BD4" s="278">
+      <c r="BD4" s="272">
         <v>46214</v>
       </c>
       <c r="BE4" s="253"/>
-      <c r="BF4" s="279">
+      <c r="BF4" s="277">
         <v>46217</v>
       </c>
       <c r="BG4" s="253"/>
-      <c r="BH4" s="279">
+      <c r="BH4" s="277">
         <v>46218</v>
       </c>
       <c r="BI4" s="253"/>
-      <c r="BJ4" s="281">
+      <c r="BJ4" s="276">
         <v>46221</v>
       </c>
       <c r="BK4" s="253"/>
-      <c r="BL4" s="280">
+      <c r="BL4" s="278">
         <v>46222</v>
       </c>
       <c r="BM4" s="253"/>
@@ -7568,19 +7568,43 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="AX4:AY4"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AR4:AS4"/>
-    <mergeCell ref="AV4:AW4"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="A2:BM2"/>
+    <mergeCell ref="AR3:AS3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="AD4:AE4"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="BJ3:BK3"/>
+    <mergeCell ref="AZ3:BA3"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="BL3:BM3"/>
+    <mergeCell ref="AJ4:AK4"/>
+    <mergeCell ref="AL4:AM4"/>
+    <mergeCell ref="BF3:BG3"/>
+    <mergeCell ref="BH3:BI3"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="A1:BM1"/>
+    <mergeCell ref="AT4:AU4"/>
+    <mergeCell ref="AZ4:BA4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="BB4:BC4"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="BD4:BE4"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="BF4:BG4"/>
+    <mergeCell ref="BL4:BM4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="BH4:BI4"/>
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AP4:AQ4"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="AP3:AQ3"/>
     <mergeCell ref="BB3:BC3"/>
@@ -7597,43 +7621,19 @@
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="AV3:AW3"/>
     <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="BH4:BI4"/>
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AP4:AQ4"/>
-    <mergeCell ref="A1:BM1"/>
-    <mergeCell ref="AT4:AU4"/>
-    <mergeCell ref="AZ4:BA4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="BB4:BC4"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="BD4:BE4"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="BF4:BG4"/>
-    <mergeCell ref="BL4:BM4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="A2:BM2"/>
-    <mergeCell ref="AR3:AS3"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="AD4:AE4"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="BJ3:BK3"/>
-    <mergeCell ref="AZ3:BA3"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="BL3:BM3"/>
-    <mergeCell ref="AJ4:AK4"/>
-    <mergeCell ref="AL4:AM4"/>
-    <mergeCell ref="BF3:BG3"/>
-    <mergeCell ref="BH3:BI3"/>
-    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="AX4:AY4"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AR4:AS4"/>
+    <mergeCell ref="AV4:AW4"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="X3:Y3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7691,7 +7691,7 @@
       <c r="AH1" s="253"/>
     </row>
     <row r="2" spans="1:34" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>1032</v>
       </c>
       <c r="B2" s="253"/>
@@ -8857,7 +8857,7 @@
       <c r="J1" s="253"/>
     </row>
     <row r="2" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>1079</v>
       </c>
       <c r="B2" s="253"/>
@@ -8871,49 +8871,49 @@
       <c r="J2" s="253"/>
     </row>
     <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="289" t="s">
+      <c r="A4" s="284" t="s">
         <v>1080</v>
       </c>
       <c r="B4" s="253"/>
-      <c r="C4" s="289" t="s">
+      <c r="C4" s="284" t="s">
         <v>1081</v>
       </c>
       <c r="D4" s="253"/>
-      <c r="E4" s="289" t="s">
+      <c r="E4" s="284" t="s">
         <v>1082</v>
       </c>
       <c r="F4" s="253"/>
-      <c r="G4" s="289" t="s">
+      <c r="G4" s="284" t="s">
         <v>1083</v>
       </c>
       <c r="H4" s="253"/>
-      <c r="I4" s="289" t="s">
+      <c r="I4" s="284" t="s">
         <v>1084</v>
       </c>
       <c r="J4" s="253"/>
     </row>
     <row r="5" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="285" t="str">
+      <c r="A5" s="286" t="str">
         <f>IFERROR(INDEX(Ranking!$I$4:$I$7,MATCH(1,Ranking!$P$4:$P$7,0)),"?")</f>
         <v>Pedro Brandao</v>
       </c>
       <c r="B5" s="253"/>
-      <c r="C5" s="284">
+      <c r="C5" s="285">
         <f>IFERROR(MAX(Ranking!$M$4:$M$7),0)</f>
         <v>0</v>
       </c>
       <c r="D5" s="253"/>
-      <c r="E5" s="287">
+      <c r="E5" s="288">
         <f>COUNTIF('Jogos - Grupos'!H3:H74,"Finalizado")</f>
         <v>6</v>
       </c>
       <c r="F5" s="253"/>
-      <c r="G5" s="286">
+      <c r="G5" s="287">
         <f>COUNTIF('Mata-Mata - Jogos'!I4:I35,"Finalizado")</f>
         <v>0</v>
       </c>
       <c r="H5" s="253"/>
-      <c r="I5" s="288" t="s">
+      <c r="I5" s="289" t="s">
         <v>1077</v>
       </c>
       <c r="J5" s="253"/>
@@ -9064,6 +9064,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="I5:J5"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="A1:J1"/>
@@ -9071,11 +9076,6 @@
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="I5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10985,7 +10985,7 @@
       <c r="EO1" s="253"/>
     </row>
     <row r="2" spans="1:145" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>186</v>
       </c>
       <c r="B2" s="253"/>
@@ -11137,219 +11137,219 @@
       <c r="A3" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="B3" s="263" t="s">
+      <c r="B3" s="256" t="s">
         <v>188</v>
       </c>
       <c r="C3" s="253"/>
-      <c r="D3" s="263" t="s">
+      <c r="D3" s="256" t="s">
         <v>189</v>
       </c>
       <c r="E3" s="253"/>
-      <c r="F3" s="263" t="s">
+      <c r="F3" s="256" t="s">
         <v>190</v>
       </c>
       <c r="G3" s="253"/>
-      <c r="H3" s="263" t="s">
+      <c r="H3" s="256" t="s">
         <v>191</v>
       </c>
       <c r="I3" s="253"/>
-      <c r="J3" s="263" t="s">
+      <c r="J3" s="256" t="s">
         <v>192</v>
       </c>
       <c r="K3" s="253"/>
-      <c r="L3" s="263" t="s">
+      <c r="L3" s="256" t="s">
         <v>193</v>
       </c>
       <c r="M3" s="253"/>
-      <c r="N3" s="264" t="s">
+      <c r="N3" s="260" t="s">
         <v>194</v>
       </c>
       <c r="O3" s="253"/>
-      <c r="P3" s="264" t="s">
+      <c r="P3" s="260" t="s">
         <v>195</v>
       </c>
       <c r="Q3" s="253"/>
-      <c r="R3" s="264" t="s">
+      <c r="R3" s="260" t="s">
         <v>196</v>
       </c>
       <c r="S3" s="253"/>
-      <c r="T3" s="264" t="s">
+      <c r="T3" s="260" t="s">
         <v>197</v>
       </c>
       <c r="U3" s="253"/>
-      <c r="V3" s="264" t="s">
+      <c r="V3" s="260" t="s">
         <v>198</v>
       </c>
       <c r="W3" s="253"/>
-      <c r="X3" s="264" t="s">
+      <c r="X3" s="260" t="s">
         <v>199</v>
       </c>
       <c r="Y3" s="253"/>
-      <c r="Z3" s="259" t="s">
+      <c r="Z3" s="261" t="s">
         <v>200</v>
       </c>
       <c r="AA3" s="253"/>
-      <c r="AB3" s="259" t="s">
+      <c r="AB3" s="261" t="s">
         <v>201</v>
       </c>
       <c r="AC3" s="253"/>
-      <c r="AD3" s="259" t="s">
+      <c r="AD3" s="261" t="s">
         <v>202</v>
       </c>
       <c r="AE3" s="253"/>
-      <c r="AF3" s="259" t="s">
+      <c r="AF3" s="261" t="s">
         <v>203</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="259" t="s">
+      <c r="AH3" s="261" t="s">
         <v>204</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="259" t="s">
+      <c r="AJ3" s="261" t="s">
         <v>205</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="260" t="s">
+      <c r="AL3" s="257" t="s">
         <v>206</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="260" t="s">
+      <c r="AN3" s="257" t="s">
         <v>207</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="260" t="s">
+      <c r="AP3" s="257" t="s">
         <v>208</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="260" t="s">
+      <c r="AR3" s="257" t="s">
         <v>209</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="260" t="s">
+      <c r="AT3" s="257" t="s">
         <v>210</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="260" t="s">
+      <c r="AV3" s="257" t="s">
         <v>211</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="265" t="s">
+      <c r="AX3" s="258" t="s">
         <v>212</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="265" t="s">
+      <c r="AZ3" s="258" t="s">
         <v>213</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="265" t="s">
+      <c r="BB3" s="258" t="s">
         <v>214</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="265" t="s">
+      <c r="BD3" s="258" t="s">
         <v>215</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="265" t="s">
+      <c r="BF3" s="258" t="s">
         <v>216</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="265" t="s">
+      <c r="BH3" s="258" t="s">
         <v>217</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="266" t="s">
+      <c r="BJ3" s="262" t="s">
         <v>218</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="266" t="s">
+      <c r="BL3" s="262" t="s">
         <v>219</v>
       </c>
       <c r="BM3" s="253"/>
-      <c r="BN3" s="266" t="s">
+      <c r="BN3" s="262" t="s">
         <v>220</v>
       </c>
       <c r="BO3" s="253"/>
-      <c r="BP3" s="266" t="s">
+      <c r="BP3" s="262" t="s">
         <v>221</v>
       </c>
       <c r="BQ3" s="253"/>
-      <c r="BR3" s="266" t="s">
+      <c r="BR3" s="262" t="s">
         <v>222</v>
       </c>
       <c r="BS3" s="253"/>
-      <c r="BT3" s="266" t="s">
+      <c r="BT3" s="262" t="s">
         <v>223</v>
       </c>
       <c r="BU3" s="253"/>
-      <c r="BV3" s="256" t="s">
+      <c r="BV3" s="263" t="s">
         <v>224</v>
       </c>
       <c r="BW3" s="253"/>
-      <c r="BX3" s="256" t="s">
+      <c r="BX3" s="263" t="s">
         <v>225</v>
       </c>
       <c r="BY3" s="253"/>
-      <c r="BZ3" s="256" t="s">
+      <c r="BZ3" s="263" t="s">
         <v>226</v>
       </c>
       <c r="CA3" s="253"/>
-      <c r="CB3" s="256" t="s">
+      <c r="CB3" s="263" t="s">
         <v>227</v>
       </c>
       <c r="CC3" s="253"/>
-      <c r="CD3" s="256" t="s">
+      <c r="CD3" s="263" t="s">
         <v>228</v>
       </c>
       <c r="CE3" s="253"/>
-      <c r="CF3" s="256" t="s">
+      <c r="CF3" s="263" t="s">
         <v>229</v>
       </c>
       <c r="CG3" s="253"/>
-      <c r="CH3" s="257" t="s">
+      <c r="CH3" s="259" t="s">
         <v>230</v>
       </c>
       <c r="CI3" s="253"/>
-      <c r="CJ3" s="257" t="s">
+      <c r="CJ3" s="259" t="s">
         <v>231</v>
       </c>
       <c r="CK3" s="253"/>
-      <c r="CL3" s="257" t="s">
+      <c r="CL3" s="259" t="s">
         <v>232</v>
       </c>
       <c r="CM3" s="253"/>
-      <c r="CN3" s="257" t="s">
+      <c r="CN3" s="259" t="s">
         <v>233</v>
       </c>
       <c r="CO3" s="253"/>
-      <c r="CP3" s="257" t="s">
+      <c r="CP3" s="259" t="s">
         <v>234</v>
       </c>
       <c r="CQ3" s="253"/>
-      <c r="CR3" s="257" t="s">
+      <c r="CR3" s="259" t="s">
         <v>235</v>
       </c>
       <c r="CS3" s="253"/>
-      <c r="CT3" s="258" t="s">
+      <c r="CT3" s="265" t="s">
         <v>236</v>
       </c>
       <c r="CU3" s="253"/>
-      <c r="CV3" s="258" t="s">
+      <c r="CV3" s="265" t="s">
         <v>237</v>
       </c>
       <c r="CW3" s="253"/>
-      <c r="CX3" s="258" t="s">
+      <c r="CX3" s="265" t="s">
         <v>238</v>
       </c>
       <c r="CY3" s="253"/>
-      <c r="CZ3" s="258" t="s">
+      <c r="CZ3" s="265" t="s">
         <v>239</v>
       </c>
       <c r="DA3" s="253"/>
-      <c r="DB3" s="258" t="s">
+      <c r="DB3" s="265" t="s">
         <v>240</v>
       </c>
       <c r="DC3" s="253"/>
-      <c r="DD3" s="258" t="s">
+      <c r="DD3" s="265" t="s">
         <v>241</v>
       </c>
       <c r="DE3" s="253"/>
@@ -11377,51 +11377,51 @@
         <v>247</v>
       </c>
       <c r="DQ3" s="253"/>
-      <c r="DR3" s="268" t="s">
+      <c r="DR3" s="266" t="s">
         <v>248</v>
       </c>
       <c r="DS3" s="253"/>
-      <c r="DT3" s="268" t="s">
+      <c r="DT3" s="266" t="s">
         <v>249</v>
       </c>
       <c r="DU3" s="253"/>
-      <c r="DV3" s="268" t="s">
+      <c r="DV3" s="266" t="s">
         <v>250</v>
       </c>
       <c r="DW3" s="253"/>
-      <c r="DX3" s="268" t="s">
+      <c r="DX3" s="266" t="s">
         <v>251</v>
       </c>
       <c r="DY3" s="253"/>
-      <c r="DZ3" s="268" t="s">
+      <c r="DZ3" s="266" t="s">
         <v>252</v>
       </c>
       <c r="EA3" s="253"/>
-      <c r="EB3" s="268" t="s">
+      <c r="EB3" s="266" t="s">
         <v>253</v>
       </c>
       <c r="EC3" s="253"/>
-      <c r="ED3" s="262" t="s">
+      <c r="ED3" s="264" t="s">
         <v>254</v>
       </c>
       <c r="EE3" s="253"/>
-      <c r="EF3" s="262" t="s">
+      <c r="EF3" s="264" t="s">
         <v>255</v>
       </c>
       <c r="EG3" s="253"/>
-      <c r="EH3" s="262" t="s">
+      <c r="EH3" s="264" t="s">
         <v>256</v>
       </c>
       <c r="EI3" s="253"/>
-      <c r="EJ3" s="262" t="s">
+      <c r="EJ3" s="264" t="s">
         <v>257</v>
       </c>
       <c r="EK3" s="253"/>
-      <c r="EL3" s="262" t="s">
+      <c r="EL3" s="264" t="s">
         <v>258</v>
       </c>
       <c r="EM3" s="253"/>
-      <c r="EN3" s="262" t="s">
+      <c r="EN3" s="264" t="s">
         <v>259</v>
       </c>
       <c r="EO3" s="253"/>
@@ -12461,6 +12461,64 @@
     </row>
   </sheetData>
   <mergeCells count="74">
+    <mergeCell ref="BX3:BY3"/>
+    <mergeCell ref="CN3:CO3"/>
+    <mergeCell ref="CZ3:DA3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="CH3:CI3"/>
+    <mergeCell ref="CD3:CE3"/>
+    <mergeCell ref="CT3:CU3"/>
+    <mergeCell ref="A2:EO2"/>
+    <mergeCell ref="EJ3:EK3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="BJ3:BK3"/>
+    <mergeCell ref="AZ3:BA3"/>
+    <mergeCell ref="BL3:BM3"/>
+    <mergeCell ref="DL3:DM3"/>
+    <mergeCell ref="BV3:BW3"/>
+    <mergeCell ref="CB3:CC3"/>
+    <mergeCell ref="DJ3:DK3"/>
+    <mergeCell ref="EL3:EM3"/>
+    <mergeCell ref="CV3:CW3"/>
+    <mergeCell ref="A1:EO1"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="BF3:BG3"/>
+    <mergeCell ref="BH3:BI3"/>
+    <mergeCell ref="BN3:BO3"/>
+    <mergeCell ref="BP3:BQ3"/>
+    <mergeCell ref="BR3:BS3"/>
+    <mergeCell ref="DP3:DQ3"/>
+    <mergeCell ref="BZ3:CA3"/>
+    <mergeCell ref="CP3:CQ3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="CR3:CS3"/>
+    <mergeCell ref="EN3:EO3"/>
+    <mergeCell ref="CX3:CY3"/>
+    <mergeCell ref="DV3:DW3"/>
+    <mergeCell ref="EB3:EC3"/>
+    <mergeCell ref="ED3:EE3"/>
+    <mergeCell ref="EH3:EI3"/>
+    <mergeCell ref="DZ3:EA3"/>
+    <mergeCell ref="EF3:EG3"/>
+    <mergeCell ref="DH3:DI3"/>
+    <mergeCell ref="DT3:DU3"/>
+    <mergeCell ref="DR3:DS3"/>
+    <mergeCell ref="DX3:DY3"/>
+    <mergeCell ref="DD3:DE3"/>
+    <mergeCell ref="DF3:DG3"/>
+    <mergeCell ref="DB3:DC3"/>
+    <mergeCell ref="DN3:DO3"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="AP3:AQ3"/>
     <mergeCell ref="BB3:BC3"/>
@@ -12477,64 +12535,6 @@
     <mergeCell ref="R3:S3"/>
     <mergeCell ref="AR3:AS3"/>
     <mergeCell ref="T3:U3"/>
-    <mergeCell ref="EN3:EO3"/>
-    <mergeCell ref="CX3:CY3"/>
-    <mergeCell ref="DV3:DW3"/>
-    <mergeCell ref="EB3:EC3"/>
-    <mergeCell ref="ED3:EE3"/>
-    <mergeCell ref="EH3:EI3"/>
-    <mergeCell ref="DZ3:EA3"/>
-    <mergeCell ref="EF3:EG3"/>
-    <mergeCell ref="DH3:DI3"/>
-    <mergeCell ref="DT3:DU3"/>
-    <mergeCell ref="DR3:DS3"/>
-    <mergeCell ref="DX3:DY3"/>
-    <mergeCell ref="DD3:DE3"/>
-    <mergeCell ref="DF3:DG3"/>
-    <mergeCell ref="DB3:DC3"/>
-    <mergeCell ref="DN3:DO3"/>
-    <mergeCell ref="A1:EO1"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="BF3:BG3"/>
-    <mergeCell ref="BH3:BI3"/>
-    <mergeCell ref="BN3:BO3"/>
-    <mergeCell ref="BP3:BQ3"/>
-    <mergeCell ref="BR3:BS3"/>
-    <mergeCell ref="DP3:DQ3"/>
-    <mergeCell ref="BZ3:CA3"/>
-    <mergeCell ref="CP3:CQ3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="CR3:CS3"/>
-    <mergeCell ref="A2:EO2"/>
-    <mergeCell ref="EJ3:EK3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="BJ3:BK3"/>
-    <mergeCell ref="AZ3:BA3"/>
-    <mergeCell ref="BL3:BM3"/>
-    <mergeCell ref="DL3:DM3"/>
-    <mergeCell ref="BV3:BW3"/>
-    <mergeCell ref="CB3:CC3"/>
-    <mergeCell ref="DJ3:DK3"/>
-    <mergeCell ref="EL3:EM3"/>
-    <mergeCell ref="CV3:CW3"/>
-    <mergeCell ref="BX3:BY3"/>
-    <mergeCell ref="CN3:CO3"/>
-    <mergeCell ref="CZ3:DA3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="CH3:CI3"/>
-    <mergeCell ref="CD3:CE3"/>
-    <mergeCell ref="CT3:CU3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12560,7 +12560,7 @@
       <c r="C1" s="253"/>
     </row>
     <row r="2" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>266</v>
       </c>
       <c r="B2" s="253"/>
@@ -12713,7 +12713,7 @@
       <c r="BV1" s="253"/>
     </row>
     <row r="2" spans="1:74" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="268" t="s">
         <v>271</v>
       </c>
       <c r="B2" s="253"/>

--- a/gabarito/Bolao_Copa2026_TurimMFO_Master - Copia.xlsx
+++ b/gabarito/Bolao_Copa2026_TurimMFO_Master - Copia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pbrandao\Projetos\bolao-copa-2026\gabarito\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5485572D-86F7-44D9-A3AC-1FB006CB9578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9339711-8290-4D40-9E5E-4D8C29A109B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4924,67 +4924,73 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="47" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="41" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="47" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="42" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="46" fillId="44" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4993,22 +4999,13 @@
     <xf numFmtId="164" fontId="46" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="51" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="52" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="46" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5024,6 +5021,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5784,7 +5784,7 @@
       <c r="BM1" s="253"/>
     </row>
     <row r="2" spans="1:65" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>1028</v>
       </c>
       <c r="B2" s="253"/>
@@ -5920,67 +5920,67 @@
         <v>994</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="273" t="s">
+      <c r="AH3" s="270" t="s">
         <v>996</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="273" t="s">
+      <c r="AJ3" s="270" t="s">
         <v>998</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="273" t="s">
+      <c r="AL3" s="270" t="s">
         <v>1000</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="273" t="s">
+      <c r="AN3" s="270" t="s">
         <v>1002</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="273" t="s">
+      <c r="AP3" s="270" t="s">
         <v>1004</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="273" t="s">
+      <c r="AR3" s="270" t="s">
         <v>1006</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="273" t="s">
+      <c r="AT3" s="270" t="s">
         <v>1008</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="273" t="s">
+      <c r="AV3" s="270" t="s">
         <v>1010</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="275" t="s">
+      <c r="AX3" s="274" t="s">
         <v>1012</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="275" t="s">
+      <c r="AZ3" s="274" t="s">
         <v>1014</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="275" t="s">
+      <c r="BB3" s="274" t="s">
         <v>1016</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="275" t="s">
+      <c r="BD3" s="274" t="s">
         <v>1018</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="281" t="s">
+      <c r="BF3" s="277" t="s">
         <v>1020</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="281" t="s">
+      <c r="BH3" s="277" t="s">
         <v>1022</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="279" t="s">
+      <c r="BJ3" s="273" t="s">
         <v>1024</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="280" t="s">
+      <c r="BL3" s="275" t="s">
         <v>1026</v>
       </c>
       <c r="BM3" s="253"/>
@@ -5989,131 +5989,131 @@
       <c r="A4" s="210" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="270">
+      <c r="B4" s="272">
         <v>46201</v>
       </c>
       <c r="C4" s="253"/>
-      <c r="D4" s="270">
+      <c r="D4" s="272">
         <v>46202</v>
       </c>
       <c r="E4" s="253"/>
-      <c r="F4" s="270">
+      <c r="F4" s="272">
         <v>46202</v>
       </c>
       <c r="G4" s="253"/>
-      <c r="H4" s="270">
+      <c r="H4" s="272">
         <v>46202</v>
       </c>
       <c r="I4" s="253"/>
-      <c r="J4" s="270">
+      <c r="J4" s="272">
         <v>46203</v>
       </c>
       <c r="K4" s="253"/>
-      <c r="L4" s="270">
+      <c r="L4" s="272">
         <v>46203</v>
       </c>
       <c r="M4" s="253"/>
-      <c r="N4" s="270">
+      <c r="N4" s="272">
         <v>46203</v>
       </c>
       <c r="O4" s="253"/>
-      <c r="P4" s="270">
+      <c r="P4" s="272">
         <v>46204</v>
       </c>
       <c r="Q4" s="253"/>
-      <c r="R4" s="270">
+      <c r="R4" s="272">
         <v>46204</v>
       </c>
       <c r="S4" s="253"/>
-      <c r="T4" s="270">
+      <c r="T4" s="272">
         <v>46204</v>
       </c>
       <c r="U4" s="253"/>
-      <c r="V4" s="270">
+      <c r="V4" s="272">
         <v>46205</v>
       </c>
       <c r="W4" s="253"/>
-      <c r="X4" s="270">
+      <c r="X4" s="272">
         <v>46205</v>
       </c>
       <c r="Y4" s="253"/>
-      <c r="Z4" s="270">
+      <c r="Z4" s="272">
         <v>46205</v>
       </c>
       <c r="AA4" s="253"/>
-      <c r="AB4" s="270">
+      <c r="AB4" s="272">
         <v>46206</v>
       </c>
       <c r="AC4" s="253"/>
-      <c r="AD4" s="270">
+      <c r="AD4" s="272">
         <v>46206</v>
       </c>
       <c r="AE4" s="253"/>
-      <c r="AF4" s="270">
+      <c r="AF4" s="272">
         <v>46206</v>
       </c>
       <c r="AG4" s="253"/>
-      <c r="AH4" s="274">
+      <c r="AH4" s="276">
         <v>46207</v>
       </c>
       <c r="AI4" s="253"/>
-      <c r="AJ4" s="274">
+      <c r="AJ4" s="276">
         <v>46207</v>
       </c>
       <c r="AK4" s="253"/>
-      <c r="AL4" s="274">
+      <c r="AL4" s="276">
         <v>46208</v>
       </c>
       <c r="AM4" s="253"/>
-      <c r="AN4" s="274">
+      <c r="AN4" s="276">
         <v>46208</v>
       </c>
       <c r="AO4" s="253"/>
-      <c r="AP4" s="274">
+      <c r="AP4" s="276">
         <v>46209</v>
       </c>
       <c r="AQ4" s="253"/>
-      <c r="AR4" s="274">
+      <c r="AR4" s="276">
         <v>46209</v>
       </c>
       <c r="AS4" s="253"/>
-      <c r="AT4" s="274">
+      <c r="AT4" s="276">
         <v>46210</v>
       </c>
       <c r="AU4" s="253"/>
-      <c r="AV4" s="274">
+      <c r="AV4" s="276">
         <v>46210</v>
       </c>
       <c r="AW4" s="253"/>
-      <c r="AX4" s="272">
+      <c r="AX4" s="278">
         <v>46212</v>
       </c>
       <c r="AY4" s="253"/>
-      <c r="AZ4" s="272">
+      <c r="AZ4" s="278">
         <v>46213</v>
       </c>
       <c r="BA4" s="253"/>
-      <c r="BB4" s="272">
+      <c r="BB4" s="278">
         <v>46214</v>
       </c>
       <c r="BC4" s="253"/>
-      <c r="BD4" s="272">
+      <c r="BD4" s="278">
         <v>46214</v>
       </c>
       <c r="BE4" s="253"/>
-      <c r="BF4" s="277">
+      <c r="BF4" s="279">
         <v>46217</v>
       </c>
       <c r="BG4" s="253"/>
-      <c r="BH4" s="277">
+      <c r="BH4" s="279">
         <v>46218</v>
       </c>
       <c r="BI4" s="253"/>
-      <c r="BJ4" s="276">
+      <c r="BJ4" s="281">
         <v>46221</v>
       </c>
       <c r="BK4" s="253"/>
-      <c r="BL4" s="278">
+      <c r="BL4" s="280">
         <v>46222</v>
       </c>
       <c r="BM4" s="253"/>
@@ -7568,6 +7568,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="AX4:AY4"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AR4:AS4"/>
+    <mergeCell ref="AV4:AW4"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="AP3:AQ3"/>
+    <mergeCell ref="BB3:BC3"/>
+    <mergeCell ref="BJ4:BK4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="BH4:BI4"/>
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AP4:AQ4"/>
+    <mergeCell ref="A1:BM1"/>
+    <mergeCell ref="AT4:AU4"/>
+    <mergeCell ref="AZ4:BA4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="BB4:BC4"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="BD4:BE4"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="BF4:BG4"/>
+    <mergeCell ref="BL4:BM4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="X4:Y4"/>
     <mergeCell ref="A2:BM2"/>
     <mergeCell ref="AR3:AS3"/>
     <mergeCell ref="T3:U3"/>
@@ -7584,56 +7634,6 @@
     <mergeCell ref="BF3:BG3"/>
     <mergeCell ref="BH3:BI3"/>
     <mergeCell ref="V4:W4"/>
-    <mergeCell ref="A1:BM1"/>
-    <mergeCell ref="AT4:AU4"/>
-    <mergeCell ref="AZ4:BA4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="BB4:BC4"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="BD4:BE4"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="BF4:BG4"/>
-    <mergeCell ref="BL4:BM4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="BH4:BI4"/>
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AP4:AQ4"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="AP3:AQ3"/>
-    <mergeCell ref="BB3:BC3"/>
-    <mergeCell ref="BJ4:BK4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="AX4:AY4"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AR4:AS4"/>
-    <mergeCell ref="AV4:AW4"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="X3:Y3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7691,7 +7691,7 @@
       <c r="AH1" s="253"/>
     </row>
     <row r="2" spans="1:34" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>1032</v>
       </c>
       <c r="B2" s="253"/>
@@ -8857,7 +8857,7 @@
       <c r="J1" s="253"/>
     </row>
     <row r="2" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>1079</v>
       </c>
       <c r="B2" s="253"/>
@@ -8871,49 +8871,49 @@
       <c r="J2" s="253"/>
     </row>
     <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="284" t="s">
+      <c r="A4" s="289" t="s">
         <v>1080</v>
       </c>
       <c r="B4" s="253"/>
-      <c r="C4" s="284" t="s">
+      <c r="C4" s="289" t="s">
         <v>1081</v>
       </c>
       <c r="D4" s="253"/>
-      <c r="E4" s="284" t="s">
+      <c r="E4" s="289" t="s">
         <v>1082</v>
       </c>
       <c r="F4" s="253"/>
-      <c r="G4" s="284" t="s">
+      <c r="G4" s="289" t="s">
         <v>1083</v>
       </c>
       <c r="H4" s="253"/>
-      <c r="I4" s="284" t="s">
+      <c r="I4" s="289" t="s">
         <v>1084</v>
       </c>
       <c r="J4" s="253"/>
     </row>
     <row r="5" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="286" t="str">
+      <c r="A5" s="285" t="str">
         <f>IFERROR(INDEX(Ranking!$I$4:$I$7,MATCH(1,Ranking!$P$4:$P$7,0)),"?")</f>
         <v>Pedro Brandao</v>
       </c>
       <c r="B5" s="253"/>
-      <c r="C5" s="285">
+      <c r="C5" s="284">
         <f>IFERROR(MAX(Ranking!$M$4:$M$7),0)</f>
         <v>0</v>
       </c>
       <c r="D5" s="253"/>
-      <c r="E5" s="288">
+      <c r="E5" s="287">
         <f>COUNTIF('Jogos - Grupos'!H3:H74,"Finalizado")</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F5" s="253"/>
-      <c r="G5" s="287">
+      <c r="G5" s="286">
         <f>COUNTIF('Mata-Mata - Jogos'!I4:I35,"Finalizado")</f>
         <v>0</v>
       </c>
       <c r="H5" s="253"/>
-      <c r="I5" s="289" t="s">
+      <c r="I5" s="288" t="s">
         <v>1077</v>
       </c>
       <c r="J5" s="253"/>
@@ -9064,11 +9064,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="I5:J5"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="A1:J1"/>
@@ -9076,6 +9071,11 @@
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="I5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9151,15 +9151,11 @@
       <c r="E3" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="10">
-        <v>3</v>
-      </c>
-      <c r="G3" s="10">
-        <v>1</v>
-      </c>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
       <c r="H3" s="11" t="str">
         <f t="shared" ref="H3:H34" si="0">IF(AND(F3="",G3=""),"Aguardando",IF(AND(ISNUMBER(F3),ISNUMBER(G3)),"Finalizado","Verificar"))</f>
-        <v>Finalizado</v>
+        <v>Aguardando</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -9178,15 +9174,11 @@
       <c r="E4" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="10">
-        <v>0</v>
-      </c>
-      <c r="G4" s="10">
-        <v>2</v>
-      </c>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
       <c r="H4" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>Finalizado</v>
+        <v>Aguardando</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -9297,15 +9289,11 @@
       <c r="E9" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="10">
-        <v>2</v>
-      </c>
-      <c r="G9" s="10">
-        <v>1</v>
-      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
       <c r="H9" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>Finalizado</v>
+        <v>Aguardando</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -9324,15 +9312,11 @@
       <c r="E10" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="10">
-        <v>1</v>
-      </c>
-      <c r="G10" s="10">
-        <v>0</v>
-      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
       <c r="H10" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>Finalizado</v>
+        <v>Aguardando</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -9443,15 +9427,11 @@
       <c r="E15" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="10">
-        <v>3</v>
-      </c>
-      <c r="G15" s="10">
-        <v>2</v>
-      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
       <c r="H15" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>Finalizado</v>
+        <v>Aguardando</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -9470,15 +9450,11 @@
       <c r="E16" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="F16" s="10">
-        <v>1</v>
-      </c>
-      <c r="G16" s="10">
-        <v>0</v>
-      </c>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
       <c r="H16" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>Finalizado</v>
+        <v>Aguardando</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -10985,7 +10961,7 @@
       <c r="EO1" s="253"/>
     </row>
     <row r="2" spans="1:145" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>186</v>
       </c>
       <c r="B2" s="253"/>
@@ -11137,219 +11113,219 @@
       <c r="A3" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="B3" s="256" t="s">
+      <c r="B3" s="263" t="s">
         <v>188</v>
       </c>
       <c r="C3" s="253"/>
-      <c r="D3" s="256" t="s">
+      <c r="D3" s="263" t="s">
         <v>189</v>
       </c>
       <c r="E3" s="253"/>
-      <c r="F3" s="256" t="s">
+      <c r="F3" s="263" t="s">
         <v>190</v>
       </c>
       <c r="G3" s="253"/>
-      <c r="H3" s="256" t="s">
+      <c r="H3" s="263" t="s">
         <v>191</v>
       </c>
       <c r="I3" s="253"/>
-      <c r="J3" s="256" t="s">
+      <c r="J3" s="263" t="s">
         <v>192</v>
       </c>
       <c r="K3" s="253"/>
-      <c r="L3" s="256" t="s">
+      <c r="L3" s="263" t="s">
         <v>193</v>
       </c>
       <c r="M3" s="253"/>
-      <c r="N3" s="260" t="s">
+      <c r="N3" s="264" t="s">
         <v>194</v>
       </c>
       <c r="O3" s="253"/>
-      <c r="P3" s="260" t="s">
+      <c r="P3" s="264" t="s">
         <v>195</v>
       </c>
       <c r="Q3" s="253"/>
-      <c r="R3" s="260" t="s">
+      <c r="R3" s="264" t="s">
         <v>196</v>
       </c>
       <c r="S3" s="253"/>
-      <c r="T3" s="260" t="s">
+      <c r="T3" s="264" t="s">
         <v>197</v>
       </c>
       <c r="U3" s="253"/>
-      <c r="V3" s="260" t="s">
+      <c r="V3" s="264" t="s">
         <v>198</v>
       </c>
       <c r="W3" s="253"/>
-      <c r="X3" s="260" t="s">
+      <c r="X3" s="264" t="s">
         <v>199</v>
       </c>
       <c r="Y3" s="253"/>
-      <c r="Z3" s="261" t="s">
+      <c r="Z3" s="259" t="s">
         <v>200</v>
       </c>
       <c r="AA3" s="253"/>
-      <c r="AB3" s="261" t="s">
+      <c r="AB3" s="259" t="s">
         <v>201</v>
       </c>
       <c r="AC3" s="253"/>
-      <c r="AD3" s="261" t="s">
+      <c r="AD3" s="259" t="s">
         <v>202</v>
       </c>
       <c r="AE3" s="253"/>
-      <c r="AF3" s="261" t="s">
+      <c r="AF3" s="259" t="s">
         <v>203</v>
       </c>
       <c r="AG3" s="253"/>
-      <c r="AH3" s="261" t="s">
+      <c r="AH3" s="259" t="s">
         <v>204</v>
       </c>
       <c r="AI3" s="253"/>
-      <c r="AJ3" s="261" t="s">
+      <c r="AJ3" s="259" t="s">
         <v>205</v>
       </c>
       <c r="AK3" s="253"/>
-      <c r="AL3" s="257" t="s">
+      <c r="AL3" s="260" t="s">
         <v>206</v>
       </c>
       <c r="AM3" s="253"/>
-      <c r="AN3" s="257" t="s">
+      <c r="AN3" s="260" t="s">
         <v>207</v>
       </c>
       <c r="AO3" s="253"/>
-      <c r="AP3" s="257" t="s">
+      <c r="AP3" s="260" t="s">
         <v>208</v>
       </c>
       <c r="AQ3" s="253"/>
-      <c r="AR3" s="257" t="s">
+      <c r="AR3" s="260" t="s">
         <v>209</v>
       </c>
       <c r="AS3" s="253"/>
-      <c r="AT3" s="257" t="s">
+      <c r="AT3" s="260" t="s">
         <v>210</v>
       </c>
       <c r="AU3" s="253"/>
-      <c r="AV3" s="257" t="s">
+      <c r="AV3" s="260" t="s">
         <v>211</v>
       </c>
       <c r="AW3" s="253"/>
-      <c r="AX3" s="258" t="s">
+      <c r="AX3" s="265" t="s">
         <v>212</v>
       </c>
       <c r="AY3" s="253"/>
-      <c r="AZ3" s="258" t="s">
+      <c r="AZ3" s="265" t="s">
         <v>213</v>
       </c>
       <c r="BA3" s="253"/>
-      <c r="BB3" s="258" t="s">
+      <c r="BB3" s="265" t="s">
         <v>214</v>
       </c>
       <c r="BC3" s="253"/>
-      <c r="BD3" s="258" t="s">
+      <c r="BD3" s="265" t="s">
         <v>215</v>
       </c>
       <c r="BE3" s="253"/>
-      <c r="BF3" s="258" t="s">
+      <c r="BF3" s="265" t="s">
         <v>216</v>
       </c>
       <c r="BG3" s="253"/>
-      <c r="BH3" s="258" t="s">
+      <c r="BH3" s="265" t="s">
         <v>217</v>
       </c>
       <c r="BI3" s="253"/>
-      <c r="BJ3" s="262" t="s">
+      <c r="BJ3" s="266" t="s">
         <v>218</v>
       </c>
       <c r="BK3" s="253"/>
-      <c r="BL3" s="262" t="s">
+      <c r="BL3" s="266" t="s">
         <v>219</v>
       </c>
       <c r="BM3" s="253"/>
-      <c r="BN3" s="262" t="s">
+      <c r="BN3" s="266" t="s">
         <v>220</v>
       </c>
       <c r="BO3" s="253"/>
-      <c r="BP3" s="262" t="s">
+      <c r="BP3" s="266" t="s">
         <v>221</v>
       </c>
       <c r="BQ3" s="253"/>
-      <c r="BR3" s="262" t="s">
+      <c r="BR3" s="266" t="s">
         <v>222</v>
       </c>
       <c r="BS3" s="253"/>
-      <c r="BT3" s="262" t="s">
+      <c r="BT3" s="266" t="s">
         <v>223</v>
       </c>
       <c r="BU3" s="253"/>
-      <c r="BV3" s="263" t="s">
+      <c r="BV3" s="256" t="s">
         <v>224</v>
       </c>
       <c r="BW3" s="253"/>
-      <c r="BX3" s="263" t="s">
+      <c r="BX3" s="256" t="s">
         <v>225</v>
       </c>
       <c r="BY3" s="253"/>
-      <c r="BZ3" s="263" t="s">
+      <c r="BZ3" s="256" t="s">
         <v>226</v>
       </c>
       <c r="CA3" s="253"/>
-      <c r="CB3" s="263" t="s">
+      <c r="CB3" s="256" t="s">
         <v>227</v>
       </c>
       <c r="CC3" s="253"/>
-      <c r="CD3" s="263" t="s">
+      <c r="CD3" s="256" t="s">
         <v>228</v>
       </c>
       <c r="CE3" s="253"/>
-      <c r="CF3" s="263" t="s">
+      <c r="CF3" s="256" t="s">
         <v>229</v>
       </c>
       <c r="CG3" s="253"/>
-      <c r="CH3" s="259" t="s">
+      <c r="CH3" s="257" t="s">
         <v>230</v>
       </c>
       <c r="CI3" s="253"/>
-      <c r="CJ3" s="259" t="s">
+      <c r="CJ3" s="257" t="s">
         <v>231</v>
       </c>
       <c r="CK3" s="253"/>
-      <c r="CL3" s="259" t="s">
+      <c r="CL3" s="257" t="s">
         <v>232</v>
       </c>
       <c r="CM3" s="253"/>
-      <c r="CN3" s="259" t="s">
+      <c r="CN3" s="257" t="s">
         <v>233</v>
       </c>
       <c r="CO3" s="253"/>
-      <c r="CP3" s="259" t="s">
+      <c r="CP3" s="257" t="s">
         <v>234</v>
       </c>
       <c r="CQ3" s="253"/>
-      <c r="CR3" s="259" t="s">
+      <c r="CR3" s="257" t="s">
         <v>235</v>
       </c>
       <c r="CS3" s="253"/>
-      <c r="CT3" s="265" t="s">
+      <c r="CT3" s="258" t="s">
         <v>236</v>
       </c>
       <c r="CU3" s="253"/>
-      <c r="CV3" s="265" t="s">
+      <c r="CV3" s="258" t="s">
         <v>237</v>
       </c>
       <c r="CW3" s="253"/>
-      <c r="CX3" s="265" t="s">
+      <c r="CX3" s="258" t="s">
         <v>238</v>
       </c>
       <c r="CY3" s="253"/>
-      <c r="CZ3" s="265" t="s">
+      <c r="CZ3" s="258" t="s">
         <v>239</v>
       </c>
       <c r="DA3" s="253"/>
-      <c r="DB3" s="265" t="s">
+      <c r="DB3" s="258" t="s">
         <v>240</v>
       </c>
       <c r="DC3" s="253"/>
-      <c r="DD3" s="265" t="s">
+      <c r="DD3" s="258" t="s">
         <v>241</v>
       </c>
       <c r="DE3" s="253"/>
@@ -11377,51 +11353,51 @@
         <v>247</v>
       </c>
       <c r="DQ3" s="253"/>
-      <c r="DR3" s="266" t="s">
+      <c r="DR3" s="268" t="s">
         <v>248</v>
       </c>
       <c r="DS3" s="253"/>
-      <c r="DT3" s="266" t="s">
+      <c r="DT3" s="268" t="s">
         <v>249</v>
       </c>
       <c r="DU3" s="253"/>
-      <c r="DV3" s="266" t="s">
+      <c r="DV3" s="268" t="s">
         <v>250</v>
       </c>
       <c r="DW3" s="253"/>
-      <c r="DX3" s="266" t="s">
+      <c r="DX3" s="268" t="s">
         <v>251</v>
       </c>
       <c r="DY3" s="253"/>
-      <c r="DZ3" s="266" t="s">
+      <c r="DZ3" s="268" t="s">
         <v>252</v>
       </c>
       <c r="EA3" s="253"/>
-      <c r="EB3" s="266" t="s">
+      <c r="EB3" s="268" t="s">
         <v>253</v>
       </c>
       <c r="EC3" s="253"/>
-      <c r="ED3" s="264" t="s">
+      <c r="ED3" s="262" t="s">
         <v>254</v>
       </c>
       <c r="EE3" s="253"/>
-      <c r="EF3" s="264" t="s">
+      <c r="EF3" s="262" t="s">
         <v>255</v>
       </c>
       <c r="EG3" s="253"/>
-      <c r="EH3" s="264" t="s">
+      <c r="EH3" s="262" t="s">
         <v>256</v>
       </c>
       <c r="EI3" s="253"/>
-      <c r="EJ3" s="264" t="s">
+      <c r="EJ3" s="262" t="s">
         <v>257</v>
       </c>
       <c r="EK3" s="253"/>
-      <c r="EL3" s="264" t="s">
+      <c r="EL3" s="262" t="s">
         <v>258</v>
       </c>
       <c r="EM3" s="253"/>
-      <c r="EN3" s="264" t="s">
+      <c r="EN3" s="262" t="s">
         <v>259</v>
       </c>
       <c r="EO3" s="253"/>
@@ -12461,16 +12437,54 @@
     </row>
   </sheetData>
   <mergeCells count="74">
-    <mergeCell ref="BX3:BY3"/>
-    <mergeCell ref="CN3:CO3"/>
-    <mergeCell ref="CZ3:DA3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="CH3:CI3"/>
-    <mergeCell ref="CD3:CE3"/>
-    <mergeCell ref="CT3:CU3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="AP3:AQ3"/>
+    <mergeCell ref="BB3:BC3"/>
+    <mergeCell ref="CJ3:CK3"/>
+    <mergeCell ref="CL3:CM3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="BT3:BU3"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="CF3:CG3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="AR3:AS3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="EN3:EO3"/>
+    <mergeCell ref="CX3:CY3"/>
+    <mergeCell ref="DV3:DW3"/>
+    <mergeCell ref="EB3:EC3"/>
+    <mergeCell ref="ED3:EE3"/>
+    <mergeCell ref="EH3:EI3"/>
+    <mergeCell ref="DZ3:EA3"/>
+    <mergeCell ref="EF3:EG3"/>
+    <mergeCell ref="DH3:DI3"/>
+    <mergeCell ref="DT3:DU3"/>
+    <mergeCell ref="DR3:DS3"/>
+    <mergeCell ref="DX3:DY3"/>
+    <mergeCell ref="DD3:DE3"/>
+    <mergeCell ref="DF3:DG3"/>
+    <mergeCell ref="DB3:DC3"/>
+    <mergeCell ref="DN3:DO3"/>
+    <mergeCell ref="A1:EO1"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="BF3:BG3"/>
+    <mergeCell ref="BH3:BI3"/>
+    <mergeCell ref="BN3:BO3"/>
+    <mergeCell ref="BP3:BQ3"/>
+    <mergeCell ref="BR3:BS3"/>
+    <mergeCell ref="DP3:DQ3"/>
+    <mergeCell ref="BZ3:CA3"/>
+    <mergeCell ref="CP3:CQ3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="CR3:CS3"/>
     <mergeCell ref="A2:EO2"/>
     <mergeCell ref="EJ3:EK3"/>
     <mergeCell ref="D3:E3"/>
@@ -12487,54 +12501,16 @@
     <mergeCell ref="DJ3:DK3"/>
     <mergeCell ref="EL3:EM3"/>
     <mergeCell ref="CV3:CW3"/>
-    <mergeCell ref="A1:EO1"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="BF3:BG3"/>
-    <mergeCell ref="BH3:BI3"/>
-    <mergeCell ref="BN3:BO3"/>
-    <mergeCell ref="BP3:BQ3"/>
-    <mergeCell ref="BR3:BS3"/>
-    <mergeCell ref="DP3:DQ3"/>
-    <mergeCell ref="BZ3:CA3"/>
-    <mergeCell ref="CP3:CQ3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="CR3:CS3"/>
-    <mergeCell ref="EN3:EO3"/>
-    <mergeCell ref="CX3:CY3"/>
-    <mergeCell ref="DV3:DW3"/>
-    <mergeCell ref="EB3:EC3"/>
-    <mergeCell ref="ED3:EE3"/>
-    <mergeCell ref="EH3:EI3"/>
-    <mergeCell ref="DZ3:EA3"/>
-    <mergeCell ref="EF3:EG3"/>
-    <mergeCell ref="DH3:DI3"/>
-    <mergeCell ref="DT3:DU3"/>
-    <mergeCell ref="DR3:DS3"/>
-    <mergeCell ref="DX3:DY3"/>
-    <mergeCell ref="DD3:DE3"/>
-    <mergeCell ref="DF3:DG3"/>
-    <mergeCell ref="DB3:DC3"/>
-    <mergeCell ref="DN3:DO3"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="AP3:AQ3"/>
-    <mergeCell ref="BB3:BC3"/>
-    <mergeCell ref="CJ3:CK3"/>
-    <mergeCell ref="CL3:CM3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="BT3:BU3"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="CF3:CG3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="AR3:AS3"/>
-    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="BX3:BY3"/>
+    <mergeCell ref="CN3:CO3"/>
+    <mergeCell ref="CZ3:DA3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="CH3:CI3"/>
+    <mergeCell ref="CD3:CE3"/>
+    <mergeCell ref="CT3:CU3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12560,7 +12536,7 @@
       <c r="C1" s="253"/>
     </row>
     <row r="2" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>266</v>
       </c>
       <c r="B2" s="253"/>
@@ -12713,7 +12689,7 @@
       <c r="BV1" s="253"/>
     </row>
     <row r="2" spans="1:74" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="261" t="s">
         <v>271</v>
       </c>
       <c r="B2" s="253"/>
@@ -13240,13 +13216,13 @@
       <c r="A5" s="81" t="s">
         <v>261</v>
       </c>
-      <c r="B5" s="106">
+      <c r="B5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F3="",'Jogos - Grupos'!G3=""),"-",IF(OR('Apostas - Grupos'!B5="",'Apostas - Grupos'!C5=""),0,IF(AND('Apostas - Grupos'!B5='Jogos - Grupos'!F3,'Apostas - Grupos'!C5='Jogos - Grupos'!G3),5,IF(OR(AND('Jogos - Grupos'!F3='Jogos - Grupos'!G3,'Apostas - Grupos'!B5='Apostas - Grupos'!C5),AND('Jogos - Grupos'!F3&gt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B5&gt;'Apostas - Grupos'!C5),AND('Jogos - Grupos'!F3&lt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B5&lt;'Apostas - Grupos'!C5)),IF(('Apostas - Grupos'!B5-'Apostas - Grupos'!C5)=('Jogos - Grupos'!F3-'Jogos - Grupos'!G3),3,2),0))))</f>
-        <v>0</v>
-      </c>
-      <c r="C5" s="106">
+        <v>-</v>
+      </c>
+      <c r="C5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F4="",'Jogos - Grupos'!G4=""),"-",IF(OR('Apostas - Grupos'!D5="",'Apostas - Grupos'!E5=""),0,IF(AND('Apostas - Grupos'!D5='Jogos - Grupos'!F4,'Apostas - Grupos'!E5='Jogos - Grupos'!G4),5,IF(OR(AND('Jogos - Grupos'!F4='Jogos - Grupos'!G4,'Apostas - Grupos'!D5='Apostas - Grupos'!E5),AND('Jogos - Grupos'!F4&gt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D5&gt;'Apostas - Grupos'!E5),AND('Jogos - Grupos'!F4&lt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D5&lt;'Apostas - Grupos'!E5)),IF(('Apostas - Grupos'!D5-'Apostas - Grupos'!E5)=('Jogos - Grupos'!F4-'Jogos - Grupos'!G4),3,2),0))))</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="D5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F5="",'Jogos - Grupos'!G5=""),"-",IF(OR('Apostas - Grupos'!F5="",'Apostas - Grupos'!G5=""),0,IF(AND('Apostas - Grupos'!F5='Jogos - Grupos'!F5,'Apostas - Grupos'!G5='Jogos - Grupos'!G5),5,IF(OR(AND('Jogos - Grupos'!F5='Jogos - Grupos'!G5,'Apostas - Grupos'!F5='Apostas - Grupos'!G5),AND('Jogos - Grupos'!F5&gt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F5&gt;'Apostas - Grupos'!G5),AND('Jogos - Grupos'!F5&lt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F5&lt;'Apostas - Grupos'!G5)),IF(('Apostas - Grupos'!F5-'Apostas - Grupos'!G5)=('Jogos - Grupos'!F5-'Jogos - Grupos'!G5),3,2),0))))</f>
@@ -13264,13 +13240,13 @@
         <f>IF(OR('Jogos - Grupos'!F8="",'Jogos - Grupos'!G8=""),"-",IF(OR('Apostas - Grupos'!L5="",'Apostas - Grupos'!M5=""),0,IF(AND('Apostas - Grupos'!L5='Jogos - Grupos'!F8,'Apostas - Grupos'!M5='Jogos - Grupos'!G8),5,IF(OR(AND('Jogos - Grupos'!F8='Jogos - Grupos'!G8,'Apostas - Grupos'!L5='Apostas - Grupos'!M5),AND('Jogos - Grupos'!F8&gt;'Jogos - Grupos'!G8,'Apostas - Grupos'!L5&gt;'Apostas - Grupos'!M5),AND('Jogos - Grupos'!F8&lt;'Jogos - Grupos'!G8,'Apostas - Grupos'!L5&lt;'Apostas - Grupos'!M5)),IF(('Apostas - Grupos'!L5-'Apostas - Grupos'!M5)=('Jogos - Grupos'!F8-'Jogos - Grupos'!G8),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="H5" s="106">
+      <c r="H5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F9="",'Jogos - Grupos'!G9=""),"-",IF(OR('Apostas - Grupos'!N5="",'Apostas - Grupos'!O5=""),0,IF(AND('Apostas - Grupos'!N5='Jogos - Grupos'!F9,'Apostas - Grupos'!O5='Jogos - Grupos'!G9),5,IF(OR(AND('Jogos - Grupos'!F9='Jogos - Grupos'!G9,'Apostas - Grupos'!N5='Apostas - Grupos'!O5),AND('Jogos - Grupos'!F9&gt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N5&gt;'Apostas - Grupos'!O5),AND('Jogos - Grupos'!F9&lt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N5&lt;'Apostas - Grupos'!O5)),IF(('Apostas - Grupos'!N5-'Apostas - Grupos'!O5)=('Jogos - Grupos'!F9-'Jogos - Grupos'!G9),3,2),0))))</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="106">
+        <v>-</v>
+      </c>
+      <c r="I5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F10="",'Jogos - Grupos'!G10=""),"-",IF(OR('Apostas - Grupos'!P5="",'Apostas - Grupos'!Q5=""),0,IF(AND('Apostas - Grupos'!P5='Jogos - Grupos'!F10,'Apostas - Grupos'!Q5='Jogos - Grupos'!G10),5,IF(OR(AND('Jogos - Grupos'!F10='Jogos - Grupos'!G10,'Apostas - Grupos'!P5='Apostas - Grupos'!Q5),AND('Jogos - Grupos'!F10&gt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P5&gt;'Apostas - Grupos'!Q5),AND('Jogos - Grupos'!F10&lt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P5&lt;'Apostas - Grupos'!Q5)),IF(('Apostas - Grupos'!P5-'Apostas - Grupos'!Q5)=('Jogos - Grupos'!F10-'Jogos - Grupos'!G10),3,2),0))))</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="J5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F11="",'Jogos - Grupos'!G11=""),"-",IF(OR('Apostas - Grupos'!R5="",'Apostas - Grupos'!S5=""),0,IF(AND('Apostas - Grupos'!R5='Jogos - Grupos'!F11,'Apostas - Grupos'!S5='Jogos - Grupos'!G11),5,IF(OR(AND('Jogos - Grupos'!F11='Jogos - Grupos'!G11,'Apostas - Grupos'!R5='Apostas - Grupos'!S5),AND('Jogos - Grupos'!F11&gt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R5&gt;'Apostas - Grupos'!S5),AND('Jogos - Grupos'!F11&lt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R5&lt;'Apostas - Grupos'!S5)),IF(('Apostas - Grupos'!R5-'Apostas - Grupos'!S5)=('Jogos - Grupos'!F11-'Jogos - Grupos'!G11),3,2),0))))</f>
@@ -13288,13 +13264,13 @@
         <f>IF(OR('Jogos - Grupos'!F14="",'Jogos - Grupos'!G14=""),"-",IF(OR('Apostas - Grupos'!X5="",'Apostas - Grupos'!Y5=""),0,IF(AND('Apostas - Grupos'!X5='Jogos - Grupos'!F14,'Apostas - Grupos'!Y5='Jogos - Grupos'!G14),5,IF(OR(AND('Jogos - Grupos'!F14='Jogos - Grupos'!G14,'Apostas - Grupos'!X5='Apostas - Grupos'!Y5),AND('Jogos - Grupos'!F14&gt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X5&gt;'Apostas - Grupos'!Y5),AND('Jogos - Grupos'!F14&lt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X5&lt;'Apostas - Grupos'!Y5)),IF(('Apostas - Grupos'!X5-'Apostas - Grupos'!Y5)=('Jogos - Grupos'!F14-'Jogos - Grupos'!G14),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="N5" s="106">
+      <c r="N5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F15="",'Jogos - Grupos'!G15=""),"-",IF(OR('Apostas - Grupos'!Z5="",'Apostas - Grupos'!AA5=""),0,IF(AND('Apostas - Grupos'!Z5='Jogos - Grupos'!F15,'Apostas - Grupos'!AA5='Jogos - Grupos'!G15),5,IF(OR(AND('Jogos - Grupos'!F15='Jogos - Grupos'!G15,'Apostas - Grupos'!Z5='Apostas - Grupos'!AA5),AND('Jogos - Grupos'!F15&gt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z5&gt;'Apostas - Grupos'!AA5),AND('Jogos - Grupos'!F15&lt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z5&lt;'Apostas - Grupos'!AA5)),IF(('Apostas - Grupos'!Z5-'Apostas - Grupos'!AA5)=('Jogos - Grupos'!F15-'Jogos - Grupos'!G15),3,2),0))))</f>
-        <v>0</v>
-      </c>
-      <c r="O5" s="106">
+        <v>-</v>
+      </c>
+      <c r="O5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F16="",'Jogos - Grupos'!G16=""),"-",IF(OR('Apostas - Grupos'!AB5="",'Apostas - Grupos'!AC5=""),0,IF(AND('Apostas - Grupos'!AB5='Jogos - Grupos'!F16,'Apostas - Grupos'!AC5='Jogos - Grupos'!G16),5,IF(OR(AND('Jogos - Grupos'!F16='Jogos - Grupos'!G16,'Apostas - Grupos'!AB5='Apostas - Grupos'!AC5),AND('Jogos - Grupos'!F16&gt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB5&gt;'Apostas - Grupos'!AC5),AND('Jogos - Grupos'!F16&lt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB5&lt;'Apostas - Grupos'!AC5)),IF(('Apostas - Grupos'!AB5-'Apostas - Grupos'!AC5)=('Jogos - Grupos'!F16-'Jogos - Grupos'!G16),3,2),0))))</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="P5" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F17="",'Jogos - Grupos'!G17=""),"-",IF(OR('Apostas - Grupos'!AD5="",'Apostas - Grupos'!AE5=""),0,IF(AND('Apostas - Grupos'!AD5='Jogos - Grupos'!F17,'Apostas - Grupos'!AE5='Jogos - Grupos'!G17),5,IF(OR(AND('Jogos - Grupos'!F17='Jogos - Grupos'!G17,'Apostas - Grupos'!AD5='Apostas - Grupos'!AE5),AND('Jogos - Grupos'!F17&gt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD5&gt;'Apostas - Grupos'!AE5),AND('Jogos - Grupos'!F17&lt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD5&lt;'Apostas - Grupos'!AE5)),IF(('Apostas - Grupos'!AD5-'Apostas - Grupos'!AE5)=('Jogos - Grupos'!F17-'Jogos - Grupos'!G17),3,2),0))))</f>
@@ -13537,13 +13513,13 @@
       <c r="A6" s="82" t="s">
         <v>262</v>
       </c>
-      <c r="B6" s="108">
+      <c r="B6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F3="",'Jogos - Grupos'!G3=""),"-",IF(OR('Apostas - Grupos'!B6="",'Apostas - Grupos'!C6=""),0,IF(AND('Apostas - Grupos'!B6='Jogos - Grupos'!F3,'Apostas - Grupos'!C6='Jogos - Grupos'!G3),5,IF(OR(AND('Jogos - Grupos'!F3='Jogos - Grupos'!G3,'Apostas - Grupos'!B6='Apostas - Grupos'!C6),AND('Jogos - Grupos'!F3&gt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B6&gt;'Apostas - Grupos'!C6),AND('Jogos - Grupos'!F3&lt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B6&lt;'Apostas - Grupos'!C6)),IF(('Apostas - Grupos'!B6-'Apostas - Grupos'!C6)=('Jogos - Grupos'!F3-'Jogos - Grupos'!G3),3,2),0))))</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="108">
+        <v>-</v>
+      </c>
+      <c r="C6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F4="",'Jogos - Grupos'!G4=""),"-",IF(OR('Apostas - Grupos'!D6="",'Apostas - Grupos'!E6=""),0,IF(AND('Apostas - Grupos'!D6='Jogos - Grupos'!F4,'Apostas - Grupos'!E6='Jogos - Grupos'!G4),5,IF(OR(AND('Jogos - Grupos'!F4='Jogos - Grupos'!G4,'Apostas - Grupos'!D6='Apostas - Grupos'!E6),AND('Jogos - Grupos'!F4&gt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D6&gt;'Apostas - Grupos'!E6),AND('Jogos - Grupos'!F4&lt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D6&lt;'Apostas - Grupos'!E6)),IF(('Apostas - Grupos'!D6-'Apostas - Grupos'!E6)=('Jogos - Grupos'!F4-'Jogos - Grupos'!G4),3,2),0))))</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="D6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F5="",'Jogos - Grupos'!G5=""),"-",IF(OR('Apostas - Grupos'!F6="",'Apostas - Grupos'!G6=""),0,IF(AND('Apostas - Grupos'!F6='Jogos - Grupos'!F5,'Apostas - Grupos'!G6='Jogos - Grupos'!G5),5,IF(OR(AND('Jogos - Grupos'!F5='Jogos - Grupos'!G5,'Apostas - Grupos'!F6='Apostas - Grupos'!G6),AND('Jogos - Grupos'!F5&gt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F6&gt;'Apostas - Grupos'!G6),AND('Jogos - Grupos'!F5&lt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F6&lt;'Apostas - Grupos'!G6)),IF(('Apostas - Grupos'!F6-'Apostas - Grupos'!G6)=('Jogos - Grupos'!F5-'Jogos - Grupos'!G5),3,2),0))))</f>
@@ -13561,13 +13537,13 @@
         <f>IF(OR('Jogos - Grupos'!F8="",'Jogos - Grupos'!G8=""),"-",IF(OR('Apostas - Grupos'!L6="",'Apostas - Grupos'!M6=""),0,IF(AND('Apostas - Grupos'!L6='Jogos - Grupos'!F8,'Apostas - Grupos'!M6='Jogos - Grupos'!G8),5,IF(OR(AND('Jogos - Grupos'!F8='Jogos - Grupos'!G8,'Apostas - Grupos'!L6='Apostas - Grupos'!M6),AND('Jogos - Grupos'!F8&gt;'Jogos - Grupos'!G8,'Apostas - Grupos'!L6&gt;'Apostas - Grupos'!M6),AND('Jogos - Grupos'!F8&lt;'Jogos - Grupos'!G8,'Apostas - Grupos'!L6&lt;'Apostas - Grupos'!M6)),IF(('Apostas - Grupos'!L6-'Apostas - Grupos'!M6)=('Jogos - Grupos'!F8-'Jogos - Grupos'!G8),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="H6" s="108">
+      <c r="H6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F9="",'Jogos - Grupos'!G9=""),"-",IF(OR('Apostas - Grupos'!N6="",'Apostas - Grupos'!O6=""),0,IF(AND('Apostas - Grupos'!N6='Jogos - Grupos'!F9,'Apostas - Grupos'!O6='Jogos - Grupos'!G9),5,IF(OR(AND('Jogos - Grupos'!F9='Jogos - Grupos'!G9,'Apostas - Grupos'!N6='Apostas - Grupos'!O6),AND('Jogos - Grupos'!F9&gt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N6&gt;'Apostas - Grupos'!O6),AND('Jogos - Grupos'!F9&lt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N6&lt;'Apostas - Grupos'!O6)),IF(('Apostas - Grupos'!N6-'Apostas - Grupos'!O6)=('Jogos - Grupos'!F9-'Jogos - Grupos'!G9),3,2),0))))</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="108">
+        <v>-</v>
+      </c>
+      <c r="I6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F10="",'Jogos - Grupos'!G10=""),"-",IF(OR('Apostas - Grupos'!P6="",'Apostas - Grupos'!Q6=""),0,IF(AND('Apostas - Grupos'!P6='Jogos - Grupos'!F10,'Apostas - Grupos'!Q6='Jogos - Grupos'!G10),5,IF(OR(AND('Jogos - Grupos'!F10='Jogos - Grupos'!G10,'Apostas - Grupos'!P6='Apostas - Grupos'!Q6),AND('Jogos - Grupos'!F10&gt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P6&gt;'Apostas - Grupos'!Q6),AND('Jogos - Grupos'!F10&lt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P6&lt;'Apostas - Grupos'!Q6)),IF(('Apostas - Grupos'!P6-'Apostas - Grupos'!Q6)=('Jogos - Grupos'!F10-'Jogos - Grupos'!G10),3,2),0))))</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="J6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F11="",'Jogos - Grupos'!G11=""),"-",IF(OR('Apostas - Grupos'!R6="",'Apostas - Grupos'!S6=""),0,IF(AND('Apostas - Grupos'!R6='Jogos - Grupos'!F11,'Apostas - Grupos'!S6='Jogos - Grupos'!G11),5,IF(OR(AND('Jogos - Grupos'!F11='Jogos - Grupos'!G11,'Apostas - Grupos'!R6='Apostas - Grupos'!S6),AND('Jogos - Grupos'!F11&gt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R6&gt;'Apostas - Grupos'!S6),AND('Jogos - Grupos'!F11&lt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R6&lt;'Apostas - Grupos'!S6)),IF(('Apostas - Grupos'!R6-'Apostas - Grupos'!S6)=('Jogos - Grupos'!F11-'Jogos - Grupos'!G11),3,2),0))))</f>
@@ -13585,13 +13561,13 @@
         <f>IF(OR('Jogos - Grupos'!F14="",'Jogos - Grupos'!G14=""),"-",IF(OR('Apostas - Grupos'!X6="",'Apostas - Grupos'!Y6=""),0,IF(AND('Apostas - Grupos'!X6='Jogos - Grupos'!F14,'Apostas - Grupos'!Y6='Jogos - Grupos'!G14),5,IF(OR(AND('Jogos - Grupos'!F14='Jogos - Grupos'!G14,'Apostas - Grupos'!X6='Apostas - Grupos'!Y6),AND('Jogos - Grupos'!F14&gt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X6&gt;'Apostas - Grupos'!Y6),AND('Jogos - Grupos'!F14&lt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X6&lt;'Apostas - Grupos'!Y6)),IF(('Apostas - Grupos'!X6-'Apostas - Grupos'!Y6)=('Jogos - Grupos'!F14-'Jogos - Grupos'!G14),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="N6" s="108">
+      <c r="N6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F15="",'Jogos - Grupos'!G15=""),"-",IF(OR('Apostas - Grupos'!Z6="",'Apostas - Grupos'!AA6=""),0,IF(AND('Apostas - Grupos'!Z6='Jogos - Grupos'!F15,'Apostas - Grupos'!AA6='Jogos - Grupos'!G15),5,IF(OR(AND('Jogos - Grupos'!F15='Jogos - Grupos'!G15,'Apostas - Grupos'!Z6='Apostas - Grupos'!AA6),AND('Jogos - Grupos'!F15&gt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z6&gt;'Apostas - Grupos'!AA6),AND('Jogos - Grupos'!F15&lt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z6&lt;'Apostas - Grupos'!AA6)),IF(('Apostas - Grupos'!Z6-'Apostas - Grupos'!AA6)=('Jogos - Grupos'!F15-'Jogos - Grupos'!G15),3,2),0))))</f>
-        <v>0</v>
-      </c>
-      <c r="O6" s="108">
+        <v>-</v>
+      </c>
+      <c r="O6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F16="",'Jogos - Grupos'!G16=""),"-",IF(OR('Apostas - Grupos'!AB6="",'Apostas - Grupos'!AC6=""),0,IF(AND('Apostas - Grupos'!AB6='Jogos - Grupos'!F16,'Apostas - Grupos'!AC6='Jogos - Grupos'!G16),5,IF(OR(AND('Jogos - Grupos'!F16='Jogos - Grupos'!G16,'Apostas - Grupos'!AB6='Apostas - Grupos'!AC6),AND('Jogos - Grupos'!F16&gt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB6&gt;'Apostas - Grupos'!AC6),AND('Jogos - Grupos'!F16&lt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB6&lt;'Apostas - Grupos'!AC6)),IF(('Apostas - Grupos'!AB6-'Apostas - Grupos'!AC6)=('Jogos - Grupos'!F16-'Jogos - Grupos'!G16),3,2),0))))</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="P6" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F17="",'Jogos - Grupos'!G17=""),"-",IF(OR('Apostas - Grupos'!AD6="",'Apostas - Grupos'!AE6=""),0,IF(AND('Apostas - Grupos'!AD6='Jogos - Grupos'!F17,'Apostas - Grupos'!AE6='Jogos - Grupos'!G17),5,IF(OR(AND('Jogos - Grupos'!F17='Jogos - Grupos'!G17,'Apostas - Grupos'!AD6='Apostas - Grupos'!AE6),AND('Jogos - Grupos'!F17&gt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD6&gt;'Apostas - Grupos'!AE6),AND('Jogos - Grupos'!F17&lt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD6&lt;'Apostas - Grupos'!AE6)),IF(('Apostas - Grupos'!AD6-'Apostas - Grupos'!AE6)=('Jogos - Grupos'!F17-'Jogos - Grupos'!G17),3,2),0))))</f>
@@ -13834,13 +13810,13 @@
       <c r="A7" s="81" t="s">
         <v>263</v>
       </c>
-      <c r="B7" s="106">
+      <c r="B7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F3="",'Jogos - Grupos'!G3=""),"-",IF(OR('Apostas - Grupos'!B7="",'Apostas - Grupos'!C7=""),0,IF(AND('Apostas - Grupos'!B7='Jogos - Grupos'!F3,'Apostas - Grupos'!C7='Jogos - Grupos'!G3),5,IF(OR(AND('Jogos - Grupos'!F3='Jogos - Grupos'!G3,'Apostas - Grupos'!B7='Apostas - Grupos'!C7),AND('Jogos - Grupos'!F3&gt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B7&gt;'Apostas - Grupos'!C7),AND('Jogos - Grupos'!F3&lt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B7&lt;'Apostas - Grupos'!C7)),IF(('Apostas - Grupos'!B7-'Apostas - Grupos'!C7)=('Jogos - Grupos'!F3-'Jogos - Grupos'!G3),3,2),0))))</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="106">
+        <v>-</v>
+      </c>
+      <c r="C7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F4="",'Jogos - Grupos'!G4=""),"-",IF(OR('Apostas - Grupos'!D7="",'Apostas - Grupos'!E7=""),0,IF(AND('Apostas - Grupos'!D7='Jogos - Grupos'!F4,'Apostas - Grupos'!E7='Jogos - Grupos'!G4),5,IF(OR(AND('Jogos - Grupos'!F4='Jogos - Grupos'!G4,'Apostas - Grupos'!D7='Apostas - Grupos'!E7),AND('Jogos - Grupos'!F4&gt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D7&gt;'Apostas - Grupos'!E7),AND('Jogos - Grupos'!F4&lt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D7&lt;'Apostas - Grupos'!E7)),IF(('Apostas - Grupos'!D7-'Apostas - Grupos'!E7)=('Jogos - Grupos'!F4-'Jogos - Grupos'!G4),3,2),0))))</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="D7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F5="",'Jogos - Grupos'!G5=""),"-",IF(OR('Apostas - Grupos'!F7="",'Apostas - Grupos'!G7=""),0,IF(AND('Apostas - Grupos'!F7='Jogos - Grupos'!F5,'Apostas - Grupos'!G7='Jogos - Grupos'!G5),5,IF(OR(AND('Jogos - Grupos'!F5='Jogos - Grupos'!G5,'Apostas - Grupos'!F7='Apostas - Grupos'!G7),AND('Jogos - Grupos'!F5&gt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F7&gt;'Apostas - Grupos'!G7),AND('Jogos - Grupos'!F5&lt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F7&lt;'Apostas - Grupos'!G7)),IF(('Apostas - Grupos'!F7-'Apostas - Grupos'!G7)=('Jogos - Grupos'!F5-'Jogos - Grupos'!G5),3,2),0))))</f>
@@ -13858,13 +13834,13 @@
         <f>IF(OR('Jogos - Grupos'!F8="",'Jogos - Grupos'!G8=""),"-",IF(OR('Apostas - Grupos'!L7="",'Apostas - Grupos'!M7=""),0,IF(AND('Apostas - Grupos'!L7='Jogos - Grupos'!F8,'Apostas - Grupos'!M7='Jogos - Grupos'!G8),5,IF(OR(AND('Jogos - Grupos'!F8='Jogos - Grupos'!G8,'Apostas - Grupos'!L7='Apostas - Grupos'!M7),AND('Jogos - Grupos'!F8&gt;'Jogos - Grupos'!G8,'Apostas - Grupos'!L7&gt;'Apostas - Grupos'!M7),AND('Jogos - Grupos'!F8&lt;'Jogos - Grupos'!G8,'Apostas - Grupos'!L7&lt;'Apostas - Grupos'!M7)),IF(('Apostas - Grupos'!L7-'Apostas - Grupos'!M7)=('Jogos - Grupos'!F8-'Jogos - Grupos'!G8),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="H7" s="106">
+      <c r="H7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F9="",'Jogos - Grupos'!G9=""),"-",IF(OR('Apostas - Grupos'!N7="",'Apostas - Grupos'!O7=""),0,IF(AND('Apostas - Grupos'!N7='Jogos - Grupos'!F9,'Apostas - Grupos'!O7='Jogos - Grupos'!G9),5,IF(OR(AND('Jogos - Grupos'!F9='Jogos - Grupos'!G9,'Apostas - Grupos'!N7='Apostas - Grupos'!O7),AND('Jogos - Grupos'!F9&gt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N7&gt;'Apostas - Grupos'!O7),AND('Jogos - Grupos'!F9&lt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N7&lt;'Apostas - Grupos'!O7)),IF(('Apostas - Grupos'!N7-'Apostas - Grupos'!O7)=('Jogos - Grupos'!F9-'Jogos - Grupos'!G9),3,2),0))))</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="106">
+        <v>-</v>
+      </c>
+      <c r="I7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F10="",'Jogos - Grupos'!G10=""),"-",IF(OR('Apostas - Grupos'!P7="",'Apostas - Grupos'!Q7=""),0,IF(AND('Apostas - Grupos'!P7='Jogos - Grupos'!F10,'Apostas - Grupos'!Q7='Jogos - Grupos'!G10),5,IF(OR(AND('Jogos - Grupos'!F10='Jogos - Grupos'!G10,'Apostas - Grupos'!P7='Apostas - Grupos'!Q7),AND('Jogos - Grupos'!F10&gt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P7&gt;'Apostas - Grupos'!Q7),AND('Jogos - Grupos'!F10&lt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P7&lt;'Apostas - Grupos'!Q7)),IF(('Apostas - Grupos'!P7-'Apostas - Grupos'!Q7)=('Jogos - Grupos'!F10-'Jogos - Grupos'!G10),3,2),0))))</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="J7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F11="",'Jogos - Grupos'!G11=""),"-",IF(OR('Apostas - Grupos'!R7="",'Apostas - Grupos'!S7=""),0,IF(AND('Apostas - Grupos'!R7='Jogos - Grupos'!F11,'Apostas - Grupos'!S7='Jogos - Grupos'!G11),5,IF(OR(AND('Jogos - Grupos'!F11='Jogos - Grupos'!G11,'Apostas - Grupos'!R7='Apostas - Grupos'!S7),AND('Jogos - Grupos'!F11&gt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R7&gt;'Apostas - Grupos'!S7),AND('Jogos - Grupos'!F11&lt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R7&lt;'Apostas - Grupos'!S7)),IF(('Apostas - Grupos'!R7-'Apostas - Grupos'!S7)=('Jogos - Grupos'!F11-'Jogos - Grupos'!G11),3,2),0))))</f>
@@ -13882,13 +13858,13 @@
         <f>IF(OR('Jogos - Grupos'!F14="",'Jogos - Grupos'!G14=""),"-",IF(OR('Apostas - Grupos'!X7="",'Apostas - Grupos'!Y7=""),0,IF(AND('Apostas - Grupos'!X7='Jogos - Grupos'!F14,'Apostas - Grupos'!Y7='Jogos - Grupos'!G14),5,IF(OR(AND('Jogos - Grupos'!F14='Jogos - Grupos'!G14,'Apostas - Grupos'!X7='Apostas - Grupos'!Y7),AND('Jogos - Grupos'!F14&gt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X7&gt;'Apostas - Grupos'!Y7),AND('Jogos - Grupos'!F14&lt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X7&lt;'Apostas - Grupos'!Y7)),IF(('Apostas - Grupos'!X7-'Apostas - Grupos'!Y7)=('Jogos - Grupos'!F14-'Jogos - Grupos'!G14),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="N7" s="106">
+      <c r="N7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F15="",'Jogos - Grupos'!G15=""),"-",IF(OR('Apostas - Grupos'!Z7="",'Apostas - Grupos'!AA7=""),0,IF(AND('Apostas - Grupos'!Z7='Jogos - Grupos'!F15,'Apostas - Grupos'!AA7='Jogos - Grupos'!G15),5,IF(OR(AND('Jogos - Grupos'!F15='Jogos - Grupos'!G15,'Apostas - Grupos'!Z7='Apostas - Grupos'!AA7),AND('Jogos - Grupos'!F15&gt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z7&gt;'Apostas - Grupos'!AA7),AND('Jogos - Grupos'!F15&lt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z7&lt;'Apostas - Grupos'!AA7)),IF(('Apostas - Grupos'!Z7-'Apostas - Grupos'!AA7)=('Jogos - Grupos'!F15-'Jogos - Grupos'!G15),3,2),0))))</f>
-        <v>0</v>
-      </c>
-      <c r="O7" s="106">
+        <v>-</v>
+      </c>
+      <c r="O7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F16="",'Jogos - Grupos'!G16=""),"-",IF(OR('Apostas - Grupos'!AB7="",'Apostas - Grupos'!AC7=""),0,IF(AND('Apostas - Grupos'!AB7='Jogos - Grupos'!F16,'Apostas - Grupos'!AC7='Jogos - Grupos'!G16),5,IF(OR(AND('Jogos - Grupos'!F16='Jogos - Grupos'!G16,'Apostas - Grupos'!AB7='Apostas - Grupos'!AC7),AND('Jogos - Grupos'!F16&gt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB7&gt;'Apostas - Grupos'!AC7),AND('Jogos - Grupos'!F16&lt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB7&lt;'Apostas - Grupos'!AC7)),IF(('Apostas - Grupos'!AB7-'Apostas - Grupos'!AC7)=('Jogos - Grupos'!F16-'Jogos - Grupos'!G16),3,2),0))))</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="P7" s="106" t="str">
         <f>IF(OR('Jogos - Grupos'!F17="",'Jogos - Grupos'!G17=""),"-",IF(OR('Apostas - Grupos'!AD7="",'Apostas - Grupos'!AE7=""),0,IF(AND('Apostas - Grupos'!AD7='Jogos - Grupos'!F17,'Apostas - Grupos'!AE7='Jogos - Grupos'!G17),5,IF(OR(AND('Jogos - Grupos'!F17='Jogos - Grupos'!G17,'Apostas - Grupos'!AD7='Apostas - Grupos'!AE7),AND('Jogos - Grupos'!F17&gt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD7&gt;'Apostas - Grupos'!AE7),AND('Jogos - Grupos'!F17&lt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD7&lt;'Apostas - Grupos'!AE7)),IF(('Apostas - Grupos'!AD7-'Apostas - Grupos'!AE7)=('Jogos - Grupos'!F17-'Jogos - Grupos'!G17),3,2),0))))</f>
@@ -14131,13 +14107,13 @@
       <c r="A8" s="82" t="s">
         <v>264</v>
       </c>
-      <c r="B8" s="108">
+      <c r="B8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F3="",'Jogos - Grupos'!G3=""),"-",IF(OR('Apostas - Grupos'!B8="",'Apostas - Grupos'!C8=""),0,IF(AND('Apostas - Grupos'!B8='Jogos - Grupos'!F3,'Apostas - Grupos'!C8='Jogos - Grupos'!G3),5,IF(OR(AND('Jogos - Grupos'!F3='Jogos - Grupos'!G3,'Apostas - Grupos'!B8='Apostas - Grupos'!C8),AND('Jogos - Grupos'!F3&gt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B8&gt;'Apostas - Grupos'!C8),AND('Jogos - Grupos'!F3&lt;'Jogos - Grupos'!G3,'Apostas - Grupos'!B8&lt;'Apostas - Grupos'!C8)),IF(('Apostas - Grupos'!B8-'Apostas - Grupos'!C8)=('Jogos - Grupos'!F3-'Jogos - Grupos'!G3),3,2),0))))</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="108">
+        <v>-</v>
+      </c>
+      <c r="C8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F4="",'Jogos - Grupos'!G4=""),"-",IF(OR('Apostas - Grupos'!D8="",'Apostas - Grupos'!E8=""),0,IF(AND('Apostas - Grupos'!D8='Jogos - Grupos'!F4,'Apostas - Grupos'!E8='Jogos - Grupos'!G4),5,IF(OR(AND('Jogos - Grupos'!F4='Jogos - Grupos'!G4,'Apostas - Grupos'!D8='Apostas - Grupos'!E8),AND('Jogos - Grupos'!F4&gt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D8&gt;'Apostas - Grupos'!E8),AND('Jogos - Grupos'!F4&lt;'Jogos - Grupos'!G4,'Apostas - Grupos'!D8&lt;'Apostas - Grupos'!E8)),IF(('Apostas - Grupos'!D8-'Apostas - Grupos'!E8)=('Jogos - Grupos'!F4-'Jogos - Grupos'!G4),3,2),0))))</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="D8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F5="",'Jogos - Grupos'!G5=""),"-",IF(OR('Apostas - Grupos'!F8="",'Apostas - Grupos'!G8=""),0,IF(AND('Apostas - Grupos'!F8='Jogos - Grupos'!F5,'Apostas - Grupos'!G8='Jogos - Grupos'!G5),5,IF(OR(AND('Jogos - Grupos'!F5='Jogos - Grupos'!G5,'Apostas - Grupos'!F8='Apostas - Grupos'!G8),AND('Jogos - Grupos'!F5&gt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F8&gt;'Apostas - Grupos'!G8),AND('Jogos - Grupos'!F5&lt;'Jogos - Grupos'!G5,'Apostas - Grupos'!F8&lt;'Apostas - Grupos'!G8)),IF(('Apostas - Grupos'!F8-'Apostas - Grupos'!G8)=('Jogos - Grupos'!F5-'Jogos - Grupos'!G5),3,2),0))))</f>
@@ -14155,13 +14131,13 @@
         <f>IF(OR('Jogos - Grupos'!F8="",'Jogos - Grupos'!G8=""),"-",IF(OR('Apostas - Grupos'!L8="",'Apostas - Grupos'!M8=""),0,IF(AND('Apostas - Grupos'!L8='Jogos - Grupos'!F8,'Apostas - Grupos'!M8='Jogos - Grupos'!G8),5,IF(OR(AND('Jogos - Grupos'!F8='Jogos - Grupos'!G8,'Apostas - Grupos'!L8='Apostas - Grupos'!M8),AND('Jogos - Grupos'!F8&gt;'Jogos - Grupos'!G8,'Apostas - Grupos'!L8&gt;'Apostas - Grupos'!M8),AND('Jogos - Grupos'!F8&lt;'Jogos - Grupos'!G8,'Apostas - Grupos'!L8&lt;'Apostas - Grupos'!M8)),IF(('Apostas - Grupos'!L8-'Apostas - Grupos'!M8)=('Jogos - Grupos'!F8-'Jogos - Grupos'!G8),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="H8" s="108">
+      <c r="H8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F9="",'Jogos - Grupos'!G9=""),"-",IF(OR('Apostas - Grupos'!N8="",'Apostas - Grupos'!O8=""),0,IF(AND('Apostas - Grupos'!N8='Jogos - Grupos'!F9,'Apostas - Grupos'!O8='Jogos - Grupos'!G9),5,IF(OR(AND('Jogos - Grupos'!F9='Jogos - Grupos'!G9,'Apostas - Grupos'!N8='Apostas - Grupos'!O8),AND('Jogos - Grupos'!F9&gt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N8&gt;'Apostas - Grupos'!O8),AND('Jogos - Grupos'!F9&lt;'Jogos - Grupos'!G9,'Apostas - Grupos'!N8&lt;'Apostas - Grupos'!O8)),IF(('Apostas - Grupos'!N8-'Apostas - Grupos'!O8)=('Jogos - Grupos'!F9-'Jogos - Grupos'!G9),3,2),0))))</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="108">
+        <v>-</v>
+      </c>
+      <c r="I8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F10="",'Jogos - Grupos'!G10=""),"-",IF(OR('Apostas - Grupos'!P8="",'Apostas - Grupos'!Q8=""),0,IF(AND('Apostas - Grupos'!P8='Jogos - Grupos'!F10,'Apostas - Grupos'!Q8='Jogos - Grupos'!G10),5,IF(OR(AND('Jogos - Grupos'!F10='Jogos - Grupos'!G10,'Apostas - Grupos'!P8='Apostas - Grupos'!Q8),AND('Jogos - Grupos'!F10&gt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P8&gt;'Apostas - Grupos'!Q8),AND('Jogos - Grupos'!F10&lt;'Jogos - Grupos'!G10,'Apostas - Grupos'!P8&lt;'Apostas - Grupos'!Q8)),IF(('Apostas - Grupos'!P8-'Apostas - Grupos'!Q8)=('Jogos - Grupos'!F10-'Jogos - Grupos'!G10),3,2),0))))</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="J8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F11="",'Jogos - Grupos'!G11=""),"-",IF(OR('Apostas - Grupos'!R8="",'Apostas - Grupos'!S8=""),0,IF(AND('Apostas - Grupos'!R8='Jogos - Grupos'!F11,'Apostas - Grupos'!S8='Jogos - Grupos'!G11),5,IF(OR(AND('Jogos - Grupos'!F11='Jogos - Grupos'!G11,'Apostas - Grupos'!R8='Apostas - Grupos'!S8),AND('Jogos - Grupos'!F11&gt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R8&gt;'Apostas - Grupos'!S8),AND('Jogos - Grupos'!F11&lt;'Jogos - Grupos'!G11,'Apostas - Grupos'!R8&lt;'Apostas - Grupos'!S8)),IF(('Apostas - Grupos'!R8-'Apostas - Grupos'!S8)=('Jogos - Grupos'!F11-'Jogos - Grupos'!G11),3,2),0))))</f>
@@ -14179,13 +14155,13 @@
         <f>IF(OR('Jogos - Grupos'!F14="",'Jogos - Grupos'!G14=""),"-",IF(OR('Apostas - Grupos'!X8="",'Apostas - Grupos'!Y8=""),0,IF(AND('Apostas - Grupos'!X8='Jogos - Grupos'!F14,'Apostas - Grupos'!Y8='Jogos - Grupos'!G14),5,IF(OR(AND('Jogos - Grupos'!F14='Jogos - Grupos'!G14,'Apostas - Grupos'!X8='Apostas - Grupos'!Y8),AND('Jogos - Grupos'!F14&gt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X8&gt;'Apostas - Grupos'!Y8),AND('Jogos - Grupos'!F14&lt;'Jogos - Grupos'!G14,'Apostas - Grupos'!X8&lt;'Apostas - Grupos'!Y8)),IF(('Apostas - Grupos'!X8-'Apostas - Grupos'!Y8)=('Jogos - Grupos'!F14-'Jogos - Grupos'!G14),3,2),0))))</f>
         <v>-</v>
       </c>
-      <c r="N8" s="108">
+      <c r="N8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F15="",'Jogos - Grupos'!G15=""),"-",IF(OR('Apostas - Grupos'!Z8="",'Apostas - Grupos'!AA8=""),0,IF(AND('Apostas - Grupos'!Z8='Jogos - Grupos'!F15,'Apostas - Grupos'!AA8='Jogos - Grupos'!G15),5,IF(OR(AND('Jogos - Grupos'!F15='Jogos - Grupos'!G15,'Apostas - Grupos'!Z8='Apostas - Grupos'!AA8),AND('Jogos - Grupos'!F15&gt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z8&gt;'Apostas - Grupos'!AA8),AND('Jogos - Grupos'!F15&lt;'Jogos - Grupos'!G15,'Apostas - Grupos'!Z8&lt;'Apostas - Grupos'!AA8)),IF(('Apostas - Grupos'!Z8-'Apostas - Grupos'!AA8)=('Jogos - Grupos'!F15-'Jogos - Grupos'!G15),3,2),0))))</f>
-        <v>0</v>
-      </c>
-      <c r="O8" s="108">
+        <v>-</v>
+      </c>
+      <c r="O8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F16="",'Jogos - Grupos'!G16=""),"-",IF(OR('Apostas - Grupos'!AB8="",'Apostas - Grupos'!AC8=""),0,IF(AND('Apostas - Grupos'!AB8='Jogos - Grupos'!F16,'Apostas - Grupos'!AC8='Jogos - Grupos'!G16),5,IF(OR(AND('Jogos - Grupos'!F16='Jogos - Grupos'!G16,'Apostas - Grupos'!AB8='Apostas - Grupos'!AC8),AND('Jogos - Grupos'!F16&gt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB8&gt;'Apostas - Grupos'!AC8),AND('Jogos - Grupos'!F16&lt;'Jogos - Grupos'!G16,'Apostas - Grupos'!AB8&lt;'Apostas - Grupos'!AC8)),IF(('Apostas - Grupos'!AB8-'Apostas - Grupos'!AC8)=('Jogos - Grupos'!F16-'Jogos - Grupos'!G16),3,2),0))))</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="P8" s="108" t="str">
         <f>IF(OR('Jogos - Grupos'!F17="",'Jogos - Grupos'!G17=""),"-",IF(OR('Apostas - Grupos'!AD8="",'Apostas - Grupos'!AE8=""),0,IF(AND('Apostas - Grupos'!AD8='Jogos - Grupos'!F17,'Apostas - Grupos'!AE8='Jogos - Grupos'!G17),5,IF(OR(AND('Jogos - Grupos'!F17='Jogos - Grupos'!G17,'Apostas - Grupos'!AD8='Apostas - Grupos'!AE8),AND('Jogos - Grupos'!F17&gt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD8&gt;'Apostas - Grupos'!AE8),AND('Jogos - Grupos'!F17&lt;'Jogos - Grupos'!G17,'Apostas - Grupos'!AD8&lt;'Apostas - Grupos'!AE8)),IF(('Apostas - Grupos'!AD8-'Apostas - Grupos'!AE8)=('Jogos - Grupos'!F17-'Jogos - Grupos'!G17),3,2),0))))</f>
@@ -14525,7 +14501,7 @@
       </c>
       <c r="C3" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A3)*('Jogos - Grupos'!$D$3:$D$74=$B3)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74&gt;'Jogos - Grupos'!$G$3:$G$74))+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A3)*('Jogos - Grupos'!$E$3:$E$74=$B3)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$G$3:$G$74&gt;'Jogos - Grupos'!$F$3:$F$74))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A3)*(('Jogos - Grupos'!$D$3:$D$74=$B3)+('Jogos - Grupos'!$E$3:$E$74=$B3))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
@@ -14533,23 +14509,23 @@
       </c>
       <c r="E3" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A3)*('Jogos - Grupos'!$D$3:$D$74=$B3)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A3)*('Jogos - Grupos'!$E$3:$E$74=$B3)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A3)*('Jogos - Grupos'!$D$3:$D$74=$B3)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A3)*('Jogos - Grupos'!$E$3:$E$74=$B3)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="110">
         <f t="shared" ref="G3:G50" si="0">E3-F3</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" s="8">
         <f t="shared" ref="H3:H50" si="1">3*C3+D3</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" s="110">
         <f t="shared" ref="I3:I50" si="2">H3*1000000000+(G3+200)*1000000+E3*1000+(500-K3)</f>
-        <v>3202003484</v>
+        <v>200000484</v>
       </c>
       <c r="J3" s="8">
         <f>RANK(I3,$I$3:$I$6,0)</f>
@@ -14576,15 +14552,15 @@
       </c>
       <c r="E4" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A4)*('Jogos - Grupos'!$D$3:$D$74=$B4)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A4)*('Jogos - Grupos'!$E$3:$E$74=$B4)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A4)*('Jogos - Grupos'!$D$3:$D$74=$B4)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A4)*('Jogos - Grupos'!$E$3:$E$74=$B4)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4" s="110">
         <f t="shared" si="0"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" si="1"/>
@@ -14592,11 +14568,11 @@
       </c>
       <c r="I4" s="110">
         <f t="shared" si="2"/>
-        <v>198001437</v>
+        <v>200000437</v>
       </c>
       <c r="J4" s="8">
         <f>RANK(I4,$I$3:$I$6,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" s="110">
         <v>63</v>
@@ -14623,11 +14599,11 @@
       </c>
       <c r="F5" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A5)*('Jogos - Grupos'!$D$3:$D$74=$B5)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A5)*('Jogos - Grupos'!$E$3:$E$74=$B5)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="110">
         <f t="shared" si="0"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="1"/>
@@ -14635,11 +14611,11 @@
       </c>
       <c r="I5" s="110">
         <f t="shared" si="2"/>
-        <v>198000477</v>
+        <v>200000477</v>
       </c>
       <c r="J5" s="8">
         <f>RANK(I5,$I$3:$I$6,0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K5" s="110">
         <v>23</v>
@@ -14654,7 +14630,7 @@
       </c>
       <c r="C6" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$D$3:$D$74=$B6)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74&gt;'Jogos - Grupos'!$G$3:$G$74))+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$E$3:$E$74=$B6)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$G$3:$G$74&gt;'Jogos - Grupos'!$F$3:$F$74))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*(('Jogos - Grupos'!$D$3:$D$74=$B6)+('Jogos - Grupos'!$E$3:$E$74=$B6))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
@@ -14662,7 +14638,7 @@
       </c>
       <c r="E6" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$D$3:$D$74=$B6)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$E$3:$E$74=$B6)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="110">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$D$3:$D$74=$B6)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A6)*('Jogos - Grupos'!$E$3:$E$74=$B6)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
@@ -14670,19 +14646,19 @@
       </c>
       <c r="G6" s="110">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" s="110">
         <f t="shared" si="2"/>
-        <v>3202002462</v>
+        <v>200000462</v>
       </c>
       <c r="J6" s="8">
         <f>RANK(I6,$I$3:$I$6,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" s="110">
         <v>38</v>
@@ -14697,7 +14673,7 @@
       </c>
       <c r="C7" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A7)*('Jogos - Grupos'!$D$3:$D$74=$B7)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74&gt;'Jogos - Grupos'!$G$3:$G$74))+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A7)*('Jogos - Grupos'!$E$3:$E$74=$B7)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$G$3:$G$74&gt;'Jogos - Grupos'!$F$3:$F$74))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A7)*(('Jogos - Grupos'!$D$3:$D$74=$B7)+('Jogos - Grupos'!$E$3:$E$74=$B7))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
@@ -14705,27 +14681,27 @@
       </c>
       <c r="E7" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A7)*('Jogos - Grupos'!$D$3:$D$74=$B7)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A7)*('Jogos - Grupos'!$E$3:$E$74=$B7)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A7)*('Jogos - Grupos'!$D$3:$D$74=$B7)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A7)*('Jogos - Grupos'!$E$3:$E$74=$B7)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="112">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="14">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I7" s="112">
         <f t="shared" si="2"/>
-        <v>3201002456</v>
+        <v>200000456</v>
       </c>
       <c r="J7" s="14">
         <f>RANK(I7,$I$7:$I$10,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K7" s="112">
         <v>44</v>
@@ -14748,15 +14724,15 @@
       </c>
       <c r="E8" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A8)*('Jogos - Grupos'!$D$3:$D$74=$B8)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A8)*('Jogos - Grupos'!$E$3:$E$74=$B8)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A8)*('Jogos - Grupos'!$D$3:$D$74=$B8)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A8)*('Jogos - Grupos'!$E$3:$E$74=$B8)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="112">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="14">
         <f t="shared" si="1"/>
@@ -14764,11 +14740,11 @@
       </c>
       <c r="I8" s="112">
         <f t="shared" si="2"/>
-        <v>199001445</v>
+        <v>200000445</v>
       </c>
       <c r="J8" s="14">
         <f>RANK(I8,$I$7:$I$10,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K8" s="112">
         <v>55</v>
@@ -14783,7 +14759,7 @@
       </c>
       <c r="C9" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A9)*('Jogos - Grupos'!$D$3:$D$74=$B9)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74&gt;'Jogos - Grupos'!$G$3:$G$74))+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A9)*('Jogos - Grupos'!$E$3:$E$74=$B9)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$G$3:$G$74&gt;'Jogos - Grupos'!$F$3:$F$74))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A9)*(('Jogos - Grupos'!$D$3:$D$74=$B9)+('Jogos - Grupos'!$E$3:$E$74=$B9))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
@@ -14791,7 +14767,7 @@
       </c>
       <c r="E9" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A9)*('Jogos - Grupos'!$D$3:$D$74=$B9)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A9)*('Jogos - Grupos'!$E$3:$E$74=$B9)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A9)*('Jogos - Grupos'!$D$3:$D$74=$B9)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A9)*('Jogos - Grupos'!$E$3:$E$74=$B9)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
@@ -14799,15 +14775,15 @@
       </c>
       <c r="G9" s="112">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="14">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I9" s="112">
         <f t="shared" si="2"/>
-        <v>3201001462</v>
+        <v>200000462</v>
       </c>
       <c r="J9" s="14">
         <f>RANK(I9,$I$7:$I$10,0)</f>
@@ -14838,11 +14814,11 @@
       </c>
       <c r="F10" s="112">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A10)*('Jogos - Grupos'!$D$3:$D$74=$B10)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A10)*('Jogos - Grupos'!$E$3:$E$74=$B10)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="112">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="14">
         <f t="shared" si="1"/>
@@ -14850,11 +14826,11 @@
       </c>
       <c r="I10" s="112">
         <f t="shared" si="2"/>
-        <v>199000480</v>
+        <v>200000480</v>
       </c>
       <c r="J10" s="14">
         <f>RANK(I10,$I$7:$I$10,0)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K10" s="112">
         <v>20</v>
@@ -14869,7 +14845,7 @@
       </c>
       <c r="C11" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$D$3:$D$74=$B11)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74&gt;'Jogos - Grupos'!$G$3:$G$74))+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$E$3:$E$74=$B11)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$G$3:$G$74&gt;'Jogos - Grupos'!$F$3:$F$74))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*(('Jogos - Grupos'!$D$3:$D$74=$B11)+('Jogos - Grupos'!$E$3:$E$74=$B11))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
@@ -14877,23 +14853,23 @@
       </c>
       <c r="E11" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$D$3:$D$74=$B11)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$E$3:$E$74=$B11)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F11" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$D$3:$D$74=$B11)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A11)*('Jogos - Grupos'!$E$3:$E$74=$B11)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" s="114">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="19">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" s="114">
         <f t="shared" si="2"/>
-        <v>3201003495</v>
+        <v>200000495</v>
       </c>
       <c r="J11" s="19">
         <f>RANK(I11,$I$11:$I$14,0)</f>
@@ -14920,15 +14896,15 @@
       </c>
       <c r="E12" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A12)*('Jogos - Grupos'!$D$3:$D$74=$B12)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A12)*('Jogos - Grupos'!$E$3:$E$74=$B12)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A12)*('Jogos - Grupos'!$D$3:$D$74=$B12)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A12)*('Jogos - Grupos'!$E$3:$E$74=$B12)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G12" s="114">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="19">
         <f t="shared" si="1"/>
@@ -14936,11 +14912,11 @@
       </c>
       <c r="I12" s="114">
         <f t="shared" si="2"/>
-        <v>199002486</v>
+        <v>200000486</v>
       </c>
       <c r="J12" s="19">
         <f>RANK(I12,$I$11:$I$14,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K12" s="114">
         <v>14</v>
@@ -14955,7 +14931,7 @@
       </c>
       <c r="C13" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A13)*('Jogos - Grupos'!$D$3:$D$74=$B13)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74&gt;'Jogos - Grupos'!$G$3:$G$74))+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A13)*('Jogos - Grupos'!$E$3:$E$74=$B13)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$G$3:$G$74&gt;'Jogos - Grupos'!$F$3:$F$74))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A13)*(('Jogos - Grupos'!$D$3:$D$74=$B13)+('Jogos - Grupos'!$E$3:$E$74=$B13))*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*('Jogos - Grupos'!$F$3:$F$74='Jogos - Grupos'!$G$3:$G$74))</f>
@@ -14963,7 +14939,7 @@
       </c>
       <c r="E13" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A13)*('Jogos - Grupos'!$D$3:$D$74=$B13)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A13)*('Jogos - Grupos'!$E$3:$E$74=$B13)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A13)*('Jogos - Grupos'!$D$3:$D$74=$B13)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A13)*('Jogos - Grupos'!$E$3:$E$74=$B13)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
@@ -14971,19 +14947,19 @@
       </c>
       <c r="G13" s="114">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="19">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I13" s="114">
         <f t="shared" si="2"/>
-        <v>3201001414</v>
+        <v>200000414</v>
       </c>
       <c r="J13" s="19">
         <f>RANK(I13,$I$11:$I$14,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K13" s="114">
         <v>86</v>
@@ -15010,11 +14986,11 @@
       </c>
       <c r="F14" s="114">
         <f>SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A14)*('Jogos - Grupos'!$D$3:$D$74=$B14)*ISNUMBER('Jogos - Grupos'!$G$3:$G$74)*'Jogos - Grupos'!$G$3:$G$74)+SUMPRODUCT(('Jogos - Grupos'!$C$3:$C$74=$A14)*('Jogos - Grupos'!$E$3:$E$74=$B14)*ISNUMBER('Jogos - Grupos'!$F$3:$F$74)*'Jogos - Grupos'!$F$3:$F$74)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="114">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="19">
         <f t="shared" si="1"/>
@@ -15022,11 +14998,11 @@
       </c>
       <c r="I14" s="114">
         <f t="shared" si="2"/>
-        <v>199000473</v>
+        <v>200000473</v>
       </c>
       <c r="J14" s="19">
         <f>RANK(I14,$I$11:$I$14,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K14" s="114">
         <v>27</v>
@@ -16607,15 +16583,15 @@
       </c>
       <c r="C53" s="135" t="str">
         <f>IFERROR(INDEX($B$3:$B$6,MATCH(2,$J$3:$J$6,0)),"?")</f>
-        <v>Tchequia</v>
+        <v>Coreia do Sul</v>
       </c>
       <c r="D53" s="135" t="str">
         <f>IFERROR(INDEX($B$3:$B$6,MATCH(3,$J$3:$J$6,0)),"?")</f>
-        <v>Africa do Sul</v>
+        <v>Tchequia</v>
       </c>
       <c r="E53" s="135" t="str">
         <f>IFERROR(INDEX($B$3:$B$6,MATCH(4,$J$3:$J$6,0)),"?")</f>
-        <v>Coreia do Sul</v>
+        <v>Africa do Sul</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
@@ -16624,7 +16600,7 @@
       </c>
       <c r="B54" s="135" t="str">
         <f>IFERROR(INDEX($B$7:$B$10,MATCH(1,$J$7:$J$10,0)),"?")</f>
-        <v>Canada</v>
+        <v>Suica</v>
       </c>
       <c r="C54" s="135" t="str">
         <f>IFERROR(INDEX($B$7:$B$10,MATCH(2,$J$7:$J$10,0)),"?")</f>
@@ -16632,11 +16608,11 @@
       </c>
       <c r="D54" s="135" t="str">
         <f>IFERROR(INDEX($B$7:$B$10,MATCH(3,$J$7:$J$10,0)),"?")</f>
-        <v>Bosnia e Herzegovina</v>
+        <v>Canada</v>
       </c>
       <c r="E54" s="135" t="str">
         <f>IFERROR(INDEX($B$7:$B$10,MATCH(4,$J$7:$J$10,0)),"?")</f>
-        <v>Suica</v>
+        <v>Bosnia e Herzegovina</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
@@ -16649,15 +16625,15 @@
       </c>
       <c r="C55" s="135" t="str">
         <f>IFERROR(INDEX($B$11:$B$14,MATCH(2,$J$11:$J$14,0)),"?")</f>
-        <v>Haiti</v>
+        <v>Marrocos</v>
       </c>
       <c r="D55" s="135" t="str">
         <f>IFERROR(INDEX($B$11:$B$14,MATCH(3,$J$11:$J$14,0)),"?")</f>
-        <v>Marrocos</v>
+        <v>Escocia</v>
       </c>
       <c r="E55" s="135" t="str">
         <f>IFERROR(INDEX($B$11:$B$14,MATCH(4,$J$11:$J$14,0)),"?")</f>
-        <v>Escocia</v>
+        <v>Haiti</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -16869,15 +16845,15 @@
       </c>
       <c r="B68" s="149" t="str">
         <f>IFERROR(INDEX($B$3:$B$6,MATCH(3,$J$3:$J$6,0)),"?")</f>
-        <v>Africa do Sul</v>
+        <v>Tchequia</v>
       </c>
       <c r="C68" s="149">
         <f>IFERROR(INDEX($I$3:$I$6,MATCH(3,$J$3:$J$6,0)),0)</f>
-        <v>198001437</v>
+        <v>200000462</v>
       </c>
       <c r="D68" s="150">
         <f t="shared" ref="D68:D79" si="3">RANK(C68,$C$68:$C$79,0)</f>
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -16886,15 +16862,15 @@
       </c>
       <c r="B69" s="149" t="str">
         <f>IFERROR(INDEX($B$7:$B$10,MATCH(3,$J$7:$J$10,0)),"?")</f>
-        <v>Bosnia e Herzegovina</v>
+        <v>Canada</v>
       </c>
       <c r="C69" s="149">
         <f>IFERROR(INDEX($I$7:$I$10,MATCH(3,$J$7:$J$10,0)),0)</f>
-        <v>199001445</v>
+        <v>200000456</v>
       </c>
       <c r="D69" s="150">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -16903,15 +16879,15 @@
       </c>
       <c r="B70" s="149" t="str">
         <f>IFERROR(INDEX($B$11:$B$14,MATCH(3,$J$11:$J$14,0)),"?")</f>
-        <v>Marrocos</v>
+        <v>Escocia</v>
       </c>
       <c r="C70" s="149">
         <f>IFERROR(INDEX($I$11:$I$14,MATCH(3,$J$11:$J$14,0)),0)</f>
-        <v>199002486</v>
+        <v>200000473</v>
       </c>
       <c r="D70" s="150">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -16928,7 +16904,7 @@
       </c>
       <c r="D71" s="150">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -16945,7 +16921,7 @@
       </c>
       <c r="D72" s="150">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -16979,7 +16955,7 @@
       </c>
       <c r="D74" s="150">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -16996,7 +16972,7 @@
       </c>
       <c r="D75" s="150">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -17013,7 +16989,7 @@
       </c>
       <c r="D76" s="150">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -17030,7 +17006,7 @@
       </c>
       <c r="D77" s="150">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -17047,7 +17023,7 @@
       </c>
       <c r="D78" s="150">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -17064,7 +17040,7 @@
       </c>
       <c r="D79" s="150">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
@@ -17090,7 +17066,7 @@
       </c>
       <c r="B83" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(2,$D$68:$D$79,0)),"?")</f>
-        <v>Noruega</v>
+        <v>Escocia</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
@@ -17099,7 +17075,7 @@
       </c>
       <c r="B84" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(3,$D$68:$D$79,0)),"?")</f>
-        <v>Argelia</v>
+        <v>Noruega</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
@@ -17108,7 +17084,7 @@
       </c>
       <c r="B85" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(4,$D$68:$D$79,0)),"?")</f>
-        <v>Turquia</v>
+        <v>Argelia</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
@@ -17117,7 +17093,7 @@
       </c>
       <c r="B86" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(5,$D$68:$D$79,0)),"?")</f>
-        <v>?</v>
+        <v>Turquia</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
@@ -17126,7 +17102,7 @@
       </c>
       <c r="B87" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(6,$D$68:$D$79,0)),"?")</f>
-        <v>Costa do Marfim</v>
+        <v>?</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
@@ -17135,7 +17111,7 @@
       </c>
       <c r="B88" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(7,$D$68:$D$79,0)),"?")</f>
-        <v>Gana</v>
+        <v>Tchequia</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
@@ -17144,7 +17120,7 @@
       </c>
       <c r="B89" s="164" t="str">
         <f>IFERROR(INDEX($B$68:$B$79,MATCH(8,$D$68:$D$79,0)),"?")</f>
-        <v>Arabia Saudita</v>
+        <v>Costa do Marfim</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
@@ -17153,7 +17129,7 @@
       </c>
       <c r="B92" s="166" t="str">
         <f>IF(D68&lt;=8,"A","")&amp;IF(D69&lt;=8,"B","")&amp;IF(D70&lt;=8,"C","")&amp;IF(D71&lt;=8,"D","")&amp;IF(D72&lt;=8,"E","")&amp;IF(D73&lt;=8,"F","")&amp;IF(D74&lt;=8,"G","")&amp;IF(D75&lt;=8,"H","")&amp;IF(D76&lt;=8,"I","")&amp;IF(D77&lt;=8,"J","")&amp;IF(D78&lt;=8,"K","")&amp;IF(D79&lt;=8,"L","")</f>
-        <v>DEFGHIJKL</v>
+        <v>ACDEFGIJ</v>
       </c>
     </row>
   </sheetData>
@@ -43662,7 +43638,7 @@
       </c>
       <c r="D4" s="175" t="str">
         <f>IFERROR('Classif - Grupos'!C53,"Aguardando")</f>
-        <v>Tchequia</v>
+        <v>Coreia do Sul</v>
       </c>
       <c r="E4" s="175" t="str">
         <f>IFERROR('Classif - Grupos'!C54,"Aguardando")</f>
@@ -43696,7 +43672,7 @@
       </c>
       <c r="E5" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,5,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Aguardando</v>
+        <v>Turquia</v>
       </c>
       <c r="F5" s="249"/>
       <c r="G5" s="249"/>
@@ -43726,7 +43702,7 @@
       </c>
       <c r="E6" s="175" t="str">
         <f>IFERROR('Classif - Grupos'!C55,"Aguardando")</f>
-        <v>Haiti</v>
+        <v>Marrocos</v>
       </c>
       <c r="F6" s="249"/>
       <c r="G6" s="249"/>
@@ -43786,7 +43762,7 @@
       </c>
       <c r="E8" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,7,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Aguardando</v>
+        <v>Suecia</v>
       </c>
       <c r="F8" s="249"/>
       <c r="G8" s="249"/>
@@ -43846,7 +43822,7 @@
       </c>
       <c r="E10" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,2,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Aguardando</v>
+        <v>Escocia</v>
       </c>
       <c r="F10" s="249"/>
       <c r="G10" s="249"/>
@@ -43876,7 +43852,7 @@
       </c>
       <c r="E11" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,9,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Aguardando</v>
+        <v>Noruega</v>
       </c>
       <c r="F11" s="249"/>
       <c r="G11" s="249"/>
@@ -43906,7 +43882,7 @@
       </c>
       <c r="E12" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,4,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Aguardando</v>
+        <v>Argelia</v>
       </c>
       <c r="F12" s="249"/>
       <c r="G12" s="249"/>
@@ -43936,7 +43912,7 @@
       </c>
       <c r="E13" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,6,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Aguardando</v>
+        <v>Tchequia</v>
       </c>
       <c r="F13" s="249"/>
       <c r="G13" s="249"/>
@@ -44022,11 +43998,11 @@
       </c>
       <c r="D16" s="175" t="str">
         <f>IFERROR('Classif - Grupos'!B54,"Aguardando")</f>
-        <v>Canada</v>
+        <v>Suica</v>
       </c>
       <c r="E16" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,3,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Aguardando</v>
+        <v>Egito</v>
       </c>
       <c r="F16" s="249"/>
       <c r="G16" s="249"/>
@@ -44086,7 +44062,7 @@
       </c>
       <c r="E18" s="175" t="str">
         <f>IFERROR(IFERROR(INDEX('Classif - Grupos'!$B$68:$B$79,MATCH(MID(IFERROR(VLOOKUP('Classif - Grupos'!B92,'T495'!$A$2:$I$496,8,FALSE),""),2,1),'Classif - Grupos'!$A$68:$A$79,0)),"Aguardando"),"Aguardando")</f>
-        <v>Aguardando</v>
+        <v>Costa do Marfim</v>
       </c>
       <c r="F18" s="249"/>
       <c r="G18" s="249"/>
